--- a/data/furniture.xlsx
+++ b/data/furniture.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E36F6A8B-3F09-412E-AF07-CDA19F143CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98AB1377-DA10-4E8D-9E0C-6724EC958207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmark" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="293">
   <si>
     <t>Prompt 1</t>
   </si>
@@ -316,6 +316,9 @@
     <t>Poziom pewności</t>
   </si>
   <si>
+    <t>Search Features</t>
+  </si>
+  <si>
     <t>Fotel typ 366</t>
   </si>
   <si>
@@ -349,6 +352,9 @@
     <t>opracowania dotyczące Józefa Chierowskiego; dokumentacja 366 Concept; zbiory Muzeum Narodowego w Warszawie; Polski New Look Ewa Solarz i Agnieszka Sural; publikacje o polskim wzornictwie powojennym</t>
   </si>
   <si>
+    <t>drewniane boczki tworzące nogi i podłokietniki; trapezowe oparcie zwężające się ku górze; trapezowe siedzisko zwężające się ku tyłowi; widoczny prześwit pod siedziskiem; oddzielne moduły tapicerowanego siedziska i oparcia; skośnie rozstawione nogi; pozioma linia podłokietników; odsłonięte drewniane elementy boczne; lekka geometryczna bryła; brak tapicerowanych boków; zwężające się ku dołowi nogi; charakterystyczny profil boczny w kształcie odwróconego V</t>
+  </si>
+  <si>
     <t>Fotel typ 300-190</t>
   </si>
   <si>
@@ -376,6 +382,9 @@
     <t>Nowohuckie Renowacje – Fotel Lisek typ 300-190; Conchita Home – 4 fotele z PRL które musisz znać; dokumentacja i opisy egzemplarzy Typ 300-190; archiwalne materiały producentów cytowane w opracowaniach specjalistycznych</t>
   </si>
   <si>
+    <t>płaskie drewniane podłokietniki; toczone nogi zwężające się ku dołowi; nogi przechodzące przez podłokietniki; widoczna prostokątna rama boczna; poziome poprzeczki między nogami; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; duży prześwit pod siedziskiem; smukła lekka bryła; odsłonięta konstrukcja drewniana; niskie podłokietniki; geometryczny profil boczny</t>
+  </si>
+  <si>
     <t>Do weryfikacji; często błędnie określany jako „Lisek”</t>
   </si>
   <si>
@@ -403,6 +412,9 @@
     <t>Patyna.pl – fotel B-7727 Radomsko PRL; Meblostan – fotel B-7727; Nowohuckie Renowacje – fotel B-7727; Vilandy – fotel Lis typ B-7727; Allegro – fotel PRL model B-7727 Radomsko lata 70; Reko-Czyny – identyfikacja fotela B-7727</t>
   </si>
   <si>
+    <t>otwarta drewniana rama boczna; prostokątne szerokie oparcie; oparcie szersze niż w modelu 300-190; prostokątne siedzisko; okrągłe toczone nogi; poziome drewniane podłokietniki; widoczne połączenia ramy bocznej; duży prześwit pod siedziskiem; lekka geometryczna bryła; drewniane belki łączące nogi; rozbieralne moduły siedziska i oparcia; nisko osadzone siedzisko</t>
+  </si>
+  <si>
     <t>Typ 300-177</t>
   </si>
   <si>
@@ -433,6 +445,9 @@
     <t>Meblostan – Fotel Bunny typ 300-177; Nowohuckie Renowacje – Fotel typ 300-177 Zajączek; Patyna.pl – Fotel Bunny typ 300-177; Tkaniny-Meblowe.pl – Fotele z PRL-u; materiały kolekcjonerskie rynku vintage</t>
   </si>
   <si>
+    <t>trójkątne podłokietniki przypominające uszy zająca; otwarta drewniana rama boczna; szeroko rozstawione nogi; podłokietniki połączone z przednimi nogami; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; duży prześwit pod siedziskiem; smukła lekka bryła; odsłonięty drewniany stelaż; skośne tylne nogi; geometryczny profil boczny; kompaktowe proporcje</t>
+  </si>
+  <si>
     <t>Fotel Ewa; Muszelka Ewa</t>
   </si>
   <si>
@@ -457,6 +472,9 @@
     <t>Meblostan – Para foteli tapicerowanych EWA; Odnowa Mebli – Fotel Ewa; Patyna.pl – Komplet foteli typ Ewa; materiały kolekcjonerskie rynku vintage</t>
   </si>
   <si>
+    <t>muszelkowy korpus; kubełkowe siedzisko; zaokrąglone oparcie; stalowy stelaż; cztery smukłe metalowe nogi; wykręcane nogi; kulowe stopki; brak drewnianych podłokietników; jednolita tapicerowana bryła; szerokie półkoliste oparcie; lekka forma na wysokich nogach; profil przypominający muszlę</t>
+  </si>
+  <si>
     <t>Typ 300-123</t>
   </si>
   <si>
@@ -484,6 +502,9 @@
     <t>Nowohuckie Renowacje – Fotel typ 300-123 Puchała; Szajba Sklep – Fotel klubowy typ 300-123 proj. M. Puchała; LookInside – Fotel typ 300-123 Puchała; Pakamera – Fotel typ 300-123 M. Puchała; Meblostan – Fotel Puchały typ 300-123</t>
   </si>
   <si>
+    <t>gięte drewniane podłokietniki; smukłe wysokie oparcie; wąskie proporcje korpusu; otwarta drewniana rama boczna; toczone nogi zwężające się ku dołowi; widoczny prześwit pod siedziskiem; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; lekka dynamiczna bryła; cienkie elementy konstrukcyjne; profil boczny z łukowato wygiętym podłokietnikiem; minimalistyczna forma lat 50./60.</t>
+  </si>
+  <si>
     <t>RM58</t>
   </si>
   <si>
@@ -511,6 +532,9 @@
     <t>Muzeum Narodowe we Wrocławiu; Vzór – dokumentacja reedycji RM58; Instytut Wzornictwa Przemysłowego; publikacje o twórczości Romana Modzelewskiego; Culture.pl</t>
   </si>
   <si>
+    <t>jednoczęściowa muszelkowa skorupa; organiczna opływowa bryła; głębokie kubełkowe siedzisko; szerokie wywinięte boki; zaokrąglone wysokie oparcie; brak oddzielnych podłokietników; korpus przypominający muszlę; zamknięta forma boczna; cztery cienkie nogi; futurystyczna sylwetka lat 50.; brak widocznej drewnianej konstrukcji; płynne przejścia między siedziskiem i oparciem; asymetrycznie zaokrąglone krawędzie; korpus wykonany jako pojedyncza skorupa</t>
+  </si>
+  <si>
     <t>B-2020</t>
   </si>
   <si>
@@ -541,6 +565,9 @@
     <t>FAMEG – Fotel Tulipan B-2020; dokumentacja reedycji FAMEG; opracowania dotyczące twórczości Teresy Kruszewskiej</t>
   </si>
   <si>
+    <t>kubełkowe siedzisko; forma przypominająca kielich tulipana; szeroko rozchylone boki; jednolita tapicerowana skorupa; zaokrąglone wysokie oparcie; płynne przejście między siedziskiem i oparciem; organiczna bryła; brak widocznej drewnianej ramy bocznej; miękkie obłe krawędzie; rzeźbiarska forma; kompaktowa podstawa; sylwetka kwiatu tulipana</t>
+  </si>
+  <si>
     <t>Typ 300-201</t>
   </si>
   <si>
@@ -566,368 +593,338 @@
   </si>
   <si>
     <t>Meblostan – Fotel Śnieżnik typ 300-201; Nowohuckie Renowacje – Fotele PRL; Pakamera – Fotel Śnieżnik typ 300-201; Audiovintage Store – Fotel klubowy Śnieżnik 300-201</t>
-  </si>
-  <si>
-    <t>GFM-57</t>
-  </si>
-  <si>
-    <t>Skoczek</t>
-  </si>
-  <si>
-    <t>Juliusz Kędziorek</t>
-  </si>
-  <si>
-    <t>Krzesło</t>
-  </si>
-  <si>
-    <t>Gościcińska Fabryka Mebli; Zamojskie Fabryki Mebli (produkcja seryjna jako typ 200-203)</t>
-  </si>
-  <si>
-    <t>łukowate podłokietniki przypominające profil skoczni narciarskiej; elipsoidalne oparcie; lekka ażurowa konstrukcja; zwężające się ku dołowi nogi; tapicerowane siedzisko; smukła sylwetka; organiczna linia boczna</t>
-  </si>
-  <si>
-    <t>drewniany stelaż; otwarta konstrukcja boczna; tapicerowane siedzisko; gięte elementy drewniane; konstrukcja przeznaczona do produkcji seryjnej</t>
-  </si>
-  <si>
-    <t>typ 200-190 Rajmunda Hałasa; krzesła Aga; krzesła patyczaki lat 60.; lekkie krzesła tapicerowane PRL</t>
-  </si>
-  <si>
-    <t>typ 200-203; GFM-107; projekty Juliusza Kędziorka dla Gościcińskiej Fabryki Mebli</t>
-  </si>
-  <si>
-    <t>Magazif – Krzesło Skoczek; Ikony Designu PL – Krzesło GFM-57 Skoczek; Meblostan – Krzesło Skoczek; Sosenko Home Decor – Krzesło Skoczek; Allegro Artykuł – Krzesło kilka słów o najtrudniejszym meblu</t>
-  </si>
-  <si>
-    <t>Typ 200-125 VAR</t>
-  </si>
-  <si>
-    <t>Aga</t>
-  </si>
-  <si>
-    <t>ok. 1972–1975 (w źródłach występują rozbieżności dotyczące dokładnego roku projektu)</t>
-  </si>
-  <si>
-    <t>Wielkopolskie Fabryki Mebli; produkcja seryjna PRL (pozostali producenci wymagają weryfikacji)</t>
-  </si>
-  <si>
-    <t>wysokie tapicerowane oparcie; trapezowy układ nóg; miękkie tapicerowane siedzisko; smukła skandynawska forma; zwężająca się ku górze bryła; lekkie proporcje; drewniana konstrukcja eksponowana po bokach</t>
-  </si>
-  <si>
-    <t>drewniany stelaż bukowy; tapicerowane siedzisko; tapicerowane oparcie; sprężyny siedziska; cztery drewniane nogi; konstrukcja przeznaczona do intensywnego użytkowania klubowego</t>
-  </si>
-  <si>
-    <t>typ 200-190 Rajmunda Hałasa; GFM-57 Skoczek; lekkie krzesła klubowe PRL lat 70.</t>
-  </si>
-  <si>
-    <t>fotel 366; meble klubowe Józefa Chierowskiego; reedycja 200-125 VAR realizowana przez 366 Concept</t>
-  </si>
-  <si>
-    <t>Elle Decoration Polska – Krzesło VAR AGA projektu Józefa Chierowskiego; Nowohuckie Renowacje – Krzesło Aga typ 200-125; Patyna.pl – Krzesła AGA typu 200-125 VAR; Linie Studio – 200-125 VAR; Meblościanka – 200-125 VAR</t>
-  </si>
-  <si>
-    <t>Typ 200-190</t>
-  </si>
-  <si>
-    <t>Hałas; Grzybek</t>
-  </si>
-  <si>
-    <t>Rajmund Teofil Hałas</t>
-  </si>
-  <si>
-    <t>lata 60. XX w.; dokładny rok projektu – Do weryfikacji</t>
-  </si>
-  <si>
-    <t>Zakłady Mebli w Gostyniu (Do weryfikacji); produkcja seryjna w kilku zakładach meblarskich PRL – Do weryfikacji</t>
-  </si>
-  <si>
-    <t>okrągła forma oparcia przypominająca kapelusz grzyba; tapicerowane oparcie i siedzisko; smukłe zwężające się nogi; lekka konstrukcja; wyraźnie wyodrębnione oparcie nad siedziskiem; proporcje inspirowane wzornictwem skandynawskim; minimalistyczna sylwetka</t>
-  </si>
-  <si>
-    <t>drewniany stelaż; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; mocowane oddzielnie siedzisko i oparcie; nogi zwężające się ku dołowi</t>
-  </si>
-  <si>
-    <t>Aga 200-125; Skoczek GFM-57; krzesła skandynawskie lat 60.; lekkie krzesła tapicerowane PRL</t>
-  </si>
-  <si>
-    <t>projekty Rajmunda Teofila Hałasa; krzesła tapicerowane PRL lat 60.; warianty produkcyjne typu 200-190</t>
-  </si>
-  <si>
-    <t>Odnawialnia – Wiem co odnawiam | krzesło Hałasa typ 200-190; Patyna.pl – Krzesła typ 200-190 Rajmund Teofil Hałas; Meblostan – Komplet krzeseł typ 200-190; Daniel Stoiński Redesign – Przewodnik po renowacji krzesła 200-190; Homebook – Krzesło Hałasa typ 200-190</t>
-  </si>
-  <si>
-    <t>B-6028</t>
-  </si>
-  <si>
-    <t>Barbara Fenrych-Węcławska (Do weryfikacji); Józef Chierowski (Do weryfikacji – atrybucja pojawiająca się wyłącznie w źródłach kolekcjonerskich)</t>
-  </si>
-  <si>
-    <t>lata 60. XX w.</t>
-  </si>
-  <si>
-    <t>Fabryka Mebli Giętych w Radomsku; FAMEG Radomsko; Radomszczańska Fabryka Mebli Giętych</t>
-  </si>
-  <si>
-    <t>wysokie profilowane oparcie; szerokie drewniane podłokietniki; gięte elementy bukowe; głębokie siedzisko; lekka otwarta konstrukcja boczna; elegancka smukła sylwetka; forma łącząca cechy fotela klubowego i wypoczynkowego</t>
-  </si>
-  <si>
-    <t>stelaż z giętego drewna bukowego; otwarta konstrukcja ramowa; tapicerowane siedzisko; tapicerowane oparcie; drewniane podłokietniki zintegrowane z ramą; konstrukcja szkieletowa</t>
-  </si>
-  <si>
-    <t>typ 300-123 Puchała; typ 300-177 Zajączek; B-7727; typ 366</t>
-  </si>
-  <si>
-    <t>fotele Radomsko z giętego drewna; projekty Barbary Fenrych-Węcławskiej (Do weryfikacji); lekkie fotele klubowe PRL lat 60.</t>
-  </si>
-  <si>
-    <t>MidMod – Fotel B6028 FAMEG Radomsko Polska lata 60; Oldsen Design – Fotel B6028 prod. FAMEG Radomsko; Nowohuckie Renowacje – Fotel PRL B-6028 z lat 60-tych; Fotelowo Facebook – fotel projektu Barbary Fenrych-Węcławskiej; Instagram Renowacja Mebli PRL – B6028 lata produkcji 1960</t>
-  </si>
-  <si>
-    <t>A. Dutka</t>
-  </si>
-  <si>
-    <t>1966–1968</t>
-  </si>
-  <si>
-    <t>Zakłady Mebli Giętych w Radomsku; Gołuchowskie Fabryki Mebli</t>
-  </si>
-  <si>
-    <t>duże gabaryty; szerokie głębokie siedzisko; masywne drewniane podłokietniki; geometryczna forma boczna; lekko pochylone oparcie; otwarta konstrukcja ramowa; modernistyczna sylwetka eksportowa</t>
-  </si>
-  <si>
-    <t>stelaż z drewna bukowego; sprężyny lejowe w siedzisku; tapicerowane siedzisko i oparcie; otwarta konstrukcja boczna; drewniane podłokietniki zintegrowane z ramą; konstrukcja rozbieralna skręcana śrubami</t>
-  </si>
-  <si>
-    <t>B-6028; GFM-64; typ 300-190 Lisek; B-7727</t>
-  </si>
-  <si>
-    <t>fotele eksportowe Radomsko lat 60.; modele Zakładów Mebli Giętych w Radomsku; konstrukcje projektowane przez A. Dutkę (Do weryfikacji)</t>
-  </si>
-  <si>
-    <t>Meblostan – Para foteli B-310 VAR; Pufa Design – Oryginalny fotel B-310 VAR; Yestersen – Fotel B-310 VAR Polska lata 70.; Reko-Czyny – Fotel B-310 VAR metamorfoza; archiwalne ogłoszenia kolekcjonerskie B-310 VAR</t>
-  </si>
-  <si>
-    <t>GFM-22 (typ 200/128)</t>
-  </si>
-  <si>
-    <t>ok. 1960</t>
-  </si>
-  <si>
-    <t>Gościcińska Fabryka Mebli (GFM)</t>
-  </si>
-  <si>
-    <t>nerkowate oparcie; lekka ażurowa konstrukcja; smukłe zwężające się nogi; gięta drewniana rama; tapicerowane siedzisko; tapicerowane oparcie; wyraźnie rozstawione tylne nogi</t>
-  </si>
-  <si>
-    <t>drewniany stelaż; gięte elementy z litego drewna; tapicerowane siedzisko; tapicerowane oparcie ze sklejki giętej; konstrukcja szkieletowa przeznaczona do produkcji seryjnej</t>
-  </si>
-  <si>
-    <t>GFM-57 Skoczek; typ 200-190 Rajmunda Hałasa; Aga 200-125; krzesła skandynawskie z lat 60.</t>
-  </si>
-  <si>
-    <t>typ 200/128; projekty Juliusza Kędziorka dla Gościcińskiej Fabryki Mebli; GFM-57; GFM-87</t>
-  </si>
-  <si>
-    <t>Pamono – Mid-Century GFM-22 Chairs by Juliusz Kędziorek; Vinterior – GFM-22 model 200/128; Selency – Iconic GFM-22 Chair by Juliusz Kędziorek; Instagram Zostań z Vintage – Krzesło GFM-22 typ 200/128</t>
-  </si>
-  <si>
-    <t>Typ 1020</t>
-  </si>
-  <si>
-    <t>Muszelka</t>
-  </si>
-  <si>
-    <t>Wiesław Leśniewski; Stanisław Lejkowski</t>
-  </si>
-  <si>
-    <t>Słupskie Fabryki Mebli</t>
-  </si>
-  <si>
-    <t>muszelkowe profilowane oparcie; jednolita tapicerowana skorupa; zaokrąglona górna krawędź oparcia; smukłe stożkowe nogi; lekka modernistyczna forma; brak podłokietników; organiczna sylwetka</t>
-  </si>
-  <si>
-    <t>profilowana skorupa ze sklejki; tapicerowana skorupa; drewniany stelaż; cztery drewniane nogi; konstrukcja szkieletowa; połączenie sklejki i drewna litego</t>
-  </si>
-  <si>
-    <t>RM58; krzesła muszelkowe produkcji NRD; krzesła skandynawskie lat 60.; fotel Ewa</t>
-  </si>
-  <si>
-    <t>krzesła muszelkowe Słupskich Fabryk Mebli; projekty Wiesława Leśniewskiego i Stanisława Lejkowskiego; meble ze sklejki profilowanej produkowane przez SFM</t>
-  </si>
-  <si>
-    <t>Archiwalne katalogi Słupskich Fabryk Mebli; opracowania kolekcjonerskie dotyczące wzornictwa SFM; materiały renowatorów specjalizujących się w meblach PRL; publikacje poświęcone projektom Wiesława Leśniewskiego i Stanisława Lejkowskiego</t>
-  </si>
-  <si>
-    <t>Bumerang</t>
-  </si>
-  <si>
-    <t>Ryszard Kulm</t>
-  </si>
-  <si>
-    <t>przełom lat 50. i 60. XX w.; produkcja seryjna od początku lat 60</t>
-  </si>
-  <si>
-    <t>Gościcińska Fabryka Mebli</t>
-  </si>
-  <si>
-    <t>charakterystyczne łukowato wygięte przednie nogi przypominające bumerang; lekka ażurowa konstrukcja; tapicerowane siedzisko; tapicerowane oparcie; smukła sylwetka; zwężające się ku dołowi nogi; modernistyczna forma inspirowana skandynawskim wzornictwem</t>
-  </si>
-  <si>
-    <t>drewniany stelaż bukowy; gięte elementy boczne; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; połączenia skręcane i klejone</t>
-  </si>
-  <si>
-    <t>GFM-22; typ 200-190 Rajmunda Hałasa; GFM-57 Skoczek; krzesła skandynawskie lat 60</t>
-  </si>
-  <si>
-    <t>krzesła Gościcińskiej Fabryki Mebli; wariant 299XB (Do weryfikacji); rodzina krzeseł Bumerang</t>
-  </si>
-  <si>
-    <t>Meblostan – Komplet 4 krzeseł Bumerang typ 299; Skarby PRL – Krzesło tapicerowane Bumerang typ 299; Patyna – Komplet krzeseł typ 299 Bumerang; Deccoria – 10 słynnych mebli z PRL; Stary Fotel – Krzesła Bumerang metamorfoza</t>
-  </si>
-  <si>
-    <t>Typ 300-227</t>
-  </si>
-  <si>
-    <t>Celia</t>
-  </si>
-  <si>
-    <t>ok. 1965; produkcja na przełomie lat 60. i 70. XX w.</t>
-  </si>
-  <si>
-    <t>Zamojskie Fabryki Mebli</t>
-  </si>
-  <si>
-    <t>brak podłokietników; toczone drewniane nogi umieszczone po bokach części tapicerowanej; trapezowe siedzisko; proste tapicerowane oparcie; lekka minimalistyczna forma; kompaktowe wymiary; stylistyka skandynawskiego modernizmu</t>
-  </si>
-  <si>
-    <t>drewniany stelaż; toczone nogi; tapicerowane siedzisko; tapicerowane oparcie; otwarta konstrukcja bez podłokietników; konstrukcja szkieletowa przeznaczona do produkcji seryjnej</t>
-  </si>
-  <si>
-    <t>typ 300-190 Lisek; typ 366; GFM-64; lekkie fotele klubowe PRL bez podłokietników</t>
-  </si>
-  <si>
-    <t>fotele Zamojskich Fabryk Mebli z lat 60. i 70.; meble klubowe produkowane w Zamościu; modele o minimalistycznej konstrukcji bez podłokietników</t>
-  </si>
-  <si>
-    <t>Meblostan – Fotel CELIA typ 300-227; Patyna – Fotel CELIA typ 300-227 PRL; Szajba Sklep – Fotel Celia typ 300-227; materiały kolekcjonerskie dotyczące Zamojskich Fabryk Mebli</t>
-  </si>
-  <si>
-    <t>Typ 300-139</t>
-  </si>
-  <si>
-    <t>Stefan</t>
-  </si>
-  <si>
-    <t>Swarzędzka Fabryka Mebli</t>
-  </si>
-  <si>
-    <t>szerokie drewniane podłokietniki o łagodnym łuku; otwarta konstrukcja boczna; luźne tapicerowane poduchy siedziska i oparcia; rozłożysta bryła; lekka skandynawska stylistyka; nisko osadzone siedzisko; masywny drewniany stelaż</t>
-  </si>
-  <si>
-    <t>stelaż z litego drewna bukowego; otwarta rama boczna; osobna poduszka siedziska; osobna poduszka oparcia; pasy tapicerskie; konstrukcja szkieletowa skręcana</t>
-  </si>
-  <si>
-    <t>typ 300-123 Puchała; typ 366; duńskie fotele Kandidaten projektu Ib Kofod-Larsena; fotele skandynawskie lat 60</t>
-  </si>
-  <si>
-    <t>sofa Stefan; zestawy wypoczynkowe Swarzędzkiej Fabryki Mebli; meble eksportowe Swarzędzkiej Fabryki Mebli z lat 60.</t>
-  </si>
-  <si>
-    <t>„Meble w produkcji 1962” – Zjednoczenie Przemysłu Meblarskiego; „Meble do małych mieszkań. Informator”, Wydawnictwo Katalogów i Cenników 1966; Laminerva – „Ikony polskiego designu: Fotel Stefan typ 300-139”; Meblostan – Para foteli Stefan typ 300-139; Patyna – Para foteli Stefan typ 300-139</t>
-  </si>
-  <si>
-    <t>B-3300</t>
-  </si>
-  <si>
-    <t>ok. 1969; produkcja w końcu lat 60. i na początku lat 70. XX w</t>
-  </si>
-  <si>
-    <t>Zakład Mebli Giętych w Radomsku; Fabryki Mebli Radomsko (późniejsze nazewnictwo zakładu)</t>
-  </si>
-  <si>
-    <t>gięte drewniane podłokietniki; szerokie tapicerowane siedzisko; prostokątne tapicerowane oparcie; otwarta konstrukcja boczna; gięty bukowy stelaż; nisko osadzona bryła; elegancka modernistyczna forma</t>
-  </si>
-  <si>
-    <t>stelaż z giętego drewna bukowego; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; elementy gięte wykonane w technologii Thoneta; konstrukcja skręcana</t>
-  </si>
-  <si>
-    <t>B-310 VAR; B-6028; GFM-64; typ 300-139 Stefan</t>
-  </si>
-  <si>
-    <t>fotele Zakładu Mebli Giętych w Radomsku; modele eksportowe Radomsko z lat 60. i 70.; rodzina foteli z giętego drewna bukowego</t>
-  </si>
-  <si>
-    <t>Patyna – Fotel B-3300 Zakład Mebli Giętych w Radomsku; Meblostan – Para foteli B-3300; archiwalne materiały Fabryk Mebli Radomsko; oferty kolekcjonerskie dokumentujące oryginalne oznaczenie modelu</t>
-  </si>
-  <si>
-    <t>Cechy AI</t>
-  </si>
-  <si>
-    <t>drewniane boczki tworzące nogi i podłokietniki; trapezowe oparcie zwężające się ku górze; trapezowe siedzisko zwężające się ku tyłowi; widoczny prześwit pod siedziskiem; oddzielne moduły tapicerowanego siedziska i oparcia; skośnie rozstawione nogi; pozioma linia podłokietników; odsłonięte drewniane elementy boczne; lekka geometryczna bryła; brak tapicerowanych boków; zwężające się ku dołowi nogi; charakterystyczny profil boczny w kształcie odwróconego V</t>
-  </si>
-  <si>
-    <t>Typ 300-190</t>
-  </si>
-  <si>
-    <t>płaskie drewniane podłokietniki; toczone nogi zwężające się ku dołowi; nogi przechodzące przez podłokietniki; widoczna prostokątna rama boczna; poziome poprzeczki między nogami; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; duży prześwit pod siedziskiem; smukła lekka bryła; odsłonięta konstrukcja drewniana; niskie podłokietniki; geometryczny profil boczny</t>
-  </si>
-  <si>
-    <t>otwarta drewniana rama boczna; prostokątne szerokie oparcie; oparcie szersze niż w modelu 300-190; prostokątne siedzisko; okrągłe toczone nogi; poziome drewniane podłokietniki; widoczne połączenia ramy bocznej; duży prześwit pod siedziskiem; lekka geometryczna bryła; drewniane belki łączące nogi; rozbieralne moduły siedziska i oparcia; nisko osadzone siedzisko</t>
-  </si>
-  <si>
-    <t>trójkątne podłokietniki przypominające uszy zająca; otwarta drewniana rama boczna; szeroko rozstawione nogi; podłokietniki połączone z przednimi nogami; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; duży prześwit pod siedziskiem; smukła lekka bryła; odsłonięty drewniany stelaż; skośne tylne nogi; geometryczny profil boczny; kompaktowe proporcje</t>
-  </si>
-  <si>
-    <t>muszelkowy korpus; kubełkowe siedzisko; zaokrąglone oparcie; stalowy stelaż; cztery smukłe metalowe nogi; wykręcane nogi; kulowe stopki; brak drewnianych podłokietników; jednolita tapicerowana bryła; szerokie półkoliste oparcie; lekka forma na wysokich nogach; profil przypominający muszlę</t>
-  </si>
-  <si>
-    <t>gięte drewniane podłokietniki; smukłe wysokie oparcie; wąskie proporcje korpusu; otwarta drewniana rama boczna; toczone nogi zwężające się ku dołowi; widoczny prześwit pod siedziskiem; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; lekka dynamiczna bryła; cienkie elementy konstrukcyjne; profil boczny z łukowato wygiętym podłokietnikiem; minimalistyczna forma lat 50./60.</t>
-  </si>
-  <si>
-    <t>jednoczęściowa muszelkowa skorupa; organiczna opływowa bryła; głębokie kubełkowe siedzisko; szerokie wywinięte boki; zaokrąglone wysokie oparcie; brak oddzielnych podłokietników; korpus przypominający muszlę; zamknięta forma boczna; cztery cienkie nogi; futurystyczna sylwetka lat 50.; brak widocznej drewnianej konstrukcji; płynne przejścia między siedziskiem i oparciem; asymetrycznie zaokrąglone krawędzie; korpus wykonany jako pojedyncza skorupa</t>
-  </si>
-  <si>
-    <t>kubełkowe siedzisko; forma przypominająca kielich tulipana; szeroko rozchylone boki; jednolita tapicerowana skorupa; zaokrąglone wysokie oparcie; płynne przejście między siedziskiem i oparciem; organiczna bryła; brak widocznej drewnianej ramy bocznej; miękkie obłe krawędzie; rzeźbiarska forma; kompaktowa podstawa; sylwetka kwiatu tulipana</t>
   </si>
   <si>
     <t>otwarta drewniana rama boczna; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; smukła lekka bryła; duży prześwit pod siedziskiem; drewniane podłokietniki zintegrowane z ramą; nogi graniaste od góry; nogi zaokrąglone w dolnej części; skośne tylne nogi; widoczne drewniane elementy konstrukcyjne; forma zbliżona do modelu Lisek; geometryczny profil boczny
 Źródła potwierdzają produkcję w Bystrzyckiej Fabryce Mebli oraz silne pokrewieństwo konstrukcyjne z modelem 300-190 „Lisek”, natomiast projektant pozostaje niepotwierdzony.</t>
   </si>
   <si>
-    <t>GFM-57 Skoczek</t>
+    <t>GFM-57</t>
+  </si>
+  <si>
+    <t>Skoczek</t>
+  </si>
+  <si>
+    <t>Juliusz Kędziorek</t>
+  </si>
+  <si>
+    <t>Krzesło</t>
+  </si>
+  <si>
+    <t>Gościcińska Fabryka Mebli; Zamojskie Fabryki Mebli (produkcja seryjna jako typ 200-203)</t>
+  </si>
+  <si>
+    <t>łukowate podłokietniki przypominające profil skoczni narciarskiej; elipsoidalne oparcie; lekka ażurowa konstrukcja; zwężające się ku dołowi nogi; tapicerowane siedzisko; smukła sylwetka; organiczna linia boczna</t>
+  </si>
+  <si>
+    <t>drewniany stelaż; otwarta konstrukcja boczna; tapicerowane siedzisko; gięte elementy drewniane; konstrukcja przeznaczona do produkcji seryjnej</t>
+  </si>
+  <si>
+    <t>typ 200-190 Rajmunda Hałasa; krzesła Aga; krzesła patyczaki lat 60.; lekkie krzesła tapicerowane PRL</t>
+  </si>
+  <si>
+    <t>typ 200-203; GFM-107; projekty Juliusza Kędziorka dla Gościcińskiej Fabryki Mebli</t>
+  </si>
+  <si>
+    <t>Magazif – Krzesło Skoczek; Ikony Designu PL – Krzesło GFM-57 Skoczek; Meblostan – Krzesło Skoczek; Sosenko Home Decor – Krzesło Skoczek; Allegro Artykuł – Krzesło kilka słów o najtrudniejszym meblu</t>
   </si>
   <si>
     <t>łukowate podłokietniki przypominające skocznię narciarską; elipsoidalne oparcie; otwarta drewniana rama boczna; smukłe zwężające się nogi; tapicerowane siedzisko; duży prześwit pod siedziskiem; płynna linia podłokietnika przechodząca w nogę; lekka ażurowa konstrukcja; organiczny profil boczny; oparcie w kształcie pionowej elipsy; cienkie elementy drewniane; dynamiczna sylwetka inspirowana skokami narciarskimi
 Źródła potwierdzają, że model został zaprojektowany przez Juliusza Kędziorka w Gościcińskiej Fabryce Mebli w 1965 r., otrzymał nagrodę „Dobre–Ładne–Poszukiwane” i został skierowany do produkcji seryjnej jako typ 200-203</t>
   </si>
   <si>
+    <t>Typ 200-125 VAR</t>
+  </si>
+  <si>
+    <t>Aga</t>
+  </si>
+  <si>
+    <t>ok. 1972–1975 (w źródłach występują rozbieżności dotyczące dokładnego roku projektu)</t>
+  </si>
+  <si>
+    <t>Wielkopolskie Fabryki Mebli; produkcja seryjna PRL (pozostali producenci wymagają weryfikacji)</t>
+  </si>
+  <si>
+    <t>wysokie tapicerowane oparcie; trapezowy układ nóg; miękkie tapicerowane siedzisko; smukła skandynawska forma; zwężająca się ku górze bryła; lekkie proporcje; drewniana konstrukcja eksponowana po bokach</t>
+  </si>
+  <si>
+    <t>drewniany stelaż bukowy; tapicerowane siedzisko; tapicerowane oparcie; sprężyny siedziska; cztery drewniane nogi; konstrukcja przeznaczona do intensywnego użytkowania klubowego</t>
+  </si>
+  <si>
+    <t>typ 200-190 Rajmunda Hałasa; GFM-57 Skoczek; lekkie krzesła klubowe PRL lat 70.</t>
+  </si>
+  <si>
+    <t>fotel 366; meble klubowe Józefa Chierowskiego; reedycja 200-125 VAR realizowana przez 366 Concept</t>
+  </si>
+  <si>
+    <t>Elle Decoration Polska – Krzesło VAR AGA projektu Józefa Chierowskiego; Nowohuckie Renowacje – Krzesło Aga typ 200-125; Patyna.pl – Krzesła AGA typu 200-125 VAR; Linie Studio – 200-125 VAR; Meblościanka – 200-125 VAR</t>
+  </si>
+  <si>
     <t>wysokie tapicerowane oparcie; trapezowy układ nóg; szerokie miękkie siedzisko; brak podłokietników; drewniane nogi rozszerzające się ku dołowi; zwężająca się ku górze sylwetka; lekka skandynawska forma; prostokątne oparcie z zaokrąglonymi krawędziami; widoczne drewniane elementy boczne; smukłe proporcje; geometryczna bryła; profil boczny z pochylonym oparciem</t>
   </si>
   <si>
+    <t>Typ 200-190</t>
+  </si>
+  <si>
+    <t>Hałas; Grzybek</t>
+  </si>
+  <si>
+    <t>Rajmund Teofil Hałas</t>
+  </si>
+  <si>
+    <t>lata 60. XX w.; dokładny rok projektu – Do weryfikacji</t>
+  </si>
+  <si>
+    <t>Zakłady Mebli w Gostyniu (Do weryfikacji); produkcja seryjna w kilku zakładach meblarskich PRL – Do weryfikacji</t>
+  </si>
+  <si>
+    <t>okrągła forma oparcia przypominająca kapelusz grzyba; tapicerowane oparcie i siedzisko; smukłe zwężające się nogi; lekka konstrukcja; wyraźnie wyodrębnione oparcie nad siedziskiem; proporcje inspirowane wzornictwem skandynawskim; minimalistyczna sylwetka</t>
+  </si>
+  <si>
+    <t>drewniany stelaż; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; mocowane oddzielnie siedzisko i oparcie; nogi zwężające się ku dołowi</t>
+  </si>
+  <si>
+    <t>Aga 200-125; Skoczek GFM-57; krzesła skandynawskie lat 60.; lekkie krzesła tapicerowane PRL</t>
+  </si>
+  <si>
+    <t>projekty Rajmunda Teofila Hałasa; krzesła tapicerowane PRL lat 60.; warianty produkcyjne typu 200-190</t>
+  </si>
+  <si>
+    <t>Odnawialnia – Wiem co odnawiam | krzesło Hałasa typ 200-190; Patyna.pl – Krzesła typ 200-190 Rajmund Teofil Hałas; Meblostan – Komplet krzeseł typ 200-190; Daniel Stoiński Redesign – Przewodnik po renowacji krzesła 200-190; Homebook – Krzesło Hałasa typ 200-190</t>
+  </si>
+  <si>
     <t>okrągłe oparcie przypominające grzybek; oparcie szersze od wspornika; tapicerowane okrągłe oparcie; tapicerowane siedzisko; smukłe nogi zwężające się ku dołowi; brak podłokietników; lekka skandynawska forma; duży prześwit pod siedziskiem; cienki drewniany stelaż; wyraźne oddzielenie oparcia od siedziska; geometryczna bryła; profil boczny z lekko odchylonym oparciem</t>
   </si>
   <si>
+    <t>B-6028</t>
+  </si>
+  <si>
+    <t>Barbara Fenrych-Węcławska (Do weryfikacji); Józef Chierowski (Do weryfikacji – atrybucja pojawiająca się wyłącznie w źródłach kolekcjonerskich)</t>
+  </si>
+  <si>
+    <t>lata 60. XX w.</t>
+  </si>
+  <si>
+    <t>Fabryka Mebli Giętych w Radomsku; FAMEG Radomsko; Radomszczańska Fabryka Mebli Giętych</t>
+  </si>
+  <si>
+    <t>wysokie profilowane oparcie; szerokie drewniane podłokietniki; gięte elementy bukowe; głębokie siedzisko; lekka otwarta konstrukcja boczna; elegancka smukła sylwetka; forma łącząca cechy fotela klubowego i wypoczynkowego</t>
+  </si>
+  <si>
+    <t>stelaż z giętego drewna bukowego; otwarta konstrukcja ramowa; tapicerowane siedzisko; tapicerowane oparcie; drewniane podłokietniki zintegrowane z ramą; konstrukcja szkieletowa</t>
+  </si>
+  <si>
+    <t>typ 300-123 Puchała; typ 300-177 Zajączek; B-7727; typ 366</t>
+  </si>
+  <si>
+    <t>fotele Radomsko z giętego drewna; projekty Barbary Fenrych-Węcławskiej (Do weryfikacji); lekkie fotele klubowe PRL lat 60.</t>
+  </si>
+  <si>
+    <t>MidMod – Fotel B6028 FAMEG Radomsko Polska lata 60; Oldsen Design – Fotel B6028 prod. FAMEG Radomsko; Nowohuckie Renowacje – Fotel PRL B-6028 z lat 60-tych; Fotelowo Facebook – fotel projektu Barbary Fenrych-Węcławskiej; Instagram Renowacja Mebli PRL – B6028 lata produkcji 1960</t>
+  </si>
+  <si>
     <t>wysokie prostokątne oparcie; szerokie drewniane podłokietniki; gięte boczne elementy z drewna; otwarta rama boczna; głębokie siedzisko; masywniejsza bryła niż typ 366; bukowy stelaż; duży prześwit pod siedziskiem; profilowane podłokietniki; smukłe nogi zintegrowane z ramą; tapicerowane oparcie i siedzisko; geometryczny profil boczny</t>
   </si>
   <si>
+    <t>A. Dutka</t>
+  </si>
+  <si>
+    <t>1966–1968</t>
+  </si>
+  <si>
+    <t>Zakłady Mebli Giętych w Radomsku; Gołuchowskie Fabryki Mebli</t>
+  </si>
+  <si>
+    <t>duże gabaryty; szerokie głębokie siedzisko; masywne drewniane podłokietniki; geometryczna forma boczna; lekko pochylone oparcie; otwarta konstrukcja ramowa; modernistyczna sylwetka eksportowa</t>
+  </si>
+  <si>
+    <t>stelaż z drewna bukowego; sprężyny lejowe w siedzisku; tapicerowane siedzisko i oparcie; otwarta konstrukcja boczna; drewniane podłokietniki zintegrowane z ramą; konstrukcja rozbieralna skręcana śrubami</t>
+  </si>
+  <si>
+    <t>B-6028; GFM-64; typ 300-190 Lisek; B-7727</t>
+  </si>
+  <si>
+    <t>fotele eksportowe Radomsko lat 60.; modele Zakładów Mebli Giętych w Radomsku; konstrukcje projektowane przez A. Dutkę (Do weryfikacji)</t>
+  </si>
+  <si>
+    <t>Meblostan – Para foteli B-310 VAR; Pufa Design – Oryginalny fotel B-310 VAR; Yestersen – Fotel B-310 VAR Polska lata 70.; Reko-Czyny – Fotel B-310 VAR metamorfoza; archiwalne ogłoszenia kolekcjonerskie B-310 VAR</t>
+  </si>
+  <si>
     <t>masywne drewniane podłokietniki; szerokie głębokie siedzisko; wysunięte przednie podłokietniki; otwarta drewniana rama boczna; prostokątne tapicerowane oparcie; grube proporcje siedziska; lekko pochylone oparcie; duży prześwit pod siedziskiem; widoczne śruby montażowe w ramie; geometryczny profil boczny; szeroki rozstaw nóg; cięższa bryła niż typ 366; bukowy stelaż; modernistyczna forma eksportowa</t>
   </si>
   <si>
+    <t>GFM-22 (typ 200/128)</t>
+  </si>
+  <si>
+    <t>ok. 1960</t>
+  </si>
+  <si>
+    <t>Gościcińska Fabryka Mebli (GFM)</t>
+  </si>
+  <si>
+    <t>nerkowate oparcie; lekka ażurowa konstrukcja; smukłe zwężające się nogi; gięta drewniana rama; tapicerowane siedzisko; tapicerowane oparcie; wyraźnie rozstawione tylne nogi</t>
+  </si>
+  <si>
+    <t>drewniany stelaż; gięte elementy z litego drewna; tapicerowane siedzisko; tapicerowane oparcie ze sklejki giętej; konstrukcja szkieletowa przeznaczona do produkcji seryjnej</t>
+  </si>
+  <si>
+    <t>GFM-57 Skoczek; typ 200-190 Rajmunda Hałasa; Aga 200-125; krzesła skandynawskie z lat 60.</t>
+  </si>
+  <si>
+    <t>typ 200/128; projekty Juliusza Kędziorka dla Gościcińskiej Fabryki Mebli; GFM-57; GFM-87</t>
+  </si>
+  <si>
+    <t>Pamono – Mid-Century GFM-22 Chairs by Juliusz Kędziorek; Vinterior – GFM-22 model 200/128; Selency – Iconic GFM-22 Chair by Juliusz Kędziorek; Instagram Zostań z Vintage – Krzesło GFM-22 typ 200/128</t>
+  </si>
+  <si>
     <t>nerkowate tapicerowane oparcie; oparcie szersze od wspornika; smukłe zwężające się nogi; lekka ażurowa konstrukcja; gięta drewniana rama; prostokątne tapicerowane siedzisko; duży prześwit pod siedziskiem; cienkie elementy konstrukcyjne; szeroko rozstawione tylne nogi; profil boczny z delikatnie pochylonym oparciem; organiczny kształt oparcia; minimalistyczna sylwetka lat 60.</t>
   </si>
   <si>
+    <t>Typ 1020</t>
+  </si>
+  <si>
+    <t>Muszelka</t>
+  </si>
+  <si>
+    <t>Wiesław Leśniewski; Stanisław Lejkowski</t>
+  </si>
+  <si>
+    <t>Słupskie Fabryki Mebli</t>
+  </si>
+  <si>
+    <t>muszelkowe profilowane oparcie; jednolita tapicerowana skorupa; zaokrąglona górna krawędź oparcia; smukłe stożkowe nogi; lekka modernistyczna forma; brak podłokietników; organiczna sylwetka</t>
+  </si>
+  <si>
+    <t>profilowana skorupa ze sklejki; tapicerowana skorupa; drewniany stelaż; cztery drewniane nogi; konstrukcja szkieletowa; połączenie sklejki i drewna litego</t>
+  </si>
+  <si>
+    <t>RM58; krzesła muszelkowe produkcji NRD; krzesła skandynawskie lat 60.; fotel Ewa</t>
+  </si>
+  <si>
+    <t>krzesła muszelkowe Słupskich Fabryk Mebli; projekty Wiesława Leśniewskiego i Stanisława Lejkowskiego; meble ze sklejki profilowanej produkowane przez SFM</t>
+  </si>
+  <si>
+    <t>Archiwalne katalogi Słupskich Fabryk Mebli; opracowania kolekcjonerskie dotyczące wzornictwa SFM; materiały renowatorów specjalizujących się w meblach PRL; publikacje poświęcone projektom Wiesława Leśniewskiego i Stanisława Lejkowskiego</t>
+  </si>
+  <si>
     <t>muszelkowe profilowane oparcie; jednolita tapicerowana skorupa; zaokrąglona górna krawędź oparcia; płynne przejście oparcia w siedzisko; brak podłokietników; cztery smukłe stożkowe drewniane nogi; lekka organiczna bryła; profilowana skorupa ze sklejki; niewielki prześwit pod siedziskiem; forma inspirowana muszlą</t>
   </si>
   <si>
+    <t>Bumerang</t>
+  </si>
+  <si>
+    <t>Ryszard Kulm</t>
+  </si>
+  <si>
+    <t>przełom lat 50. i 60. XX w.; produkcja seryjna od początku lat 60</t>
+  </si>
+  <si>
+    <t>Gościcińska Fabryka Mebli</t>
+  </si>
+  <si>
+    <t>charakterystyczne łukowato wygięte przednie nogi przypominające bumerang; lekka ażurowa konstrukcja; tapicerowane siedzisko; tapicerowane oparcie; smukła sylwetka; zwężające się ku dołowi nogi; modernistyczna forma inspirowana skandynawskim wzornictwem</t>
+  </si>
+  <si>
+    <t>drewniany stelaż bukowy; gięte elementy boczne; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; połączenia skręcane i klejone</t>
+  </si>
+  <si>
+    <t>GFM-22; typ 200-190 Rajmunda Hałasa; GFM-57 Skoczek; krzesła skandynawskie lat 60</t>
+  </si>
+  <si>
+    <t>krzesła Gościcińskiej Fabryki Mebli; wariant 299XB (Do weryfikacji); rodzina krzeseł Bumerang</t>
+  </si>
+  <si>
+    <t>Meblostan – Komplet 4 krzeseł Bumerang typ 299; Skarby PRL – Krzesło tapicerowane Bumerang typ 299; Patyna – Komplet krzeseł typ 299 Bumerang; Deccoria – 10 słynnych mebli z PRL; Stary Fotel – Krzesła Bumerang metamorfoza</t>
+  </si>
+  <si>
     <t>łukowato wygięte przednie nogi w kształcie bumerangu; gięte boczne elementy drewniane; tapicerowane prostokątne siedzisko; tapicerowane oparcie; smukła lekka bryła; cienki drewniany stelaż; zwężające się ku dołowi nogi; wyraźny prześwit pod siedziskiem; organiczny profil boczny; lekko odchylone oparcie; minimalistyczna forma lat 60.; charakterystyczna sylwetka bumerangu</t>
   </si>
   <si>
+    <t>Typ 300-227</t>
+  </si>
+  <si>
+    <t>Celia</t>
+  </si>
+  <si>
+    <t>ok. 1965; produkcja na przełomie lat 60. i 70. XX w.</t>
+  </si>
+  <si>
+    <t>Zamojskie Fabryki Mebli</t>
+  </si>
+  <si>
+    <t>brak podłokietników; toczone drewniane nogi umieszczone po bokach części tapicerowanej; trapezowe siedzisko; proste tapicerowane oparcie; lekka minimalistyczna forma; kompaktowe wymiary; stylistyka skandynawskiego modernizmu</t>
+  </si>
+  <si>
+    <t>drewniany stelaż; toczone nogi; tapicerowane siedzisko; tapicerowane oparcie; otwarta konstrukcja bez podłokietników; konstrukcja szkieletowa przeznaczona do produkcji seryjnej</t>
+  </si>
+  <si>
+    <t>typ 300-190 Lisek; typ 366; GFM-64; lekkie fotele klubowe PRL bez podłokietników</t>
+  </si>
+  <si>
+    <t>fotele Zamojskich Fabryk Mebli z lat 60. i 70.; meble klubowe produkowane w Zamościu; modele o minimalistycznej konstrukcji bez podłokietników</t>
+  </si>
+  <si>
+    <t>Meblostan – Fotel CELIA typ 300-227; Patyna – Fotel CELIA typ 300-227 PRL; Szajba Sklep – Fotel Celia typ 300-227; materiały kolekcjonerskie dotyczące Zamojskich Fabryk Mebli</t>
+  </si>
+  <si>
     <t>brak podłokietników; toczone drewniane nogi umieszczone po bokach korpusu; trapezowe tapicerowane siedzisko; prostokątne tapicerowane oparcie; lekka minimalistyczna bryła; duży prześwit pod siedziskiem; cienki drewniany stelaż; zwężające się ku dołowi nogi; odsłonięte drewniane elementy boczne; kompaktowe proporcje; geometryczny profil boczny; forma inspirowana skandynawskim modernizmem</t>
   </si>
   <si>
+    <t>Typ 300-139</t>
+  </si>
+  <si>
+    <t>Stefan</t>
+  </si>
+  <si>
+    <t>Swarzędzka Fabryka Mebli</t>
+  </si>
+  <si>
+    <t>szerokie drewniane podłokietniki o łagodnym łuku; otwarta konstrukcja boczna; luźne tapicerowane poduchy siedziska i oparcia; rozłożysta bryła; lekka skandynawska stylistyka; nisko osadzone siedzisko; masywny drewniany stelaż</t>
+  </si>
+  <si>
+    <t>stelaż z litego drewna bukowego; otwarta rama boczna; osobna poduszka siedziska; osobna poduszka oparcia; pasy tapicerskie; konstrukcja szkieletowa skręcana</t>
+  </si>
+  <si>
+    <t>typ 300-123 Puchała; typ 366; duńskie fotele Kandidaten projektu Ib Kofod-Larsena; fotele skandynawskie lat 60</t>
+  </si>
+  <si>
+    <t>sofa Stefan; zestawy wypoczynkowe Swarzędzkiej Fabryki Mebli; meble eksportowe Swarzędzkiej Fabryki Mebli z lat 60.</t>
+  </si>
+  <si>
+    <t>„Meble w produkcji 1962” – Zjednoczenie Przemysłu Meblarskiego; „Meble do małych mieszkań. Informator”, Wydawnictwo Katalogów i Cenników 1966; Laminerva – „Ikony polskiego designu: Fotel Stefan typ 300-139”; Meblostan – Para foteli Stefan typ 300-139; Patyna – Para foteli Stefan typ 300-139</t>
+  </si>
+  <si>
     <t>szerokie wyprofilowane drewniane podłokietniki; otwarta drewniana rama boczna; luźna poduszka siedziska; luźna poduszka oparcia; nisko osadzone głębokie siedzisko; prostokątne grube poduchy; lekko odchylone oparcie; masywny bukowy stelaż; duży prześwit pod siedziskiem; szeroki rozstaw przednich nóg; profil boczny inspirowany wzornictwem skandynawskim; rozłożysta bryła eksportowa</t>
   </si>
   <si>
+    <t>B-3300</t>
+  </si>
+  <si>
+    <t>ok. 1969; produkcja w końcu lat 60. i na początku lat 70. XX w</t>
+  </si>
+  <si>
+    <t>Zakład Mebli Giętych w Radomsku; Fabryki Mebli Radomsko (późniejsze nazewnictwo zakładu)</t>
+  </si>
+  <si>
+    <t>gięte drewniane podłokietniki; szerokie tapicerowane siedzisko; prostokątne tapicerowane oparcie; otwarta konstrukcja boczna; gięty bukowy stelaż; nisko osadzona bryła; elegancka modernistyczna forma</t>
+  </si>
+  <si>
+    <t>stelaż z giętego drewna bukowego; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; elementy gięte wykonane w technologii Thoneta; konstrukcja skręcana</t>
+  </si>
+  <si>
+    <t>B-310 VAR; B-6028; GFM-64; typ 300-139 Stefan</t>
+  </si>
+  <si>
+    <t>fotele Zakładu Mebli Giętych w Radomsku; modele eksportowe Radomsko z lat 60. i 70.; rodzina foteli z giętego drewna bukowego</t>
+  </si>
+  <si>
+    <t>Patyna – Fotel B-3300 Zakład Mebli Giętych w Radomsku; Meblostan – Para foteli B-3300; archiwalne materiały Fabryk Mebli Radomsko; oferty kolekcjonerskie dokumentujące oryginalne oznaczenie modelu</t>
+  </si>
+  <si>
     <t>gięte drewniane podłokietniki; otwarta drewniana rama boczna; szerokie prostokątne oparcie; szerokie głębokie siedzisko; bukowy gięty stelaż; duży prześwit pod siedziskiem; łagodnie wygięte boki; zwężające się ku dołowi nogi; lekko pochylone oparcie; masywniejsza bryła niż typ 366; widoczne elementy z giętego drewna; modernistyczna forma gabinetowa</t>
+  </si>
+  <si>
+    <t>Cechy AI</t>
   </si>
 </sst>
 </file>
@@ -1031,9 +1028,48 @@
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="20">
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1346,7 +1382,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAC340A0-F689-4CF5-934F-277213A09CD2}" name="Tabela1" displayName="Tabela1" ref="A2:M42" totalsRowShown="0" headerRowDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAC340A0-F689-4CF5-934F-277213A09CD2}" name="Tabela1" displayName="Tabela1" ref="A2:M42" totalsRowShown="0" headerRowDxfId="19">
   <autoFilter ref="A2:M42" xr:uid="{AAC340A0-F689-4CF5-934F-277213A09CD2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M8">
     <sortCondition ref="C2:C8"/>
@@ -1360,7 +1396,7 @@
     <tableColumn id="5" xr3:uid="{FC87805C-8F21-4877-A2BB-F94A46848488}" name="Top3 contains"/>
     <tableColumn id="12" xr3:uid="{083260FC-C283-425D-8992-A120FCD63F58}" name="Model Family"/>
     <tableColumn id="6" xr3:uid="{C375EF1E-B099-4419-8B9C-B2440FD0A8ED}" name="Designer"/>
-    <tableColumn id="7" xr3:uid="{DD17F6C6-7610-4EE0-A977-F8A13F1B8EBA}" name="Confidence" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{DD17F6C6-7610-4EE0-A977-F8A13F1B8EBA}" name="Confidence" dataDxfId="18"/>
     <tableColumn id="8" xr3:uid="{B609250C-19DF-4BCE-8148-69FA85A5C4D5}" name="Error Type"/>
     <tableColumn id="9" xr3:uid="{7ECB45DF-B162-4E08-85FE-5889D14F4EA2}" name="Notes"/>
     <tableColumn id="10" xr3:uid="{7DB3FB91-9C91-4420-A0AD-58F455F6AD18}" name="Severity"/>
@@ -1371,22 +1407,23 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0B9BF425-AAE6-496E-A318-81223EDA70A0}" name="Table2" displayName="Table2" ref="A1:M21" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:M21" xr:uid="{0B9BF425-AAE6-496E-A318-81223EDA70A0}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{BEC8128C-B6F8-41AF-8B4E-AC51172C6F9B}" name="ID" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{A4D5EBAD-8137-4068-9AB3-4017AE021691}" name="Model" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{2E31A0DA-DF43-4372-8896-81E05381952A}" name="Potoczna nazwa" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{BFBF567B-85D5-410F-86B7-E7A5AE9C3740}" name="Projektant" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{C0BA823A-68AD-4568-86DC-D7A0821FE81E}" name="Rok" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{A85EDE16-4C80-416A-961D-E6418592861C}" name="Typ" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{B6F3255D-9933-44DB-84CE-345F6ADC20CF}" name="Producent" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{444D790F-7610-4FF6-B3B8-84C2F85CD109}" name="Cechy Charakterystyczne" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{98CF13B3-BB3C-451C-BD71-AA322E9D297B}" name="Konstrukcja" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{CED6A324-3FA7-4066-97E4-A5BE6D00D638}" name="Mylony z" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{7D23AC8B-5C76-4D9D-94A1-5E0E701AC60B}" name="Rodzina modeli" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{6E7FC306-D5DA-4E3A-8481-0DE3695A5890}" name="Źródła" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{86F52982-86F4-44FD-8A46-84423C74DFF2}" name="Poziom pewności" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0B9BF425-AAE6-496E-A318-81223EDA70A0}" name="Table2" displayName="Table2" ref="A1:N21" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A1:N21" xr:uid="{0B9BF425-AAE6-496E-A318-81223EDA70A0}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{BEC8128C-B6F8-41AF-8B4E-AC51172C6F9B}" name="ID" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{A4D5EBAD-8137-4068-9AB3-4017AE021691}" name="Model" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{2E31A0DA-DF43-4372-8896-81E05381952A}" name="Potoczna nazwa" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{BFBF567B-85D5-410F-86B7-E7A5AE9C3740}" name="Projektant" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{C0BA823A-68AD-4568-86DC-D7A0821FE81E}" name="Rok" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{A85EDE16-4C80-416A-961D-E6418592861C}" name="Typ" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{B6F3255D-9933-44DB-84CE-345F6ADC20CF}" name="Producent" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{444D790F-7610-4FF6-B3B8-84C2F85CD109}" name="Cechy Charakterystyczne" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{98CF13B3-BB3C-451C-BD71-AA322E9D297B}" name="Konstrukcja" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{CED6A324-3FA7-4066-97E4-A5BE6D00D638}" name="Mylony z" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{7D23AC8B-5C76-4D9D-94A1-5E0E701AC60B}" name="Rodzina modeli" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{6E7FC306-D5DA-4E3A-8481-0DE3695A5890}" name="Źródła" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{86F52982-86F4-44FD-8A46-84423C74DFF2}" name="Poziom pewności" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{633CC391-CD9D-4406-9436-B55C83554066}" name="Search Features" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1396,7 +1433,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{61559DFE-BFDA-476F-A468-7B9F99C28CB5}" name="Table3" displayName="Table3" ref="A1:B21" totalsRowShown="0">
   <autoFilter ref="A1:B21" xr:uid="{61559DFE-BFDA-476F-A468-7B9F99C28CB5}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{27F92EA0-9427-4162-90E8-85D5CAEC32F6}" name="Model"/>
+    <tableColumn id="1" xr3:uid="{27F92EA0-9427-4162-90E8-85D5CAEC32F6}" name="Model" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{67610278-00DF-4DEA-BF65-7097C76D8F9A}" name="Cechy AI" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3080,7 +3117,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E570A043-1276-4CEE-AF12-19208D26EAA5}">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -3095,9 +3132,10 @@
     <col min="11" max="11" width="31" customWidth="1"/>
     <col min="12" max="12" width="24.140625" customWidth="1"/>
     <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="5" t="s">
         <v>77</v>
       </c>
@@ -3137,90 +3175,99 @@
       <c r="M1" s="10" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="152.25">
+      <c r="N1" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="409.6">
       <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M2" s="11">
         <v>0.98</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="152.25">
+      <c r="N2" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="409.6">
       <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E3" s="9">
         <v>1967</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M3" s="11">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="152.25">
+      <c r="N3" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="381.75">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -3228,81 +3275,87 @@
         <v>26</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M4" s="11">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="213">
+      <c r="N4" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="409.6">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="M5" s="11">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="106.5">
+      <c r="N5" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="321">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -3310,366 +3363,393 @@
         <v>38</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E6" s="9">
         <v>1962</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="M6" s="11">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="152.25">
+      <c r="N6" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="409.6">
       <c r="A7" s="9">
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="M7" s="11">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="137.25">
+      <c r="N7" s="9" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="409.6">
       <c r="A8" s="9">
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="E8" s="9">
         <v>1958</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M8" s="11">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="91.5">
+      <c r="N8" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="366">
       <c r="A9" s="9">
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="M9" s="11">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="137.25">
+      <c r="N9" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="409.6">
       <c r="A10" s="9">
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="M10" s="11">
         <v>0.87</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="137.25">
+      <c r="N10" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="409.6">
       <c r="A11" s="9">
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="E11" s="9">
         <v>1965</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="M11" s="11">
         <v>0.96</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="152.25">
+      <c r="N11" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="409.6">
       <c r="A12" s="9">
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="M12" s="11">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="183">
+      <c r="N12" s="9" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="409.6">
       <c r="A13" s="9">
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="M13" s="11">
         <v>0.96</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="229.5">
+      <c r="N13" s="9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="366">
       <c r="A14" s="9">
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="M14" s="11">
         <v>0.72</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="137.25">
+      <c r="N14" s="9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="409.6">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -3678,117 +3758,126 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="M15" s="11">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="137.25">
+      <c r="N15" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="396.75">
       <c r="A16" s="9">
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="M16" s="11">
         <v>0.93</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="167.25">
+      <c r="N16" s="9" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="321">
       <c r="A17" s="9">
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="E17" s="9">
         <v>1962</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="M17" s="11">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="152.25">
+      <c r="N17" s="9" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="381.75">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -3796,152 +3885,164 @@
         <v>67</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="M18" s="11">
         <v>0.91</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="121.5">
+      <c r="N18" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="409.6">
       <c r="A19" s="9">
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="C19" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="M19" s="11">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="213">
+      <c r="N19" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="396.75">
       <c r="A20" s="9">
         <v>19</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="M20" s="11">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="137.25">
+      <c r="N20" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="366">
       <c r="A21" s="9">
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="M21" s="11">
         <v>0.86</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -3966,167 +4067,167 @@
         <v>78</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="106.5">
-      <c r="A2">
-        <v>366</v>
+      <c r="A2" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>272</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="91.5">
-      <c r="A3" t="s">
+      <c r="A3" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="91.5">
+      <c r="A4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="91.5">
+      <c r="A5" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="76.5">
+      <c r="A6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="91.5">
+      <c r="A7" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="106.5">
+      <c r="A8" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="76.5">
+      <c r="A9" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="152.25">
+      <c r="A10" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="183">
+      <c r="A11" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="91.5">
+      <c r="A12" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="91.5">
+      <c r="A13" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="76.5">
+      <c r="A14" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="91.5">
+      <c r="A15" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="91.5">
+      <c r="A16" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="76.5">
+      <c r="A17" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="91.5">
+      <c r="A18" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="91.5">
+      <c r="A19" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="20" spans="1:2" ht="91.5">
+      <c r="A20" s="9" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="91.5">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="91.5">
-      <c r="A5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="76.5">
-      <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="91.5">
-      <c r="A7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="106.5">
-      <c r="A8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="76.5">
-      <c r="A9" t="s">
-        <v>155</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="152.25">
-      <c r="A10" t="s">
-        <v>165</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="183">
-      <c r="A11" t="s">
+      <c r="B20" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B11" s="1" t="s">
+    </row>
+    <row r="21" spans="1:2" ht="76.5">
+      <c r="A21" s="9" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="91.5">
-      <c r="A12" t="s">
-        <v>184</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="91.5">
-      <c r="A13" t="s">
-        <v>193</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="76.5">
-      <c r="A14" t="s">
-        <v>203</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="91.5">
-      <c r="A15" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="91.5">
-      <c r="A16" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="76.5">
-      <c r="A17" t="s">
-        <v>228</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="91.5">
-      <c r="A18" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="91.5">
-      <c r="A19" t="s">
-        <v>246</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>291</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="91.5">
-      <c r="A20" t="s">
-        <v>255</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="76.5">
-      <c r="A21" t="s">
-        <v>263</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/data/furniture.xlsx
+++ b/data/furniture.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98AB1377-DA10-4E8D-9E0C-6724EC958207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3147F11-BFBA-4623-B963-325CD87AC8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmark" sheetId="1" r:id="rId1"/>
@@ -337,10 +337,10 @@
     <t>Dolnośląska Fabryka Mebli w Świebodzicach</t>
   </si>
   <si>
-    <t>drewniane boczki pełniące funkcję nóg i podłokietników; lekka modernistyczna forma; trapezowe siedzisko; trapezowe oparcie; widoczne elementy drewniane; oddzielne moduły tapicerowane; niewielkie gabaryty</t>
-  </si>
-  <si>
-    <t>drewniana konstrukcja nośna; boczki z litego drewna; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja przeznaczona do produkcji seryjnej</t>
+    <t>Fotel składa się z tapicerowanej „łupiny” tworzonej przez zintegrowane siedzisko i oparcie. Po rozłożeniu jej obrys przypomina trapez o lekko wyokrąglonych bokach i narożnikach. Boczne podpory wykonane z drewna łączą po dwie zwężające się ku dołowi nogi z wyoblonym podłokietnikiem o organicznym kształcie. Mebel pozbawiony jest dekoracyjnych elementów. Tapicerkę zdobią wyłącznie guziki pikowania, natomiast elementy drewniane posiadają widoczne śruby o dużych główkach. Poszczególne egzemplarze różnią się tkaniną obiciową, gatunkiem drewna, kolorem lakieru oraz występują także warianty z czarno malowanymi podłokietnikami.</t>
+  </si>
+  <si>
+    <t>Konstrukcja składa się z tapicerowanej łupiny zintegrowanego siedziska i oparcia oraz dwóch drewnianych podpór bocznych. Każda podpora stanowi element łączący podłokietnik z dwiema nogami. W wersji produkcyjnej zastosowano widoczne połączenia śrubowe zamiast projektowanych niewidocznych mocowań.</t>
   </si>
   <si>
     <t>GFM-64; RM58; polskie fotele klubowe lat 60.</t>
@@ -352,7 +352,31 @@
     <t>opracowania dotyczące Józefa Chierowskiego; dokumentacja 366 Concept; zbiory Muzeum Narodowego w Warszawie; Polski New Look Ewa Solarz i Agnieszka Sural; publikacje o polskim wzornictwie powojennym</t>
   </si>
   <si>
-    <t>drewniane boczki tworzące nogi i podłokietniki; trapezowe oparcie zwężające się ku górze; trapezowe siedzisko zwężające się ku tyłowi; widoczny prześwit pod siedziskiem; oddzielne moduły tapicerowanego siedziska i oparcia; skośnie rozstawione nogi; pozioma linia podłokietników; odsłonięte drewniane elementy boczne; lekka geometryczna bryła; brak tapicerowanych boków; zwężające się ku dołowi nogi; charakterystyczny profil boczny w kształcie odwróconego V</t>
+    <t>drewniane boczki;
+otwarta rama boczna;
+widoczna drewniana rama;
+tapicerowana łupina;
+jednolita łupina;
+zintegrowane siedzisko;
+zintegrowane oparcie;
+trapezowy obrys korpusu;
+zaokrąglone narożniki korpusu;
+zaokrąglone boki korpusu;
+tapicerowane siedzisko;
+tapicerowane oparcie;
+wyoblone podłokietniki;
+organiczny kształt podłokietników;
+drewniane podłokietniki;
+zwężające się nogi;
+skośnie rozstawione nogi;
+cztery drewniane nogi;
+widoczne śruby;
+duże główki śrub;
+guziki pikowania;
+prześwit pod siedziskiem;
+odsłonięta drewniana konstrukcja;
+widoczne drewniane elementy;
+brak ozdobnych detali</t>
   </si>
   <si>
     <t>Fotel typ 300-190</t>
@@ -367,10 +391,10 @@
     <t>Dolnośląska Fabryka Mebli w Świebodzicach; Bystrzyckie Fabryki Mebli; Zakład Mebli Giętych FAMEG Radomsko; Świdnicki Ośrodek Przemysłu Meblarskiego</t>
   </si>
   <si>
-    <t>smukła lekka sylwetka; płaskie drewniane podłokietniki; toczone nogi zwężające się ku dołowi; widoczna drewniana rama boczna; prostokątne tapicerowane oparcie; kompaktowe wymiary; modernistyczna forma</t>
-  </si>
-  <si>
-    <t>konstrukcja nośna z drewna bukowego; toczone nogi mocowane do podłokietników; poprzeczne belki usztywniające ramę; pasy tapicerskie; formatki gumowe jako wypełnienie; lakierowane elementy drewniane</t>
+    <t>Fotel posiada lekką, smukłą konstrukcję opartą na odsłoniętej drewnianej ramie. Tapicerowane siedzisko i oparcie osadzone są pomiędzy drewnianymi boczkami zakończonymi płaskimi podłokietnikami. Konstrukcja wsparta jest na czterech toczonych, lekko zwężających się nogach. W połowie wysokości nóg widoczne są poprzeczne belki tworzące charakterystyczną ramę usztywniającą. Drewniane elementy wykończone były lakierem o wykończeniu matowym, półmatowym lub z połyskiem.</t>
+  </si>
+  <si>
+    <t>Konstrukcję nośną tworzą drewniane boczki połączone poprzecznymi belkami oraz stelażem. Nogi są mocowane do płaskich podłokietników. Do wykonania stolarki zastosowano drewno bukowe. Siedzisko wykorzystuje formatki gumowe osadzone na elastycznych pasach zamiast sprężyn i tradycyjnych wypełnień.</t>
   </si>
   <si>
     <t>typ 366; GFM-64; fotele klubowe PRL z lat 60.</t>
@@ -382,7 +406,31 @@
     <t>Nowohuckie Renowacje – Fotel Lisek typ 300-190; Conchita Home – 4 fotele z PRL które musisz znać; dokumentacja i opisy egzemplarzy Typ 300-190; archiwalne materiały producentów cytowane w opracowaniach specjalistycznych</t>
   </si>
   <si>
-    <t>płaskie drewniane podłokietniki; toczone nogi zwężające się ku dołowi; nogi przechodzące przez podłokietniki; widoczna prostokątna rama boczna; poziome poprzeczki między nogami; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; duży prześwit pod siedziskiem; smukła lekka bryła; odsłonięta konstrukcja drewniana; niskie podłokietniki; geometryczny profil boczny</t>
+    <t>toczone nogi;
+lekko zwężające się nogi;
+cztery drewniane nogi;
+drewniane boczki;
+otwarta rama boczna;
+widoczna drewniana rama;
+poprzeczne belki;
+widoczne belki między nogami;
+płaskie podłokietniki;
+drewniane podłokietniki;
+odsłonięta konstrukcja;
+prześwit pod siedziskiem;
+tapicerowane siedzisko;
+tapicerowane oparcie;
+prostokątne oparcie;
+prostokątne siedzisko;
+smukła bryła;
+wysokie oparcie;
+widoczne boczne podpory;
+drewniany stelaż;
+proste linie konstrukcji;
+otwarte boki;
+rama usztywniająca;
+widoczna konstrukcja pod siedziskiem;
+minimalistyczna forma</t>
   </si>
   <si>
     <t>Do weryfikacji; często błędnie określany jako „Lisek”</t>
@@ -397,10 +445,10 @@
     <t>Zakłady Przemysłu Meblarskiego im. Gwardii Ludowej w Radomsku; Fabryki Mebli Radomsko</t>
   </si>
   <si>
-    <t>otwarta drewniana rama boczna; prostokątne tapicerowane siedzisko; szerokie tapicerowane oparcie; toczone okrągłe nogi; nisko osadzone siedzisko; lekka konstrukcja szkieletowa; widoczne drewniane podłokietniki</t>
-  </si>
-  <si>
-    <t>rama z drewna bukowego; toczone elementy nóg; tapicerowane siedzisko montowane śrubami; tapicerowane oparcie montowane śrubami; wewnętrzny szkielet z drewna iglastego; konstrukcja rozbieralna</t>
+    <t>Fotel posiada otwartą drewnianą konstrukcję zewnętrzną wykonaną z litego drewna. Tapicerowane siedzisko i oparcie zamocowane są wewnątrz drewnianej ramy za pomocą wkrętów lub śrub. Konstrukcja opiera się na czterech toczonych nogach połączonych belkami podtrzymującymi siedzisko. Charakterystycznym elementem są zaokrąglone drewniane podłokietniki stanowiące integralną część bocznej ramy.</t>
+  </si>
+  <si>
+    <t>Konstrukcja wykonana jest z litej tarcicy bukowej. Szkielet ukryty pod tapicerką wykonano z tarcicy iglastej. Siedzisko i oparcie mocowane są do ramy za pomocą wkrętów lub śrub. Połączenia konstrukcyjne obejmują połączenia czopowe oraz połączenia na wkręty. W siedzisku zastosowano pasy tapicerskie i tworzywo piankowe.</t>
   </si>
   <si>
     <t>typ 300-190 Lisek; BW-14; typ 366</t>
@@ -412,7 +460,30 @@
     <t>Patyna.pl – fotel B-7727 Radomsko PRL; Meblostan – fotel B-7727; Nowohuckie Renowacje – fotel B-7727; Vilandy – fotel Lis typ B-7727; Allegro – fotel PRL model B-7727 Radomsko lata 70; Reko-Czyny – identyfikacja fotela B-7727</t>
   </si>
   <si>
-    <t>otwarta drewniana rama boczna; prostokątne szerokie oparcie; oparcie szersze niż w modelu 300-190; prostokątne siedzisko; okrągłe toczone nogi; poziome drewniane podłokietniki; widoczne połączenia ramy bocznej; duży prześwit pod siedziskiem; lekka geometryczna bryła; drewniane belki łączące nogi; rozbieralne moduły siedziska i oparcia; nisko osadzone siedzisko</t>
+    <t>toczone nogi;
+cztery drewniane nogi;
+zaokrąglone podłokietniki;
+drewniane podłokietniki;
+otwarta rama boczna;
+widoczna drewniana rama;
+drewniane boczki;
+belki pod siedziskiem;
+widoczne belki;
+tapicerowane siedzisko;
+tapicerowane oparcie;
+oddzielne siedzisko;
+oddzielne oparcie;
+prostokątne oparcie;
+prostokątne siedzisko;
+widoczne śruby;
+widoczne wkręty;
+prześwit pod siedziskiem;
+odsłonięta drewniana konstrukcja;
+rama zewnętrzna;
+otwarte boki;
+widoczne mocowanie siedziska;
+widoczne mocowanie oparcia;
+drewniany stelaż</t>
   </si>
   <si>
     <t>Typ 300-177</t>
@@ -457,10 +528,10 @@
     <t>Strzeleckie Zakłady Przemysłu Terenowego w Strzelcach Opolskich</t>
   </si>
   <si>
-    <t>stalowy stelaż; muszelkowa forma korpusu; kubełkowe siedzisko; smukłe wykręcane nogi; ruchome stopki kulowe; lekka wizualnie konstrukcja; obłe linie oparcia</t>
-  </si>
-  <si>
-    <t>spawana rama z prętów stalowych; tapicerowany korpus; cztery stalowe wykręcane nogi; siedzisko na pasach tapicerskich; konstrukcja metalowa bez drewnianych boczków</t>
+    <t>Fotel posiada muszelkowy, kubełkowy korpus tworzący jednolitą tapicerowaną bryłę. Szerokie, półkoliste oparcie płynnie przechodzi w siedzisko, nadając bryle profil przypominający muszlę. Korpus osadzony jest na odsłoniętym stalowym stelażu wspartym na czterech smukłych metalowych nogach. Fotel nie posiada drewnianych podłokietników, a wysoka podstawa nadaje konstrukcji lekką formę.</t>
+  </si>
+  <si>
+    <t>Konstrukcję nośną stanowi rama wykonana ze spawanych prętów stalowych. Rama wsparta jest na czterech stalowych, wykręcanych nogach zakończonych ruchomymi stopkami. W modelu Koeln 1 zastosowano pojedynczą stalową nogę obrotową.</t>
   </si>
   <si>
     <t>fotel Köln 1; fotel Muszelka; fotele klubowe na stelażu stalowym z lat 60.</t>
@@ -472,7 +543,31 @@
     <t>Meblostan – Para foteli tapicerowanych EWA; Odnowa Mebli – Fotel Ewa; Patyna.pl – Komplet foteli typ Ewa; materiały kolekcjonerskie rynku vintage</t>
   </si>
   <si>
-    <t>muszelkowy korpus; kubełkowe siedzisko; zaokrąglone oparcie; stalowy stelaż; cztery smukłe metalowe nogi; wykręcane nogi; kulowe stopki; brak drewnianych podłokietników; jednolita tapicerowana bryła; szerokie półkoliste oparcie; lekka forma na wysokich nogach; profil przypominający muszlę</t>
+    <t>muszelkowy korpus;
+kubełkowe siedzisko;
+jednolita tapicerowana bryła;
+tapicerowane siedzisko;
+tapicerowane oparcie;
+zaokrąglone oparcie;
+szerokie półkoliste oparcie;
+profil przypominający muszlę;
+stalowy stelaż;
+stalowa rama;
+rama z prętów stalowych;
+spawana rama;
+odsłonięty stalowy stelaż;
+widoczna stalowa konstrukcja;
+cztery metalowe nogi;
+smukłe metalowe nogi;
+wysokie nogi;
+wykręcane nogi;
+kulowe stopki;
+ruchome stopki;
+prześwit pod siedziskiem;
+brak drewnianych podłokietników;
+otwarta konstrukcja;
+obszerne siedzisko;
+obszerne oparcie</t>
   </si>
   <si>
     <t>Typ 300-123</t>
@@ -1026,7 +1121,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="20">
     <dxf>
@@ -3267,7 +3362,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="381.75">
+    <row r="4" spans="1:14" ht="409.6">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -3355,7 +3450,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="321">
+    <row r="6" spans="1:14" ht="409.6">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -4070,7 +4165,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="106.5">
+    <row r="2" spans="1:2" ht="381.75">
       <c r="A2" s="9" t="s">
         <v>91</v>
       </c>
@@ -4078,7 +4173,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="91.5">
+    <row r="3" spans="1:2" ht="381.75">
       <c r="A3" s="9" t="s">
         <v>103</v>
       </c>
@@ -4086,7 +4181,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="91.5">
+    <row r="4" spans="1:2" ht="366">
       <c r="A4" s="9" t="s">
         <v>26</v>
       </c>
@@ -4102,7 +4197,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="76.5">
+    <row r="6" spans="1:2" ht="381.75">
       <c r="A6" s="9" t="s">
         <v>38</v>
       </c>

--- a/data/furniture.xlsx
+++ b/data/furniture.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3147F11-BFBA-4623-B963-325CD87AC8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B691E158-FE89-466B-8953-B0ED820191F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmark" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="294">
   <si>
     <t>Prompt 1</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>Potoczna nazwa</t>
+  </si>
+  <si>
+    <t>REFERENCE_ID</t>
   </si>
   <si>
     <t>Projektant</t>
@@ -1123,7 +1126,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="21">
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1164,6 +1167,25 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1477,7 +1499,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAC340A0-F689-4CF5-934F-277213A09CD2}" name="Tabela1" displayName="Tabela1" ref="A2:M42" totalsRowShown="0" headerRowDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAC340A0-F689-4CF5-934F-277213A09CD2}" name="Tabela1" displayName="Tabela1" ref="A2:M42" totalsRowShown="0" headerRowDxfId="20">
   <autoFilter ref="A2:M42" xr:uid="{AAC340A0-F689-4CF5-934F-277213A09CD2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M8">
     <sortCondition ref="C2:C8"/>
@@ -1491,7 +1513,7 @@
     <tableColumn id="5" xr3:uid="{FC87805C-8F21-4877-A2BB-F94A46848488}" name="Top3 contains"/>
     <tableColumn id="12" xr3:uid="{083260FC-C283-425D-8992-A120FCD63F58}" name="Model Family"/>
     <tableColumn id="6" xr3:uid="{C375EF1E-B099-4419-8B9C-B2440FD0A8ED}" name="Designer"/>
-    <tableColumn id="7" xr3:uid="{DD17F6C6-7610-4EE0-A977-F8A13F1B8EBA}" name="Confidence" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{DD17F6C6-7610-4EE0-A977-F8A13F1B8EBA}" name="Confidence" dataDxfId="19"/>
     <tableColumn id="8" xr3:uid="{B609250C-19DF-4BCE-8148-69FA85A5C4D5}" name="Error Type"/>
     <tableColumn id="9" xr3:uid="{7ECB45DF-B162-4E08-85FE-5889D14F4EA2}" name="Notes"/>
     <tableColumn id="10" xr3:uid="{7DB3FB91-9C91-4420-A0AD-58F455F6AD18}" name="Severity"/>
@@ -1502,12 +1524,13 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0B9BF425-AAE6-496E-A318-81223EDA70A0}" name="Table2" displayName="Table2" ref="A1:N21" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A1:N21" xr:uid="{0B9BF425-AAE6-496E-A318-81223EDA70A0}"/>
-  <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{BEC8128C-B6F8-41AF-8B4E-AC51172C6F9B}" name="ID" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{A4D5EBAD-8137-4068-9AB3-4017AE021691}" name="Model" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{2E31A0DA-DF43-4372-8896-81E05381952A}" name="Potoczna nazwa" dataDxfId="13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0B9BF425-AAE6-496E-A318-81223EDA70A0}" name="Table2" displayName="Table2" ref="A1:O21" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A1:O21" xr:uid="{0B9BF425-AAE6-496E-A318-81223EDA70A0}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{BEC8128C-B6F8-41AF-8B4E-AC51172C6F9B}" name="ID" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{A4D5EBAD-8137-4068-9AB3-4017AE021691}" name="Model" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{2E31A0DA-DF43-4372-8896-81E05381952A}" name="Potoczna nazwa" dataDxfId="14"/>
+    <tableColumn id="16" xr3:uid="{21289632-27BD-4A17-A0EC-06689B74EAF5}" name="REFERENCE_ID" dataDxfId="13"/>
     <tableColumn id="4" xr3:uid="{BFBF567B-85D5-410F-86B7-E7A5AE9C3740}" name="Projektant" dataDxfId="12"/>
     <tableColumn id="5" xr3:uid="{C0BA823A-68AD-4568-86DC-D7A0821FE81E}" name="Rok" dataDxfId="11"/>
     <tableColumn id="6" xr3:uid="{A85EDE16-4C80-416A-961D-E6418592861C}" name="Typ" dataDxfId="10"/>
@@ -3212,25 +3235,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E570A043-1276-4CEE-AF12-19208D26EAA5}">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" customWidth="1"/>
-    <col min="6" max="6" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.5703125" customWidth="1"/>
-    <col min="8" max="8" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.7109375" customWidth="1"/>
-    <col min="10" max="10" width="27" customWidth="1"/>
-    <col min="11" max="11" width="31" customWidth="1"/>
-    <col min="12" max="12" width="24.140625" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.5703125" customWidth="1"/>
+    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" customWidth="1"/>
+    <col min="11" max="11" width="27" customWidth="1"/>
+    <col min="12" max="12" width="31" customWidth="1"/>
+    <col min="13" max="13" width="24.140625" customWidth="1"/>
+    <col min="14" max="14" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="5" t="s">
         <v>77</v>
       </c>
@@ -3264,7 +3288,7 @@
       <c r="K1" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="5" t="s">
         <v>88</v>
       </c>
       <c r="M1" s="10" t="s">
@@ -3273,19 +3297,22 @@
       <c r="N1" s="10" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="409.6">
+      <c r="O1" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="409.6">
       <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" s="9" t="s">
         <v>93</v>
+      </c>
+      <c r="D2" s="9">
+        <v>366</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>94</v>
@@ -3311,34 +3338,37 @@
       <c r="L2" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="N2" s="11">
         <v>0.98</v>
       </c>
-      <c r="N2" s="9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="409.6">
+      <c r="O2" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="409.6">
       <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D3" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="9">
+      <c r="D3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3" s="9">
         <v>1967</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>95</v>
-      </c>
       <c r="G3" s="9" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>107</v>
@@ -3355,14 +3385,17 @@
       <c r="L3" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="N3" s="11">
         <v>0.88</v>
       </c>
-      <c r="N3" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="409.6">
+      <c r="O3" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="409.6">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -3370,19 +3403,19 @@
         <v>26</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="D4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>115</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>117</v>
@@ -3399,34 +3432,37 @@
       <c r="L4" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="M4" s="11">
+      <c r="M4" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="N4" s="11">
         <v>0.8</v>
       </c>
-      <c r="N4" s="9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="409.6">
+      <c r="O4" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="409.6">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>125</v>
+        <v>34</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>128</v>
@@ -3443,14 +3479,17 @@
       <c r="L5" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="N5" s="11">
         <v>0.82</v>
       </c>
-      <c r="N5" s="9" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="409.6">
+      <c r="O5" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="409.6">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -3458,19 +3497,19 @@
         <v>38</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E6" s="9">
+        <v>38</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6" s="9">
         <v>1962</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>95</v>
-      </c>
       <c r="G6" s="9" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>137</v>
@@ -3487,37 +3526,40 @@
       <c r="L6" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="N6" s="11">
         <v>0.85</v>
       </c>
-      <c r="N6" s="9" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="409.6">
+      <c r="O6" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="409.6">
       <c r="A7" s="9">
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>145</v>
+        <v>42</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>146</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>148</v>
@@ -3531,34 +3573,37 @@
       <c r="L7" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="N7" s="11">
         <v>0.9</v>
       </c>
-      <c r="N7" s="9" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="409.6">
+      <c r="O7" s="9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="409.6">
       <c r="A8" s="9">
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="E8" s="9">
+        <v>45</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F8" s="9">
         <v>1958</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>95</v>
-      </c>
       <c r="G8" s="9" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>157</v>
@@ -3575,34 +3620,35 @@
       <c r="L8" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="M8" s="11">
+      <c r="M8" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="N8" s="11">
         <v>0.99</v>
       </c>
-      <c r="N8" s="9" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="366">
+      <c r="O8" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="366">
       <c r="A9" s="9">
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="D9" s="9" t="s">
         <v>165</v>
       </c>
+      <c r="D9" s="9"/>
       <c r="E9" s="9" t="s">
         <v>166</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>167</v>
+        <v>96</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>168</v>
@@ -3619,34 +3665,35 @@
       <c r="L9" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="M9" s="11">
+      <c r="M9" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="N9" s="11">
         <v>0.92</v>
       </c>
-      <c r="N9" s="9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="409.6">
+      <c r="O9" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="409.6">
       <c r="A10" s="9">
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>135</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>178</v>
@@ -3663,31 +3710,32 @@
       <c r="L10" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="M10" s="11">
+      <c r="M10" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="N10" s="11">
         <v>0.87</v>
       </c>
-      <c r="N10" s="9" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="409.6">
+      <c r="O10" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="409.6">
       <c r="A11" s="9">
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="D11" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="E11" s="9">
+      <c r="D11" s="9"/>
+      <c r="E11" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F11" s="9">
         <v>1965</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>187</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>188</v>
@@ -3707,34 +3755,35 @@
       <c r="L11" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="M11" s="11">
+      <c r="M11" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="N11" s="11">
         <v>0.96</v>
       </c>
-      <c r="N11" s="9" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="409.6">
+      <c r="O11" s="9" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="409.6">
       <c r="A12" s="9">
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>93</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
-        <v>197</v>
+        <v>94</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>199</v>
@@ -3751,34 +3800,35 @@
       <c r="L12" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="M12" s="11">
+      <c r="M12" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="N12" s="11">
         <v>0.94</v>
       </c>
-      <c r="N12" s="9" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="409.6">
+      <c r="O12" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="409.6">
       <c r="A13" s="9">
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="D13" s="9" t="s">
         <v>207</v>
       </c>
+      <c r="D13" s="9"/>
       <c r="E13" s="9" t="s">
         <v>208</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>210</v>
@@ -3795,32 +3845,33 @@
       <c r="L13" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="M13" s="11">
+      <c r="M13" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="N13" s="11">
         <v>0.96</v>
       </c>
-      <c r="N13" s="9" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="366">
+      <c r="O13" s="9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="366">
       <c r="A14" s="9">
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="9" t="s">
-        <v>217</v>
-      </c>
+      <c r="D14" s="9"/>
       <c r="E14" s="9" t="s">
         <v>218</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>95</v>
+        <v>219</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>220</v>
@@ -3837,14 +3888,17 @@
       <c r="L14" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="M14" s="11">
+      <c r="M14" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="N14" s="11">
         <v>0.72</v>
       </c>
-      <c r="N14" s="9" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="409.6">
+      <c r="O14" s="9" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="409.6">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -3852,17 +3906,15 @@
         <v>60</v>
       </c>
       <c r="C15" s="9"/>
-      <c r="D15" s="9" t="s">
-        <v>226</v>
-      </c>
+      <c r="D15" s="9"/>
       <c r="E15" s="9" t="s">
         <v>227</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>95</v>
+        <v>228</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>228</v>
+        <v>96</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>229</v>
@@ -3879,32 +3931,33 @@
       <c r="L15" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="M15" s="11">
+      <c r="M15" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="N15" s="11">
         <v>0.9</v>
       </c>
-      <c r="N15" s="9" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="396.75">
+      <c r="O15" s="9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="396.75">
       <c r="A16" s="9">
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C16" s="9"/>
-      <c r="D16" s="9" t="s">
-        <v>186</v>
-      </c>
+      <c r="D16" s="9"/>
       <c r="E16" s="9" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>187</v>
+        <v>237</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>238</v>
@@ -3921,34 +3974,35 @@
       <c r="L16" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="M16" s="11">
+      <c r="M16" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="N16" s="11">
         <v>0.93</v>
       </c>
-      <c r="N16" s="9" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="321">
+      <c r="O16" s="9" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="321">
       <c r="A17" s="9">
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="D17" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E17" s="9">
+      <c r="D17" s="9"/>
+      <c r="E17" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F17" s="9">
         <v>1962</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="G17" s="9" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>248</v>
@@ -3965,14 +4019,17 @@
       <c r="L17" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="M17" s="11">
+      <c r="M17" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="N17" s="11">
         <v>0.9</v>
       </c>
-      <c r="N17" s="9" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="381.75">
+      <c r="O17" s="9" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="381.75">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -3980,19 +4037,17 @@
         <v>67</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D18" s="9" t="s">
         <v>255</v>
       </c>
+      <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
         <v>256</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>257</v>
+        <v>188</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>258</v>
@@ -4009,32 +4064,32 @@
       <c r="L18" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="M18" s="11">
+      <c r="M18" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="N18" s="11">
         <v>0.91</v>
       </c>
-      <c r="N18" s="9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="409.6">
+      <c r="O18" s="9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="409.6">
       <c r="A19" s="9">
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C19" t="s">
-        <v>265</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9" t="s">
         <v>266</v>
       </c>
+      <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>95</v>
+        <v>267</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>267</v>
+        <v>96</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>268</v>
@@ -4051,32 +4106,33 @@
       <c r="L19" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="M19" s="11">
+      <c r="M19" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="N19" s="11">
         <v>0.95</v>
       </c>
-      <c r="N19" s="9" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="396.75">
+      <c r="O19" s="9" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="396.75">
       <c r="A20" s="9">
         <v>19</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D20" s="9"/>
-      <c r="E20" s="9" t="s">
-        <v>218</v>
-      </c>
+      <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>95</v>
+        <v>219</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>276</v>
+        <v>96</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>277</v>
@@ -4093,32 +4149,33 @@
       <c r="L20" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="M20" s="11">
+      <c r="M20" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="N20" s="11">
         <v>0.95</v>
       </c>
-      <c r="N20" s="9" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="366">
+      <c r="O20" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="366">
       <c r="A21" s="9">
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
-      <c r="E21" s="9" t="s">
-        <v>284</v>
-      </c>
+      <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="G21" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="G21" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>286</v>
       </c>
       <c r="I21" s="9" t="s">
@@ -4133,11 +4190,14 @@
       <c r="L21" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="M21" s="11">
+      <c r="M21" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="N21" s="11">
         <v>0.86</v>
       </c>
-      <c r="N21" s="9" t="s">
-        <v>291</v>
+      <c r="O21" s="9" t="s">
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -4162,23 +4222,23 @@
         <v>78</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="381.75">
       <c r="A2" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="381.75">
       <c r="A3" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="366">
@@ -4186,15 +4246,15 @@
         <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="91.5">
       <c r="A5" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="381.75">
@@ -4202,71 +4262,71 @@
         <v>38</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="91.5">
       <c r="A7" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="106.5">
       <c r="A8" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="76.5">
       <c r="A9" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="152.25">
       <c r="A10" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="183">
       <c r="A11" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="91.5">
       <c r="A12" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="91.5">
       <c r="A13" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="76.5">
       <c r="A14" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="91.5">
@@ -4274,23 +4334,23 @@
         <v>60</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="91.5">
       <c r="A16" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="76.5">
       <c r="A17" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="91.5">
@@ -4298,31 +4358,31 @@
         <v>67</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="91.5">
       <c r="A19" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="91.5">
       <c r="A20" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="76.5">
       <c r="A21" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>

--- a/data/furniture.xlsx
+++ b/data/furniture.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B691E158-FE89-466B-8953-B0ED820191F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21A469CB-CEF7-437C-AD60-690DE7A566ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmark" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="298">
   <si>
     <t>Prompt 1</t>
   </si>
@@ -353,6 +353,681 @@
   </si>
   <si>
     <t>opracowania dotyczące Józefa Chierowskiego; dokumentacja 366 Concept; zbiory Muzeum Narodowego w Warszawie; Polski New Look Ewa Solarz i Agnieszka Sural; publikacje o polskim wzornictwie powojennym</t>
+  </si>
+  <si>
+    <t>armchair;
+wooden frame;
+open frame;
+a-frame side construction;
+triangular side frame;
+angled front support;
+flat plank armrests;
+rounded wooden armrests;
+wide wooden armrests;
+visible screw joints;
+tapered wooden legs;
+splayed legs;
+floating seat;
+rounded box seat cushion;
+rounded rectangular backrest;
+slightly reclined backrest;
+button tufting;
+integrated seat and backrest;
+open space under seat;
+exposed wooden structure;
+organic armrest shape;</t>
+  </si>
+  <si>
+    <t>Fotel typ 300-190</t>
+  </si>
+  <si>
+    <t>Lisek</t>
+  </si>
+  <si>
+    <t>Henryk Lis</t>
+  </si>
+  <si>
+    <t>Dolnośląska Fabryka Mebli w Świebodzicach; Bystrzyckie Fabryki Mebli; Zakład Mebli Giętych FAMEG Radomsko; Świdnicki Ośrodek Przemysłu Meblarskiego</t>
+  </si>
+  <si>
+    <t>Fotel posiada lekką, smukłą konstrukcję opartą na odsłoniętej drewnianej ramie. Tapicerowane siedzisko i oparcie osadzone są pomiędzy drewnianymi boczkami zakończonymi płaskimi podłokietnikami. Konstrukcja wsparta jest na czterech toczonych, lekko zwężających się nogach. W połowie wysokości nóg widoczne są poprzeczne belki tworzące charakterystyczną ramę usztywniającą. Drewniane elementy wykończone były lakierem o wykończeniu matowym, półmatowym lub z połyskiem.</t>
+  </si>
+  <si>
+    <t>Konstrukcję nośną tworzą drewniane boczki połączone poprzecznymi belkami oraz stelażem. Nogi są mocowane do płaskich podłokietników. Do wykonania stolarki zastosowano drewno bukowe. Siedzisko wykorzystuje formatki gumowe osadzone na elastycznych pasach zamiast sprężyn i tradycyjnych wypełnień.</t>
+  </si>
+  <si>
+    <t>typ 366; GFM-64; fotele klubowe PRL z lat 60.</t>
+  </si>
+  <si>
+    <t>zestaw Odra; zestaw Syrena; warianty produkcyjne różnych fabryk (Do weryfikacji)</t>
+  </si>
+  <si>
+    <t>Nowohuckie Renowacje – Fotel Lisek typ 300-190; Conchita Home – 4 fotele z PRL które musisz znać; dokumentacja i opisy egzemplarzy Typ 300-190; archiwalne materiały producentów cytowane w opracowaniach specjalistycznych</t>
+  </si>
+  <si>
+    <t>armchair;
+wooden frame;
+open frame;
+rectangular side frame;
+horizontal lower stretcher;
+flat plank armrests;
+long narrow armrests;
+rounded armrest ends;
+vertical front support;
+angled rear support;
+tapered wooden legs;
+slightly splayed legs;
+floating upholstered seat;
+box seat cushion;
+tall rectangular backrest;
+slightly reclined backrest;
+thin side profile;
+lightweight construction;
+visible wooden frame;
+open space under seat;
+straight geometric lines;
+minimalist frame;
+visible side rails;
+parallel armrests;
+rectangular geometry;
+exposed wooden structure;</t>
+  </si>
+  <si>
+    <t>Do weryfikacji; często błędnie określany jako „Lisek”</t>
+  </si>
+  <si>
+    <t>Henryk Lis (do potwierdzenia)</t>
+  </si>
+  <si>
+    <t>1969–1970</t>
+  </si>
+  <si>
+    <t>Zakłady Przemysłu Meblarskiego im. Gwardii Ludowej w Radomsku; Fabryki Mebli Radomsko</t>
+  </si>
+  <si>
+    <t>Fotel posiada otwartą drewnianą konstrukcję zewnętrzną wykonaną z litego drewna. Tapicerowane siedzisko i oparcie zamocowane są wewnątrz drewnianej ramy za pomocą wkrętów lub śrub. Konstrukcja opiera się na czterech toczonych nogach połączonych belkami podtrzymującymi siedzisko. Charakterystycznym elementem są zaokrąglone drewniane podłokietniki stanowiące integralną część bocznej ramy.</t>
+  </si>
+  <si>
+    <t>Konstrukcja wykonana jest z litej tarcicy bukowej. Szkielet ukryty pod tapicerką wykonano z tarcicy iglastej. Siedzisko i oparcie mocowane są do ramy za pomocą wkrętów lub śrub. Połączenia konstrukcyjne obejmują połączenia czopowe oraz połączenia na wkręty. W siedzisku zastosowano pasy tapicerskie i tworzywo piankowe.</t>
+  </si>
+  <si>
+    <t>typ 300-190 Lisek; BW-14; typ 366</t>
+  </si>
+  <si>
+    <t>rodzina foteli Radomsko o otwartej konstrukcji ramowej; BW-14; typ 300-190 Lisek (wizualnie pokrewny)</t>
+  </si>
+  <si>
+    <t>Patyna.pl – fotel B-7727 Radomsko PRL; Meblostan – fotel B-7727; Nowohuckie Renowacje – fotel B-7727; Vilandy – fotel Lis typ B-7727; Allegro – fotel PRL model B-7727 Radomsko lata 70; Reko-Czyny – identyfikacja fotela B-7727</t>
+  </si>
+  <si>
+    <t>wooden frame;
+open frame;
+rectangular side frame;
+floating seat;
+floating backrest;
+separate seat cushion;
+separate backrest;
+box seat cushion;
+tall rectangular backrest;
+slightly reclined backrest;
+rounded plank armrests;
+wide rounded armrests;
+thick armrests;
+rounded armrest ends;
+curved armrest profile;
+vertical front support;
+angled rear support;
+horizontal lower stretcher;
+tapered wooden legs;
+slightly splayed legs;
+rounded wooden posts;
+visible screw joints;
+visible frame connections;
+solid wooden frame;
+heavier frame;
+robust construction;
+visible wooden side rails;
+open space under seat;</t>
+  </si>
+  <si>
+    <t>Typ 300-177</t>
+  </si>
+  <si>
+    <t>Bunny; Zajączek</t>
+  </si>
+  <si>
+    <t>Józef Chierowski (Do weryfikacji – atrybucja często powtarzana w źródłach kolekcjonerskich, słabo potwierdzona w publikacjach naukowych)</t>
+  </si>
+  <si>
+    <t>początek lat 60. XX w.</t>
+  </si>
+  <si>
+    <t>Świebodzińskie Fabryki Mebli; Gościcińskie Fabryki Mebli</t>
+  </si>
+  <si>
+    <t>trójkątne podłokietniki; lekka drewniana konstrukcja; kompaktowe wymiary; szeroko rozstawione nogi; tapicerowane siedzisko i oparcie; forma nawiązująca do modelu 366</t>
+  </si>
+  <si>
+    <t>bukowy stelaż; otwarta konstrukcja boczna; tapicerowane moduły siedziska i oparcia; drewniane podłokietniki zintegrowane z ramą; konstrukcja szkieletowa</t>
+  </si>
+  <si>
+    <t>typ 366; typ 300-190 Lisek; BW-14</t>
+  </si>
+  <si>
+    <t>typ 366; grupa lekkich foteli drewnianych PRL z lat 60.; modele produkowane przez Świebodzińskie i Gościcińskie Fabryki Mebli (Do weryfikacji)</t>
+  </si>
+  <si>
+    <t>Meblostan – Fotel Bunny typ 300-177; Nowohuckie Renowacje – Fotel typ 300-177 Zajączek; Patyna.pl – Fotel Bunny typ 300-177; Tkaniny-Meblowe.pl – Fotele z PRL-u; materiały kolekcjonerskie rynku vintage</t>
+  </si>
+  <si>
+    <t>trójkątne podłokietniki przypominające uszy zająca; otwarta drewniana rama boczna; szeroko rozstawione nogi; podłokietniki połączone z przednimi nogami; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; duży prześwit pod siedziskiem; smukła lekka bryła; odsłonięty drewniany stelaż; skośne tylne nogi; geometryczny profil boczny; kompaktowe proporcje</t>
+  </si>
+  <si>
+    <t>Fotel Ewa; Muszelka Ewa</t>
+  </si>
+  <si>
+    <t>Do weryfikacji</t>
+  </si>
+  <si>
+    <t>Strzeleckie Zakłady Przemysłu Terenowego w Strzelcach Opolskich</t>
+  </si>
+  <si>
+    <t>Fotel posiada muszelkowy, kubełkowy korpus tworzący jednolitą tapicerowaną bryłę. Szerokie, półkoliste oparcie płynnie przechodzi w siedzisko, nadając bryle profil przypominający muszlę. Korpus osadzony jest na odsłoniętym stalowym stelażu wspartym na czterech smukłych metalowych nogach. Fotel nie posiada drewnianych podłokietników, a wysoka podstawa nadaje konstrukcji lekką formę.</t>
+  </si>
+  <si>
+    <t>Konstrukcję nośną stanowi rama wykonana ze spawanych prętów stalowych. Rama wsparta jest na czterech stalowych, wykręcanych nogach zakończonych ruchomymi stopkami. W modelu Koeln 1 zastosowano pojedynczą stalową nogę obrotową.</t>
+  </si>
+  <si>
+    <t>fotel Köln 1; fotel Muszelka; fotele klubowe na stelażu stalowym z lat 60.</t>
+  </si>
+  <si>
+    <t>Köln 1 (NRD); fotele muszelkowe PRL; metalowe fotele klubowe lat 60.</t>
+  </si>
+  <si>
+    <t>Meblostan – Para foteli tapicerowanych EWA; Odnowa Mebli – Fotel Ewa; Patyna.pl – Komplet foteli typ Ewa; materiały kolekcjonerskie rynku vintage</t>
+  </si>
+  <si>
+    <t>rounded_shell;
+bucket_seat;
+integrated_shell;
+one_piece_body;
+continuous_backrest;
+continuous_armrests;
+curved_side_profile;
+organic_shape;
+wide_rounded_backrest;
+rounded_top_backrest;
+high_backrest;
+integrated_armrests;
+wrapped_armrests;
+upholstered_shell;
+soft_shell;
+floating_shell;
+metal_frame;
+steel_frame;
+four_metal_legs;
+slender_metal_legs;
+slightly_splayed_legs;
+black_metal_legs;
+metal_feet;
+round_feet_caps;
+open_space_under_shell;
+no_wooden_frame;
+no_wooden_armrests;
+lightweight_construction;
+minimalist_design;</t>
+  </si>
+  <si>
+    <t>Typ 300-123</t>
+  </si>
+  <si>
+    <t>Puchała; wersja damska (Do weryfikacji)</t>
+  </si>
+  <si>
+    <t>Mieczysław Puchała</t>
+  </si>
+  <si>
+    <t>1956 (według części źródeł); początek lat 60. XX w.</t>
+  </si>
+  <si>
+    <t>lekka smukła sylwetka; gięte drewniane podłokietniki; wysokie oparcie; wąskie proporcje; odsłonięta drewniana konstrukcja; toczone nogi; modernistyczna forma inspirowana wzornictwem skandynawskim</t>
+  </si>
+  <si>
+    <t>drewniany stelaż bukowy; otwarta konstrukcja boczna; tapicerowane siedzisko; tapicerowane oparcie; pasy tapicerskie; konstrukcja szkieletowa</t>
+  </si>
+  <si>
+    <t>typ 300-137; typ 300-190 Lisek; typ 366</t>
+  </si>
+  <si>
+    <t>typ 300-137 wersja męska; rodzina foteli projektu Mieczysława Puchały; lekkie fotele drewniane PRL lat 50. i 60</t>
+  </si>
+  <si>
+    <t>Nowohuckie Renowacje – Fotel typ 300-123 Puchała; Szajba Sklep – Fotel klubowy typ 300-123 proj. M. Puchała; LookInside – Fotel typ 300-123 Puchała; Pakamera – Fotel typ 300-123 M. Puchała; Meblostan – Fotel Puchały typ 300-123</t>
+  </si>
+  <si>
+    <t>gięte drewniane podłokietniki; smukłe wysokie oparcie; wąskie proporcje korpusu; otwarta drewniana rama boczna; toczone nogi zwężające się ku dołowi; widoczny prześwit pod siedziskiem; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; lekka dynamiczna bryła; cienkie elementy konstrukcyjne; profil boczny z łukowato wygiętym podłokietnikiem; minimalistyczna forma lat 50./60.</t>
+  </si>
+  <si>
+    <t>RM58</t>
+  </si>
+  <si>
+    <t>Muszelka; RM58</t>
+  </si>
+  <si>
+    <t>Roman Modzelewski</t>
+  </si>
+  <si>
+    <t>Zakłady Mebli Artystycznych w Łodzi (prototyp); Vzór Sp. z o.o. (reedycja od 2012 r.)</t>
+  </si>
+  <si>
+    <t>organiczna muszelkowa forma; jednolita zamknięta bryła; głębokie kubełkowe siedzisko; szerokie wywinięte boki; opływowy futurystyczny kształt; brak klasycznych podłokietników; rzeźbiarska sylwetka</t>
+  </si>
+  <si>
+    <t>jednoczęściowy korpus z laminatu poliestrowo-szklanego; tapicerowana wkładka siedziska; cztery smukłe nogi; technologia laminatu wyprzedzająca epokę w Polsce; konstrukcja skorupowa</t>
+  </si>
+  <si>
+    <t>fotel Ewa; fotele muszelkowe produkcji NRD; zachodnie fotele fiberglass lat 50.; projekty Eero Saarinena</t>
+  </si>
+  <si>
+    <t>prototypowe meble z laminatu Romana Modzelewskiego; współczesne reedycje RM58; warianty kolorystyczne RM58 Classic</t>
+  </si>
+  <si>
+    <t>Muzeum Narodowe we Wrocławiu; Vzór – dokumentacja reedycji RM58; Instytut Wzornictwa Przemysłowego; publikacje o twórczości Romana Modzelewskiego; Culture.pl</t>
+  </si>
+  <si>
+    <t>jednoczęściowa muszelkowa skorupa; organiczna opływowa bryła; głębokie kubełkowe siedzisko; szerokie wywinięte boki; zaokrąglone wysokie oparcie; brak oddzielnych podłokietników; korpus przypominający muszlę; zamknięta forma boczna; cztery cienkie nogi; futurystyczna sylwetka lat 50.; brak widocznej drewnianej konstrukcji; płynne przejścia między siedziskiem i oparciem; asymetrycznie zaokrąglone krawędzie; korpus wykonany jako pojedyncza skorupa</t>
+  </si>
+  <si>
+    <t>B-2020</t>
+  </si>
+  <si>
+    <t>Tulipan</t>
+  </si>
+  <si>
+    <t>Teresa Kruszewska</t>
+  </si>
+  <si>
+    <t>1973 (prototyp)</t>
+  </si>
+  <si>
+    <t>FAMEG Radomsko (reedycja współczesna)</t>
+  </si>
+  <si>
+    <t>organiczna forma inspirowana kielichem kwiatu; szerokie kubełkowe siedzisko; płynne przejście między siedziskiem i oparciem; miękkie zaokrąglone linie; wyraźnie rozchylone boki; rzeźbiarska bryła</t>
+  </si>
+  <si>
+    <t>korpus ze sklejki formowanej; tapicerowana skorupa; drewniana podstawa; konstrukcja monolityczna; technologia giętej sklejki</t>
+  </si>
+  <si>
+    <t>RM58; fotele muszelkowe PRL; fotele skandynawskie o organicznej formie</t>
+  </si>
+  <si>
+    <t>projekty Teresy Kruszewskiej; meble ze sklejki formowanej; współczesna kolekcja Tulipan FAMEG</t>
+  </si>
+  <si>
+    <t>FAMEG – Fotel Tulipan B-2020; dokumentacja reedycji FAMEG; opracowania dotyczące twórczości Teresy Kruszewskiej</t>
+  </si>
+  <si>
+    <t>kubełkowe siedzisko; forma przypominająca kielich tulipana; szeroko rozchylone boki; jednolita tapicerowana skorupa; zaokrąglone wysokie oparcie; płynne przejście między siedziskiem i oparciem; organiczna bryła; brak widocznej drewnianej ramy bocznej; miękkie obłe krawędzie; rzeźbiarska forma; kompaktowa podstawa; sylwetka kwiatu tulipana</t>
+  </si>
+  <si>
+    <t>Typ 300-201</t>
+  </si>
+  <si>
+    <t>Śnieżnik; Śnieżka (Do weryfikacji – obie nazwy występują w obiegu kolekcjonerskim, częściej spotykana jest nazwa Śnieżnik)</t>
+  </si>
+  <si>
+    <t>1973 (najwcześniejsza potwierdzona wzmianka źródłowa)</t>
+  </si>
+  <si>
+    <t>Bystrzycka Fabryka Mebli w Bystrzycy Kłodzkiej</t>
+  </si>
+  <si>
+    <t>lekka konstrukcja drewniana; forma inspirowana modelem Lisek 300-190; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; otwarta rama boczna; charakterystyczne nogi częściowo graniaste i częściowo zaokrąglone; smukłe proporcje</t>
+  </si>
+  <si>
+    <t>drewniany stelaż brzozowy lub bukowy; otwarta konstrukcja boczna; tapicerowane siedzisko; tapicerowane oparcie; pasy tapicerskie; konstrukcja szkieletowa</t>
+  </si>
+  <si>
+    <t>typ 300-190 Lisek; Śnieżka; BW-14 typ 300-199; B-7727</t>
+  </si>
+  <si>
+    <t>typ 300-190 Lisek; Śnieżka; BW-14 typ 300-199; BW-20 typ 300-193; B-7727</t>
+  </si>
+  <si>
+    <t>Meblostan – Fotel Śnieżnik typ 300-201; Nowohuckie Renowacje – Fotele PRL; Pakamera – Fotel Śnieżnik typ 300-201; Audiovintage Store – Fotel klubowy Śnieżnik 300-201</t>
+  </si>
+  <si>
+    <t>otwarta drewniana rama boczna; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; smukła lekka bryła; duży prześwit pod siedziskiem; drewniane podłokietniki zintegrowane z ramą; nogi graniaste od góry; nogi zaokrąglone w dolnej części; skośne tylne nogi; widoczne drewniane elementy konstrukcyjne; forma zbliżona do modelu Lisek; geometryczny profil boczny
+Źródła potwierdzają produkcję w Bystrzyckiej Fabryce Mebli oraz silne pokrewieństwo konstrukcyjne z modelem 300-190 „Lisek”, natomiast projektant pozostaje niepotwierdzony.</t>
+  </si>
+  <si>
+    <t>GFM-57</t>
+  </si>
+  <si>
+    <t>Skoczek</t>
+  </si>
+  <si>
+    <t>Juliusz Kędziorek</t>
+  </si>
+  <si>
+    <t>Krzesło</t>
+  </si>
+  <si>
+    <t>Gościcińska Fabryka Mebli; Zamojskie Fabryki Mebli (produkcja seryjna jako typ 200-203)</t>
+  </si>
+  <si>
+    <t>łukowate podłokietniki przypominające profil skoczni narciarskiej; elipsoidalne oparcie; lekka ażurowa konstrukcja; zwężające się ku dołowi nogi; tapicerowane siedzisko; smukła sylwetka; organiczna linia boczna</t>
+  </si>
+  <si>
+    <t>drewniany stelaż; otwarta konstrukcja boczna; tapicerowane siedzisko; gięte elementy drewniane; konstrukcja przeznaczona do produkcji seryjnej</t>
+  </si>
+  <si>
+    <t>typ 200-190 Rajmunda Hałasa; krzesła Aga; krzesła patyczaki lat 60.; lekkie krzesła tapicerowane PRL</t>
+  </si>
+  <si>
+    <t>typ 200-203; GFM-107; projekty Juliusza Kędziorka dla Gościcińskiej Fabryki Mebli</t>
+  </si>
+  <si>
+    <t>Magazif – Krzesło Skoczek; Ikony Designu PL – Krzesło GFM-57 Skoczek; Meblostan – Krzesło Skoczek; Sosenko Home Decor – Krzesło Skoczek; Allegro Artykuł – Krzesło kilka słów o najtrudniejszym meblu</t>
+  </si>
+  <si>
+    <t>łukowate podłokietniki przypominające skocznię narciarską; elipsoidalne oparcie; otwarta drewniana rama boczna; smukłe zwężające się nogi; tapicerowane siedzisko; duży prześwit pod siedziskiem; płynna linia podłokietnika przechodząca w nogę; lekka ażurowa konstrukcja; organiczny profil boczny; oparcie w kształcie pionowej elipsy; cienkie elementy drewniane; dynamiczna sylwetka inspirowana skokami narciarskimi
+Źródła potwierdzają, że model został zaprojektowany przez Juliusza Kędziorka w Gościcińskiej Fabryce Mebli w 1965 r., otrzymał nagrodę „Dobre–Ładne–Poszukiwane” i został skierowany do produkcji seryjnej jako typ 200-203</t>
+  </si>
+  <si>
+    <t>Typ 200-125 VAR</t>
+  </si>
+  <si>
+    <t>Aga</t>
+  </si>
+  <si>
+    <t>ok. 1972–1975 (w źródłach występują rozbieżności dotyczące dokładnego roku projektu)</t>
+  </si>
+  <si>
+    <t>Wielkopolskie Fabryki Mebli; produkcja seryjna PRL (pozostali producenci wymagają weryfikacji)</t>
+  </si>
+  <si>
+    <t>wysokie tapicerowane oparcie; trapezowy układ nóg; miękkie tapicerowane siedzisko; smukła skandynawska forma; zwężająca się ku górze bryła; lekkie proporcje; drewniana konstrukcja eksponowana po bokach</t>
+  </si>
+  <si>
+    <t>drewniany stelaż bukowy; tapicerowane siedzisko; tapicerowane oparcie; sprężyny siedziska; cztery drewniane nogi; konstrukcja przeznaczona do intensywnego użytkowania klubowego</t>
+  </si>
+  <si>
+    <t>typ 200-190 Rajmunda Hałasa; GFM-57 Skoczek; lekkie krzesła klubowe PRL lat 70.</t>
+  </si>
+  <si>
+    <t>fotel 366; meble klubowe Józefa Chierowskiego; reedycja 200-125 VAR realizowana przez 366 Concept</t>
+  </si>
+  <si>
+    <t>Elle Decoration Polska – Krzesło VAR AGA projektu Józefa Chierowskiego; Nowohuckie Renowacje – Krzesło Aga typ 200-125; Patyna.pl – Krzesła AGA typu 200-125 VAR; Linie Studio – 200-125 VAR; Meblościanka – 200-125 VAR</t>
+  </si>
+  <si>
+    <t>wysokie tapicerowane oparcie; trapezowy układ nóg; szerokie miękkie siedzisko; brak podłokietników; drewniane nogi rozszerzające się ku dołowi; zwężająca się ku górze sylwetka; lekka skandynawska forma; prostokątne oparcie z zaokrąglonymi krawędziami; widoczne drewniane elementy boczne; smukłe proporcje; geometryczna bryła; profil boczny z pochylonym oparciem</t>
+  </si>
+  <si>
+    <t>Typ 200-190</t>
+  </si>
+  <si>
+    <t>Hałas; Grzybek</t>
+  </si>
+  <si>
+    <t>Rajmund Teofil Hałas</t>
+  </si>
+  <si>
+    <t>lata 60. XX w.; dokładny rok projektu – Do weryfikacji</t>
+  </si>
+  <si>
+    <t>Zakłady Mebli w Gostyniu (Do weryfikacji); produkcja seryjna w kilku zakładach meblarskich PRL – Do weryfikacji</t>
+  </si>
+  <si>
+    <t>okrągła forma oparcia przypominająca kapelusz grzyba; tapicerowane oparcie i siedzisko; smukłe zwężające się nogi; lekka konstrukcja; wyraźnie wyodrębnione oparcie nad siedziskiem; proporcje inspirowane wzornictwem skandynawskim; minimalistyczna sylwetka</t>
+  </si>
+  <si>
+    <t>drewniany stelaż; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; mocowane oddzielnie siedzisko i oparcie; nogi zwężające się ku dołowi</t>
+  </si>
+  <si>
+    <t>Aga 200-125; Skoczek GFM-57; krzesła skandynawskie lat 60.; lekkie krzesła tapicerowane PRL</t>
+  </si>
+  <si>
+    <t>projekty Rajmunda Teofila Hałasa; krzesła tapicerowane PRL lat 60.; warianty produkcyjne typu 200-190</t>
+  </si>
+  <si>
+    <t>Odnawialnia – Wiem co odnawiam | krzesło Hałasa typ 200-190; Patyna.pl – Krzesła typ 200-190 Rajmund Teofil Hałas; Meblostan – Komplet krzeseł typ 200-190; Daniel Stoiński Redesign – Przewodnik po renowacji krzesła 200-190; Homebook – Krzesło Hałasa typ 200-190</t>
+  </si>
+  <si>
+    <t>okrągłe oparcie przypominające grzybek; oparcie szersze od wspornika; tapicerowane okrągłe oparcie; tapicerowane siedzisko; smukłe nogi zwężające się ku dołowi; brak podłokietników; lekka skandynawska forma; duży prześwit pod siedziskiem; cienki drewniany stelaż; wyraźne oddzielenie oparcia od siedziska; geometryczna bryła; profil boczny z lekko odchylonym oparciem</t>
+  </si>
+  <si>
+    <t>B-6028</t>
+  </si>
+  <si>
+    <t>Barbara Fenrych-Węcławska (Do weryfikacji); Józef Chierowski (Do weryfikacji – atrybucja pojawiająca się wyłącznie w źródłach kolekcjonerskich)</t>
+  </si>
+  <si>
+    <t>lata 60. XX w.</t>
+  </si>
+  <si>
+    <t>Fabryka Mebli Giętych w Radomsku; FAMEG Radomsko; Radomszczańska Fabryka Mebli Giętych</t>
+  </si>
+  <si>
+    <t>wysokie profilowane oparcie; szerokie drewniane podłokietniki; gięte elementy bukowe; głębokie siedzisko; lekka otwarta konstrukcja boczna; elegancka smukła sylwetka; forma łącząca cechy fotela klubowego i wypoczynkowego</t>
+  </si>
+  <si>
+    <t>stelaż z giętego drewna bukowego; otwarta konstrukcja ramowa; tapicerowane siedzisko; tapicerowane oparcie; drewniane podłokietniki zintegrowane z ramą; konstrukcja szkieletowa</t>
+  </si>
+  <si>
+    <t>typ 300-123 Puchała; typ 300-177 Zajączek; B-7727; typ 366</t>
+  </si>
+  <si>
+    <t>fotele Radomsko z giętego drewna; projekty Barbary Fenrych-Węcławskiej (Do weryfikacji); lekkie fotele klubowe PRL lat 60.</t>
+  </si>
+  <si>
+    <t>MidMod – Fotel B6028 FAMEG Radomsko Polska lata 60; Oldsen Design – Fotel B6028 prod. FAMEG Radomsko; Nowohuckie Renowacje – Fotel PRL B-6028 z lat 60-tych; Fotelowo Facebook – fotel projektu Barbary Fenrych-Węcławskiej; Instagram Renowacja Mebli PRL – B6028 lata produkcji 1960</t>
+  </si>
+  <si>
+    <t>wysokie prostokątne oparcie; szerokie drewniane podłokietniki; gięte boczne elementy z drewna; otwarta rama boczna; głębokie siedzisko; masywniejsza bryła niż typ 366; bukowy stelaż; duży prześwit pod siedziskiem; profilowane podłokietniki; smukłe nogi zintegrowane z ramą; tapicerowane oparcie i siedzisko; geometryczny profil boczny</t>
+  </si>
+  <si>
+    <t>A. Dutka</t>
+  </si>
+  <si>
+    <t>1966–1968</t>
+  </si>
+  <si>
+    <t>Zakłady Mebli Giętych w Radomsku; Gołuchowskie Fabryki Mebli</t>
+  </si>
+  <si>
+    <t>duże gabaryty; szerokie głębokie siedzisko; masywne drewniane podłokietniki; geometryczna forma boczna; lekko pochylone oparcie; otwarta konstrukcja ramowa; modernistyczna sylwetka eksportowa</t>
+  </si>
+  <si>
+    <t>stelaż z drewna bukowego; sprężyny lejowe w siedzisku; tapicerowane siedzisko i oparcie; otwarta konstrukcja boczna; drewniane podłokietniki zintegrowane z ramą; konstrukcja rozbieralna skręcana śrubami</t>
+  </si>
+  <si>
+    <t>B-6028; GFM-64; typ 300-190 Lisek; B-7727</t>
+  </si>
+  <si>
+    <t>fotele eksportowe Radomsko lat 60.; modele Zakładów Mebli Giętych w Radomsku; konstrukcje projektowane przez A. Dutkę (Do weryfikacji)</t>
+  </si>
+  <si>
+    <t>Meblostan – Para foteli B-310 VAR; Pufa Design – Oryginalny fotel B-310 VAR; Yestersen – Fotel B-310 VAR Polska lata 70.; Reko-Czyny – Fotel B-310 VAR metamorfoza; archiwalne ogłoszenia kolekcjonerskie B-310 VAR</t>
+  </si>
+  <si>
+    <t>masywne drewniane podłokietniki; szerokie głębokie siedzisko; wysunięte przednie podłokietniki; otwarta drewniana rama boczna; prostokątne tapicerowane oparcie; grube proporcje siedziska; lekko pochylone oparcie; duży prześwit pod siedziskiem; widoczne śruby montażowe w ramie; geometryczny profil boczny; szeroki rozstaw nóg; cięższa bryła niż typ 366; bukowy stelaż; modernistyczna forma eksportowa</t>
+  </si>
+  <si>
+    <t>GFM-22 (typ 200/128)</t>
+  </si>
+  <si>
+    <t>ok. 1960</t>
+  </si>
+  <si>
+    <t>Gościcińska Fabryka Mebli (GFM)</t>
+  </si>
+  <si>
+    <t>nerkowate oparcie; lekka ażurowa konstrukcja; smukłe zwężające się nogi; gięta drewniana rama; tapicerowane siedzisko; tapicerowane oparcie; wyraźnie rozstawione tylne nogi</t>
+  </si>
+  <si>
+    <t>drewniany stelaż; gięte elementy z litego drewna; tapicerowane siedzisko; tapicerowane oparcie ze sklejki giętej; konstrukcja szkieletowa przeznaczona do produkcji seryjnej</t>
+  </si>
+  <si>
+    <t>GFM-57 Skoczek; typ 200-190 Rajmunda Hałasa; Aga 200-125; krzesła skandynawskie z lat 60.</t>
+  </si>
+  <si>
+    <t>typ 200/128; projekty Juliusza Kędziorka dla Gościcińskiej Fabryki Mebli; GFM-57; GFM-87</t>
+  </si>
+  <si>
+    <t>Pamono – Mid-Century GFM-22 Chairs by Juliusz Kędziorek; Vinterior – GFM-22 model 200/128; Selency – Iconic GFM-22 Chair by Juliusz Kędziorek; Instagram Zostań z Vintage – Krzesło GFM-22 typ 200/128</t>
+  </si>
+  <si>
+    <t>nerkowate tapicerowane oparcie; oparcie szersze od wspornika; smukłe zwężające się nogi; lekka ażurowa konstrukcja; gięta drewniana rama; prostokątne tapicerowane siedzisko; duży prześwit pod siedziskiem; cienkie elementy konstrukcyjne; szeroko rozstawione tylne nogi; profil boczny z delikatnie pochylonym oparciem; organiczny kształt oparcia; minimalistyczna sylwetka lat 60.</t>
+  </si>
+  <si>
+    <t>Typ 1020</t>
+  </si>
+  <si>
+    <t>Muszelka</t>
+  </si>
+  <si>
+    <t>Wiesław Leśniewski; Stanisław Lejkowski</t>
+  </si>
+  <si>
+    <t>Słupskie Fabryki Mebli</t>
+  </si>
+  <si>
+    <t>muszelkowe profilowane oparcie; jednolita tapicerowana skorupa; zaokrąglona górna krawędź oparcia; smukłe stożkowe nogi; lekka modernistyczna forma; brak podłokietników; organiczna sylwetka</t>
+  </si>
+  <si>
+    <t>profilowana skorupa ze sklejki; tapicerowana skorupa; drewniany stelaż; cztery drewniane nogi; konstrukcja szkieletowa; połączenie sklejki i drewna litego</t>
+  </si>
+  <si>
+    <t>RM58; krzesła muszelkowe produkcji NRD; krzesła skandynawskie lat 60.; fotel Ewa</t>
+  </si>
+  <si>
+    <t>krzesła muszelkowe Słupskich Fabryk Mebli; projekty Wiesława Leśniewskiego i Stanisława Lejkowskiego; meble ze sklejki profilowanej produkowane przez SFM</t>
+  </si>
+  <si>
+    <t>Archiwalne katalogi Słupskich Fabryk Mebli; opracowania kolekcjonerskie dotyczące wzornictwa SFM; materiały renowatorów specjalizujących się w meblach PRL; publikacje poświęcone projektom Wiesława Leśniewskiego i Stanisława Lejkowskiego</t>
+  </si>
+  <si>
+    <t>muszelkowe profilowane oparcie; jednolita tapicerowana skorupa; zaokrąglona górna krawędź oparcia; płynne przejście oparcia w siedzisko; brak podłokietników; cztery smukłe stożkowe drewniane nogi; lekka organiczna bryła; profilowana skorupa ze sklejki; niewielki prześwit pod siedziskiem; forma inspirowana muszlą</t>
+  </si>
+  <si>
+    <t>Bumerang</t>
+  </si>
+  <si>
+    <t>Ryszard Kulm</t>
+  </si>
+  <si>
+    <t>przełom lat 50. i 60. XX w.; produkcja seryjna od początku lat 60</t>
+  </si>
+  <si>
+    <t>Gościcińska Fabryka Mebli</t>
+  </si>
+  <si>
+    <t>charakterystyczne łukowato wygięte przednie nogi przypominające bumerang; lekka ażurowa konstrukcja; tapicerowane siedzisko; tapicerowane oparcie; smukła sylwetka; zwężające się ku dołowi nogi; modernistyczna forma inspirowana skandynawskim wzornictwem</t>
+  </si>
+  <si>
+    <t>drewniany stelaż bukowy; gięte elementy boczne; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; połączenia skręcane i klejone</t>
+  </si>
+  <si>
+    <t>GFM-22; typ 200-190 Rajmunda Hałasa; GFM-57 Skoczek; krzesła skandynawskie lat 60</t>
+  </si>
+  <si>
+    <t>krzesła Gościcińskiej Fabryki Mebli; wariant 299XB (Do weryfikacji); rodzina krzeseł Bumerang</t>
+  </si>
+  <si>
+    <t>Meblostan – Komplet 4 krzeseł Bumerang typ 299; Skarby PRL – Krzesło tapicerowane Bumerang typ 299; Patyna – Komplet krzeseł typ 299 Bumerang; Deccoria – 10 słynnych mebli z PRL; Stary Fotel – Krzesła Bumerang metamorfoza</t>
+  </si>
+  <si>
+    <t>łukowato wygięte przednie nogi w kształcie bumerangu; gięte boczne elementy drewniane; tapicerowane prostokątne siedzisko; tapicerowane oparcie; smukła lekka bryła; cienki drewniany stelaż; zwężające się ku dołowi nogi; wyraźny prześwit pod siedziskiem; organiczny profil boczny; lekko odchylone oparcie; minimalistyczna forma lat 60.; charakterystyczna sylwetka bumerangu</t>
+  </si>
+  <si>
+    <t>Typ 300-227</t>
+  </si>
+  <si>
+    <t>Celia</t>
+  </si>
+  <si>
+    <t>ok. 1965; produkcja na przełomie lat 60. i 70. XX w.</t>
+  </si>
+  <si>
+    <t>Zamojskie Fabryki Mebli</t>
+  </si>
+  <si>
+    <t>brak podłokietników; toczone drewniane nogi umieszczone po bokach części tapicerowanej; trapezowe siedzisko; proste tapicerowane oparcie; lekka minimalistyczna forma; kompaktowe wymiary; stylistyka skandynawskiego modernizmu</t>
+  </si>
+  <si>
+    <t>drewniany stelaż; toczone nogi; tapicerowane siedzisko; tapicerowane oparcie; otwarta konstrukcja bez podłokietników; konstrukcja szkieletowa przeznaczona do produkcji seryjnej</t>
+  </si>
+  <si>
+    <t>typ 300-190 Lisek; typ 366; GFM-64; lekkie fotele klubowe PRL bez podłokietników</t>
+  </si>
+  <si>
+    <t>fotele Zamojskich Fabryk Mebli z lat 60. i 70.; meble klubowe produkowane w Zamościu; modele o minimalistycznej konstrukcji bez podłokietników</t>
+  </si>
+  <si>
+    <t>Meblostan – Fotel CELIA typ 300-227; Patyna – Fotel CELIA typ 300-227 PRL; Szajba Sklep – Fotel Celia typ 300-227; materiały kolekcjonerskie dotyczące Zamojskich Fabryk Mebli</t>
+  </si>
+  <si>
+    <t>brak podłokietników; toczone drewniane nogi umieszczone po bokach korpusu; trapezowe tapicerowane siedzisko; prostokątne tapicerowane oparcie; lekka minimalistyczna bryła; duży prześwit pod siedziskiem; cienki drewniany stelaż; zwężające się ku dołowi nogi; odsłonięte drewniane elementy boczne; kompaktowe proporcje; geometryczny profil boczny; forma inspirowana skandynawskim modernizmem</t>
+  </si>
+  <si>
+    <t>Typ 300-139</t>
+  </si>
+  <si>
+    <t>Stefan</t>
+  </si>
+  <si>
+    <t>Swarzędzka Fabryka Mebli</t>
+  </si>
+  <si>
+    <t>szerokie drewniane podłokietniki o łagodnym łuku; otwarta konstrukcja boczna; luźne tapicerowane poduchy siedziska i oparcia; rozłożysta bryła; lekka skandynawska stylistyka; nisko osadzone siedzisko; masywny drewniany stelaż</t>
+  </si>
+  <si>
+    <t>stelaż z litego drewna bukowego; otwarta rama boczna; osobna poduszka siedziska; osobna poduszka oparcia; pasy tapicerskie; konstrukcja szkieletowa skręcana</t>
+  </si>
+  <si>
+    <t>typ 300-123 Puchała; typ 366; duńskie fotele Kandidaten projektu Ib Kofod-Larsena; fotele skandynawskie lat 60</t>
+  </si>
+  <si>
+    <t>sofa Stefan; zestawy wypoczynkowe Swarzędzkiej Fabryki Mebli; meble eksportowe Swarzędzkiej Fabryki Mebli z lat 60.</t>
+  </si>
+  <si>
+    <t>„Meble w produkcji 1962” – Zjednoczenie Przemysłu Meblarskiego; „Meble do małych mieszkań. Informator”, Wydawnictwo Katalogów i Cenników 1966; Laminerva – „Ikony polskiego designu: Fotel Stefan typ 300-139”; Meblostan – Para foteli Stefan typ 300-139; Patyna – Para foteli Stefan typ 300-139</t>
+  </si>
+  <si>
+    <t>szerokie wyprofilowane drewniane podłokietniki; otwarta drewniana rama boczna; luźna poduszka siedziska; luźna poduszka oparcia; nisko osadzone głębokie siedzisko; prostokątne grube poduchy; lekko odchylone oparcie; masywny bukowy stelaż; duży prześwit pod siedziskiem; szeroki rozstaw przednich nóg; profil boczny inspirowany wzornictwem skandynawskim; rozłożysta bryła eksportowa</t>
+  </si>
+  <si>
+    <t>B-3300</t>
+  </si>
+  <si>
+    <t>ok. 1969; produkcja w końcu lat 60. i na początku lat 70. XX w</t>
+  </si>
+  <si>
+    <t>Zakład Mebli Giętych w Radomsku; Fabryki Mebli Radomsko (późniejsze nazewnictwo zakładu)</t>
+  </si>
+  <si>
+    <t>gięte drewniane podłokietniki; szerokie tapicerowane siedzisko; prostokątne tapicerowane oparcie; otwarta konstrukcja boczna; gięty bukowy stelaż; nisko osadzona bryła; elegancka modernistyczna forma</t>
+  </si>
+  <si>
+    <t>stelaż z giętego drewna bukowego; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; elementy gięte wykonane w technologii Thoneta; konstrukcja skręcana</t>
+  </si>
+  <si>
+    <t>B-310 VAR; B-6028; GFM-64; typ 300-139 Stefan</t>
+  </si>
+  <si>
+    <t>fotele Zakładu Mebli Giętych w Radomsku; modele eksportowe Radomsko z lat 60. i 70.; rodzina foteli z giętego drewna bukowego</t>
+  </si>
+  <si>
+    <t>Patyna – Fotel B-3300 Zakład Mebli Giętych w Radomsku; Meblostan – Para foteli B-3300; archiwalne materiały Fabryk Mebli Radomsko; oferty kolekcjonerskie dokumentujące oryginalne oznaczenie modelu</t>
+  </si>
+  <si>
+    <t>gięte drewniane podłokietniki; otwarta drewniana rama boczna; szerokie prostokątne oparcie; szerokie głębokie siedzisko; bukowy gięty stelaż; duży prześwit pod siedziskiem; łagodnie wygięte boki; zwężające się ku dołowi nogi; lekko pochylone oparcie; masywniejsza bryła niż typ 366; widoczne elementy z giętego drewna; modernistyczna forma gabinetowa</t>
+  </si>
+  <si>
+    <t>Cechy AI</t>
   </si>
   <si>
     <t>drewniane boczki;
@@ -382,33 +1057,6 @@
 brak ozdobnych detali</t>
   </si>
   <si>
-    <t>Fotel typ 300-190</t>
-  </si>
-  <si>
-    <t>Lisek</t>
-  </si>
-  <si>
-    <t>Henryk Lis</t>
-  </si>
-  <si>
-    <t>Dolnośląska Fabryka Mebli w Świebodzicach; Bystrzyckie Fabryki Mebli; Zakład Mebli Giętych FAMEG Radomsko; Świdnicki Ośrodek Przemysłu Meblarskiego</t>
-  </si>
-  <si>
-    <t>Fotel posiada lekką, smukłą konstrukcję opartą na odsłoniętej drewnianej ramie. Tapicerowane siedzisko i oparcie osadzone są pomiędzy drewnianymi boczkami zakończonymi płaskimi podłokietnikami. Konstrukcja wsparta jest na czterech toczonych, lekko zwężających się nogach. W połowie wysokości nóg widoczne są poprzeczne belki tworzące charakterystyczną ramę usztywniającą. Drewniane elementy wykończone były lakierem o wykończeniu matowym, półmatowym lub z połyskiem.</t>
-  </si>
-  <si>
-    <t>Konstrukcję nośną tworzą drewniane boczki połączone poprzecznymi belkami oraz stelażem. Nogi są mocowane do płaskich podłokietników. Do wykonania stolarki zastosowano drewno bukowe. Siedzisko wykorzystuje formatki gumowe osadzone na elastycznych pasach zamiast sprężyn i tradycyjnych wypełnień.</t>
-  </si>
-  <si>
-    <t>typ 366; GFM-64; fotele klubowe PRL z lat 60.</t>
-  </si>
-  <si>
-    <t>zestaw Odra; zestaw Syrena; warianty produkcyjne różnych fabryk (Do weryfikacji)</t>
-  </si>
-  <si>
-    <t>Nowohuckie Renowacje – Fotel Lisek typ 300-190; Conchita Home – 4 fotele z PRL które musisz znać; dokumentacja i opisy egzemplarzy Typ 300-190; archiwalne materiały producentów cytowane w opracowaniach specjalistycznych</t>
-  </si>
-  <si>
     <t>toczone nogi;
 lekko zwężające się nogi;
 cztery drewniane nogi;
@@ -436,33 +1084,6 @@
 minimalistyczna forma</t>
   </si>
   <si>
-    <t>Do weryfikacji; często błędnie określany jako „Lisek”</t>
-  </si>
-  <si>
-    <t>Henryk Lis (do potwierdzenia)</t>
-  </si>
-  <si>
-    <t>1969–1970</t>
-  </si>
-  <si>
-    <t>Zakłady Przemysłu Meblarskiego im. Gwardii Ludowej w Radomsku; Fabryki Mebli Radomsko</t>
-  </si>
-  <si>
-    <t>Fotel posiada otwartą drewnianą konstrukcję zewnętrzną wykonaną z litego drewna. Tapicerowane siedzisko i oparcie zamocowane są wewnątrz drewnianej ramy za pomocą wkrętów lub śrub. Konstrukcja opiera się na czterech toczonych nogach połączonych belkami podtrzymującymi siedzisko. Charakterystycznym elementem są zaokrąglone drewniane podłokietniki stanowiące integralną część bocznej ramy.</t>
-  </si>
-  <si>
-    <t>Konstrukcja wykonana jest z litej tarcicy bukowej. Szkielet ukryty pod tapicerką wykonano z tarcicy iglastej. Siedzisko i oparcie mocowane są do ramy za pomocą wkrętów lub śrub. Połączenia konstrukcyjne obejmują połączenia czopowe oraz połączenia na wkręty. W siedzisku zastosowano pasy tapicerskie i tworzywo piankowe.</t>
-  </si>
-  <si>
-    <t>typ 300-190 Lisek; BW-14; typ 366</t>
-  </si>
-  <si>
-    <t>rodzina foteli Radomsko o otwartej konstrukcji ramowej; BW-14; typ 300-190 Lisek (wizualnie pokrewny)</t>
-  </si>
-  <si>
-    <t>Patyna.pl – fotel B-7727 Radomsko PRL; Meblostan – fotel B-7727; Nowohuckie Renowacje – fotel B-7727; Vilandy – fotel Lis typ B-7727; Allegro – fotel PRL model B-7727 Radomsko lata 70; Reko-Czyny – identyfikacja fotela B-7727</t>
-  </si>
-  <si>
     <t>toczone nogi;
 cztery drewniane nogi;
 zaokrąglone podłokietniki;
@@ -487,63 +1108,6 @@
 widoczne mocowanie siedziska;
 widoczne mocowanie oparcia;
 drewniany stelaż</t>
-  </si>
-  <si>
-    <t>Typ 300-177</t>
-  </si>
-  <si>
-    <t>Bunny; Zajączek</t>
-  </si>
-  <si>
-    <t>Józef Chierowski (Do weryfikacji – atrybucja często powtarzana w źródłach kolekcjonerskich, słabo potwierdzona w publikacjach naukowych)</t>
-  </si>
-  <si>
-    <t>początek lat 60. XX w.</t>
-  </si>
-  <si>
-    <t>Świebodzińskie Fabryki Mebli; Gościcińskie Fabryki Mebli</t>
-  </si>
-  <si>
-    <t>trójkątne podłokietniki; lekka drewniana konstrukcja; kompaktowe wymiary; szeroko rozstawione nogi; tapicerowane siedzisko i oparcie; forma nawiązująca do modelu 366</t>
-  </si>
-  <si>
-    <t>bukowy stelaż; otwarta konstrukcja boczna; tapicerowane moduły siedziska i oparcia; drewniane podłokietniki zintegrowane z ramą; konstrukcja szkieletowa</t>
-  </si>
-  <si>
-    <t>typ 366; typ 300-190 Lisek; BW-14</t>
-  </si>
-  <si>
-    <t>typ 366; grupa lekkich foteli drewnianych PRL z lat 60.; modele produkowane przez Świebodzińskie i Gościcińskie Fabryki Mebli (Do weryfikacji)</t>
-  </si>
-  <si>
-    <t>Meblostan – Fotel Bunny typ 300-177; Nowohuckie Renowacje – Fotel typ 300-177 Zajączek; Patyna.pl – Fotel Bunny typ 300-177; Tkaniny-Meblowe.pl – Fotele z PRL-u; materiały kolekcjonerskie rynku vintage</t>
-  </si>
-  <si>
-    <t>trójkątne podłokietniki przypominające uszy zająca; otwarta drewniana rama boczna; szeroko rozstawione nogi; podłokietniki połączone z przednimi nogami; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; duży prześwit pod siedziskiem; smukła lekka bryła; odsłonięty drewniany stelaż; skośne tylne nogi; geometryczny profil boczny; kompaktowe proporcje</t>
-  </si>
-  <si>
-    <t>Fotel Ewa; Muszelka Ewa</t>
-  </si>
-  <si>
-    <t>Do weryfikacji</t>
-  </si>
-  <si>
-    <t>Strzeleckie Zakłady Przemysłu Terenowego w Strzelcach Opolskich</t>
-  </si>
-  <si>
-    <t>Fotel posiada muszelkowy, kubełkowy korpus tworzący jednolitą tapicerowaną bryłę. Szerokie, półkoliste oparcie płynnie przechodzi w siedzisko, nadając bryle profil przypominający muszlę. Korpus osadzony jest na odsłoniętym stalowym stelażu wspartym na czterech smukłych metalowych nogach. Fotel nie posiada drewnianych podłokietników, a wysoka podstawa nadaje konstrukcji lekką formę.</t>
-  </si>
-  <si>
-    <t>Konstrukcję nośną stanowi rama wykonana ze spawanych prętów stalowych. Rama wsparta jest na czterech stalowych, wykręcanych nogach zakończonych ruchomymi stopkami. W modelu Koeln 1 zastosowano pojedynczą stalową nogę obrotową.</t>
-  </si>
-  <si>
-    <t>fotel Köln 1; fotel Muszelka; fotele klubowe na stelażu stalowym z lat 60.</t>
-  </si>
-  <si>
-    <t>Köln 1 (NRD); fotele muszelkowe PRL; metalowe fotele klubowe lat 60.</t>
-  </si>
-  <si>
-    <t>Meblostan – Para foteli tapicerowanych EWA; Odnowa Mebli – Fotel Ewa; Patyna.pl – Komplet foteli typ Ewa; materiały kolekcjonerskie rynku vintage</t>
   </si>
   <si>
     <t>muszelkowy korpus;
@@ -571,458 +1135,6 @@
 otwarta konstrukcja;
 obszerne siedzisko;
 obszerne oparcie</t>
-  </si>
-  <si>
-    <t>Typ 300-123</t>
-  </si>
-  <si>
-    <t>Puchała; wersja damska (Do weryfikacji)</t>
-  </si>
-  <si>
-    <t>Mieczysław Puchała</t>
-  </si>
-  <si>
-    <t>1956 (według części źródeł); początek lat 60. XX w.</t>
-  </si>
-  <si>
-    <t>lekka smukła sylwetka; gięte drewniane podłokietniki; wysokie oparcie; wąskie proporcje; odsłonięta drewniana konstrukcja; toczone nogi; modernistyczna forma inspirowana wzornictwem skandynawskim</t>
-  </si>
-  <si>
-    <t>drewniany stelaż bukowy; otwarta konstrukcja boczna; tapicerowane siedzisko; tapicerowane oparcie; pasy tapicerskie; konstrukcja szkieletowa</t>
-  </si>
-  <si>
-    <t>typ 300-137; typ 300-190 Lisek; typ 366</t>
-  </si>
-  <si>
-    <t>typ 300-137 wersja męska; rodzina foteli projektu Mieczysława Puchały; lekkie fotele drewniane PRL lat 50. i 60</t>
-  </si>
-  <si>
-    <t>Nowohuckie Renowacje – Fotel typ 300-123 Puchała; Szajba Sklep – Fotel klubowy typ 300-123 proj. M. Puchała; LookInside – Fotel typ 300-123 Puchała; Pakamera – Fotel typ 300-123 M. Puchała; Meblostan – Fotel Puchały typ 300-123</t>
-  </si>
-  <si>
-    <t>gięte drewniane podłokietniki; smukłe wysokie oparcie; wąskie proporcje korpusu; otwarta drewniana rama boczna; toczone nogi zwężające się ku dołowi; widoczny prześwit pod siedziskiem; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; lekka dynamiczna bryła; cienkie elementy konstrukcyjne; profil boczny z łukowato wygiętym podłokietnikiem; minimalistyczna forma lat 50./60.</t>
-  </si>
-  <si>
-    <t>RM58</t>
-  </si>
-  <si>
-    <t>Muszelka; RM58</t>
-  </si>
-  <si>
-    <t>Roman Modzelewski</t>
-  </si>
-  <si>
-    <t>Zakłady Mebli Artystycznych w Łodzi (prototyp); Vzór Sp. z o.o. (reedycja od 2012 r.)</t>
-  </si>
-  <si>
-    <t>organiczna muszelkowa forma; jednolita zamknięta bryła; głębokie kubełkowe siedzisko; szerokie wywinięte boki; opływowy futurystyczny kształt; brak klasycznych podłokietników; rzeźbiarska sylwetka</t>
-  </si>
-  <si>
-    <t>jednoczęściowy korpus z laminatu poliestrowo-szklanego; tapicerowana wkładka siedziska; cztery smukłe nogi; technologia laminatu wyprzedzająca epokę w Polsce; konstrukcja skorupowa</t>
-  </si>
-  <si>
-    <t>fotel Ewa; fotele muszelkowe produkcji NRD; zachodnie fotele fiberglass lat 50.; projekty Eero Saarinena</t>
-  </si>
-  <si>
-    <t>prototypowe meble z laminatu Romana Modzelewskiego; współczesne reedycje RM58; warianty kolorystyczne RM58 Classic</t>
-  </si>
-  <si>
-    <t>Muzeum Narodowe we Wrocławiu; Vzór – dokumentacja reedycji RM58; Instytut Wzornictwa Przemysłowego; publikacje o twórczości Romana Modzelewskiego; Culture.pl</t>
-  </si>
-  <si>
-    <t>jednoczęściowa muszelkowa skorupa; organiczna opływowa bryła; głębokie kubełkowe siedzisko; szerokie wywinięte boki; zaokrąglone wysokie oparcie; brak oddzielnych podłokietników; korpus przypominający muszlę; zamknięta forma boczna; cztery cienkie nogi; futurystyczna sylwetka lat 50.; brak widocznej drewnianej konstrukcji; płynne przejścia między siedziskiem i oparciem; asymetrycznie zaokrąglone krawędzie; korpus wykonany jako pojedyncza skorupa</t>
-  </si>
-  <si>
-    <t>B-2020</t>
-  </si>
-  <si>
-    <t>Tulipan</t>
-  </si>
-  <si>
-    <t>Teresa Kruszewska</t>
-  </si>
-  <si>
-    <t>1973 (prototyp)</t>
-  </si>
-  <si>
-    <t>FAMEG Radomsko (reedycja współczesna)</t>
-  </si>
-  <si>
-    <t>organiczna forma inspirowana kielichem kwiatu; szerokie kubełkowe siedzisko; płynne przejście między siedziskiem i oparciem; miękkie zaokrąglone linie; wyraźnie rozchylone boki; rzeźbiarska bryła</t>
-  </si>
-  <si>
-    <t>korpus ze sklejki formowanej; tapicerowana skorupa; drewniana podstawa; konstrukcja monolityczna; technologia giętej sklejki</t>
-  </si>
-  <si>
-    <t>RM58; fotele muszelkowe PRL; fotele skandynawskie o organicznej formie</t>
-  </si>
-  <si>
-    <t>projekty Teresy Kruszewskiej; meble ze sklejki formowanej; współczesna kolekcja Tulipan FAMEG</t>
-  </si>
-  <si>
-    <t>FAMEG – Fotel Tulipan B-2020; dokumentacja reedycji FAMEG; opracowania dotyczące twórczości Teresy Kruszewskiej</t>
-  </si>
-  <si>
-    <t>kubełkowe siedzisko; forma przypominająca kielich tulipana; szeroko rozchylone boki; jednolita tapicerowana skorupa; zaokrąglone wysokie oparcie; płynne przejście między siedziskiem i oparciem; organiczna bryła; brak widocznej drewnianej ramy bocznej; miękkie obłe krawędzie; rzeźbiarska forma; kompaktowa podstawa; sylwetka kwiatu tulipana</t>
-  </si>
-  <si>
-    <t>Typ 300-201</t>
-  </si>
-  <si>
-    <t>Śnieżnik; Śnieżka (Do weryfikacji – obie nazwy występują w obiegu kolekcjonerskim, częściej spotykana jest nazwa Śnieżnik)</t>
-  </si>
-  <si>
-    <t>1973 (najwcześniejsza potwierdzona wzmianka źródłowa)</t>
-  </si>
-  <si>
-    <t>Bystrzycka Fabryka Mebli w Bystrzycy Kłodzkiej</t>
-  </si>
-  <si>
-    <t>lekka konstrukcja drewniana; forma inspirowana modelem Lisek 300-190; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; otwarta rama boczna; charakterystyczne nogi częściowo graniaste i częściowo zaokrąglone; smukłe proporcje</t>
-  </si>
-  <si>
-    <t>drewniany stelaż brzozowy lub bukowy; otwarta konstrukcja boczna; tapicerowane siedzisko; tapicerowane oparcie; pasy tapicerskie; konstrukcja szkieletowa</t>
-  </si>
-  <si>
-    <t>typ 300-190 Lisek; Śnieżka; BW-14 typ 300-199; B-7727</t>
-  </si>
-  <si>
-    <t>typ 300-190 Lisek; Śnieżka; BW-14 typ 300-199; BW-20 typ 300-193; B-7727</t>
-  </si>
-  <si>
-    <t>Meblostan – Fotel Śnieżnik typ 300-201; Nowohuckie Renowacje – Fotele PRL; Pakamera – Fotel Śnieżnik typ 300-201; Audiovintage Store – Fotel klubowy Śnieżnik 300-201</t>
-  </si>
-  <si>
-    <t>otwarta drewniana rama boczna; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; smukła lekka bryła; duży prześwit pod siedziskiem; drewniane podłokietniki zintegrowane z ramą; nogi graniaste od góry; nogi zaokrąglone w dolnej części; skośne tylne nogi; widoczne drewniane elementy konstrukcyjne; forma zbliżona do modelu Lisek; geometryczny profil boczny
-Źródła potwierdzają produkcję w Bystrzyckiej Fabryce Mebli oraz silne pokrewieństwo konstrukcyjne z modelem 300-190 „Lisek”, natomiast projektant pozostaje niepotwierdzony.</t>
-  </si>
-  <si>
-    <t>GFM-57</t>
-  </si>
-  <si>
-    <t>Skoczek</t>
-  </si>
-  <si>
-    <t>Juliusz Kędziorek</t>
-  </si>
-  <si>
-    <t>Krzesło</t>
-  </si>
-  <si>
-    <t>Gościcińska Fabryka Mebli; Zamojskie Fabryki Mebli (produkcja seryjna jako typ 200-203)</t>
-  </si>
-  <si>
-    <t>łukowate podłokietniki przypominające profil skoczni narciarskiej; elipsoidalne oparcie; lekka ażurowa konstrukcja; zwężające się ku dołowi nogi; tapicerowane siedzisko; smukła sylwetka; organiczna linia boczna</t>
-  </si>
-  <si>
-    <t>drewniany stelaż; otwarta konstrukcja boczna; tapicerowane siedzisko; gięte elementy drewniane; konstrukcja przeznaczona do produkcji seryjnej</t>
-  </si>
-  <si>
-    <t>typ 200-190 Rajmunda Hałasa; krzesła Aga; krzesła patyczaki lat 60.; lekkie krzesła tapicerowane PRL</t>
-  </si>
-  <si>
-    <t>typ 200-203; GFM-107; projekty Juliusza Kędziorka dla Gościcińskiej Fabryki Mebli</t>
-  </si>
-  <si>
-    <t>Magazif – Krzesło Skoczek; Ikony Designu PL – Krzesło GFM-57 Skoczek; Meblostan – Krzesło Skoczek; Sosenko Home Decor – Krzesło Skoczek; Allegro Artykuł – Krzesło kilka słów o najtrudniejszym meblu</t>
-  </si>
-  <si>
-    <t>łukowate podłokietniki przypominające skocznię narciarską; elipsoidalne oparcie; otwarta drewniana rama boczna; smukłe zwężające się nogi; tapicerowane siedzisko; duży prześwit pod siedziskiem; płynna linia podłokietnika przechodząca w nogę; lekka ażurowa konstrukcja; organiczny profil boczny; oparcie w kształcie pionowej elipsy; cienkie elementy drewniane; dynamiczna sylwetka inspirowana skokami narciarskimi
-Źródła potwierdzają, że model został zaprojektowany przez Juliusza Kędziorka w Gościcińskiej Fabryce Mebli w 1965 r., otrzymał nagrodę „Dobre–Ładne–Poszukiwane” i został skierowany do produkcji seryjnej jako typ 200-203</t>
-  </si>
-  <si>
-    <t>Typ 200-125 VAR</t>
-  </si>
-  <si>
-    <t>Aga</t>
-  </si>
-  <si>
-    <t>ok. 1972–1975 (w źródłach występują rozbieżności dotyczące dokładnego roku projektu)</t>
-  </si>
-  <si>
-    <t>Wielkopolskie Fabryki Mebli; produkcja seryjna PRL (pozostali producenci wymagają weryfikacji)</t>
-  </si>
-  <si>
-    <t>wysokie tapicerowane oparcie; trapezowy układ nóg; miękkie tapicerowane siedzisko; smukła skandynawska forma; zwężająca się ku górze bryła; lekkie proporcje; drewniana konstrukcja eksponowana po bokach</t>
-  </si>
-  <si>
-    <t>drewniany stelaż bukowy; tapicerowane siedzisko; tapicerowane oparcie; sprężyny siedziska; cztery drewniane nogi; konstrukcja przeznaczona do intensywnego użytkowania klubowego</t>
-  </si>
-  <si>
-    <t>typ 200-190 Rajmunda Hałasa; GFM-57 Skoczek; lekkie krzesła klubowe PRL lat 70.</t>
-  </si>
-  <si>
-    <t>fotel 366; meble klubowe Józefa Chierowskiego; reedycja 200-125 VAR realizowana przez 366 Concept</t>
-  </si>
-  <si>
-    <t>Elle Decoration Polska – Krzesło VAR AGA projektu Józefa Chierowskiego; Nowohuckie Renowacje – Krzesło Aga typ 200-125; Patyna.pl – Krzesła AGA typu 200-125 VAR; Linie Studio – 200-125 VAR; Meblościanka – 200-125 VAR</t>
-  </si>
-  <si>
-    <t>wysokie tapicerowane oparcie; trapezowy układ nóg; szerokie miękkie siedzisko; brak podłokietników; drewniane nogi rozszerzające się ku dołowi; zwężająca się ku górze sylwetka; lekka skandynawska forma; prostokątne oparcie z zaokrąglonymi krawędziami; widoczne drewniane elementy boczne; smukłe proporcje; geometryczna bryła; profil boczny z pochylonym oparciem</t>
-  </si>
-  <si>
-    <t>Typ 200-190</t>
-  </si>
-  <si>
-    <t>Hałas; Grzybek</t>
-  </si>
-  <si>
-    <t>Rajmund Teofil Hałas</t>
-  </si>
-  <si>
-    <t>lata 60. XX w.; dokładny rok projektu – Do weryfikacji</t>
-  </si>
-  <si>
-    <t>Zakłady Mebli w Gostyniu (Do weryfikacji); produkcja seryjna w kilku zakładach meblarskich PRL – Do weryfikacji</t>
-  </si>
-  <si>
-    <t>okrągła forma oparcia przypominająca kapelusz grzyba; tapicerowane oparcie i siedzisko; smukłe zwężające się nogi; lekka konstrukcja; wyraźnie wyodrębnione oparcie nad siedziskiem; proporcje inspirowane wzornictwem skandynawskim; minimalistyczna sylwetka</t>
-  </si>
-  <si>
-    <t>drewniany stelaż; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; mocowane oddzielnie siedzisko i oparcie; nogi zwężające się ku dołowi</t>
-  </si>
-  <si>
-    <t>Aga 200-125; Skoczek GFM-57; krzesła skandynawskie lat 60.; lekkie krzesła tapicerowane PRL</t>
-  </si>
-  <si>
-    <t>projekty Rajmunda Teofila Hałasa; krzesła tapicerowane PRL lat 60.; warianty produkcyjne typu 200-190</t>
-  </si>
-  <si>
-    <t>Odnawialnia – Wiem co odnawiam | krzesło Hałasa typ 200-190; Patyna.pl – Krzesła typ 200-190 Rajmund Teofil Hałas; Meblostan – Komplet krzeseł typ 200-190; Daniel Stoiński Redesign – Przewodnik po renowacji krzesła 200-190; Homebook – Krzesło Hałasa typ 200-190</t>
-  </si>
-  <si>
-    <t>okrągłe oparcie przypominające grzybek; oparcie szersze od wspornika; tapicerowane okrągłe oparcie; tapicerowane siedzisko; smukłe nogi zwężające się ku dołowi; brak podłokietników; lekka skandynawska forma; duży prześwit pod siedziskiem; cienki drewniany stelaż; wyraźne oddzielenie oparcia od siedziska; geometryczna bryła; profil boczny z lekko odchylonym oparciem</t>
-  </si>
-  <si>
-    <t>B-6028</t>
-  </si>
-  <si>
-    <t>Barbara Fenrych-Węcławska (Do weryfikacji); Józef Chierowski (Do weryfikacji – atrybucja pojawiająca się wyłącznie w źródłach kolekcjonerskich)</t>
-  </si>
-  <si>
-    <t>lata 60. XX w.</t>
-  </si>
-  <si>
-    <t>Fabryka Mebli Giętych w Radomsku; FAMEG Radomsko; Radomszczańska Fabryka Mebli Giętych</t>
-  </si>
-  <si>
-    <t>wysokie profilowane oparcie; szerokie drewniane podłokietniki; gięte elementy bukowe; głębokie siedzisko; lekka otwarta konstrukcja boczna; elegancka smukła sylwetka; forma łącząca cechy fotela klubowego i wypoczynkowego</t>
-  </si>
-  <si>
-    <t>stelaż z giętego drewna bukowego; otwarta konstrukcja ramowa; tapicerowane siedzisko; tapicerowane oparcie; drewniane podłokietniki zintegrowane z ramą; konstrukcja szkieletowa</t>
-  </si>
-  <si>
-    <t>typ 300-123 Puchała; typ 300-177 Zajączek; B-7727; typ 366</t>
-  </si>
-  <si>
-    <t>fotele Radomsko z giętego drewna; projekty Barbary Fenrych-Węcławskiej (Do weryfikacji); lekkie fotele klubowe PRL lat 60.</t>
-  </si>
-  <si>
-    <t>MidMod – Fotel B6028 FAMEG Radomsko Polska lata 60; Oldsen Design – Fotel B6028 prod. FAMEG Radomsko; Nowohuckie Renowacje – Fotel PRL B-6028 z lat 60-tych; Fotelowo Facebook – fotel projektu Barbary Fenrych-Węcławskiej; Instagram Renowacja Mebli PRL – B6028 lata produkcji 1960</t>
-  </si>
-  <si>
-    <t>wysokie prostokątne oparcie; szerokie drewniane podłokietniki; gięte boczne elementy z drewna; otwarta rama boczna; głębokie siedzisko; masywniejsza bryła niż typ 366; bukowy stelaż; duży prześwit pod siedziskiem; profilowane podłokietniki; smukłe nogi zintegrowane z ramą; tapicerowane oparcie i siedzisko; geometryczny profil boczny</t>
-  </si>
-  <si>
-    <t>A. Dutka</t>
-  </si>
-  <si>
-    <t>1966–1968</t>
-  </si>
-  <si>
-    <t>Zakłady Mebli Giętych w Radomsku; Gołuchowskie Fabryki Mebli</t>
-  </si>
-  <si>
-    <t>duże gabaryty; szerokie głębokie siedzisko; masywne drewniane podłokietniki; geometryczna forma boczna; lekko pochylone oparcie; otwarta konstrukcja ramowa; modernistyczna sylwetka eksportowa</t>
-  </si>
-  <si>
-    <t>stelaż z drewna bukowego; sprężyny lejowe w siedzisku; tapicerowane siedzisko i oparcie; otwarta konstrukcja boczna; drewniane podłokietniki zintegrowane z ramą; konstrukcja rozbieralna skręcana śrubami</t>
-  </si>
-  <si>
-    <t>B-6028; GFM-64; typ 300-190 Lisek; B-7727</t>
-  </si>
-  <si>
-    <t>fotele eksportowe Radomsko lat 60.; modele Zakładów Mebli Giętych w Radomsku; konstrukcje projektowane przez A. Dutkę (Do weryfikacji)</t>
-  </si>
-  <si>
-    <t>Meblostan – Para foteli B-310 VAR; Pufa Design – Oryginalny fotel B-310 VAR; Yestersen – Fotel B-310 VAR Polska lata 70.; Reko-Czyny – Fotel B-310 VAR metamorfoza; archiwalne ogłoszenia kolekcjonerskie B-310 VAR</t>
-  </si>
-  <si>
-    <t>masywne drewniane podłokietniki; szerokie głębokie siedzisko; wysunięte przednie podłokietniki; otwarta drewniana rama boczna; prostokątne tapicerowane oparcie; grube proporcje siedziska; lekko pochylone oparcie; duży prześwit pod siedziskiem; widoczne śruby montażowe w ramie; geometryczny profil boczny; szeroki rozstaw nóg; cięższa bryła niż typ 366; bukowy stelaż; modernistyczna forma eksportowa</t>
-  </si>
-  <si>
-    <t>GFM-22 (typ 200/128)</t>
-  </si>
-  <si>
-    <t>ok. 1960</t>
-  </si>
-  <si>
-    <t>Gościcińska Fabryka Mebli (GFM)</t>
-  </si>
-  <si>
-    <t>nerkowate oparcie; lekka ażurowa konstrukcja; smukłe zwężające się nogi; gięta drewniana rama; tapicerowane siedzisko; tapicerowane oparcie; wyraźnie rozstawione tylne nogi</t>
-  </si>
-  <si>
-    <t>drewniany stelaż; gięte elementy z litego drewna; tapicerowane siedzisko; tapicerowane oparcie ze sklejki giętej; konstrukcja szkieletowa przeznaczona do produkcji seryjnej</t>
-  </si>
-  <si>
-    <t>GFM-57 Skoczek; typ 200-190 Rajmunda Hałasa; Aga 200-125; krzesła skandynawskie z lat 60.</t>
-  </si>
-  <si>
-    <t>typ 200/128; projekty Juliusza Kędziorka dla Gościcińskiej Fabryki Mebli; GFM-57; GFM-87</t>
-  </si>
-  <si>
-    <t>Pamono – Mid-Century GFM-22 Chairs by Juliusz Kędziorek; Vinterior – GFM-22 model 200/128; Selency – Iconic GFM-22 Chair by Juliusz Kędziorek; Instagram Zostań z Vintage – Krzesło GFM-22 typ 200/128</t>
-  </si>
-  <si>
-    <t>nerkowate tapicerowane oparcie; oparcie szersze od wspornika; smukłe zwężające się nogi; lekka ażurowa konstrukcja; gięta drewniana rama; prostokątne tapicerowane siedzisko; duży prześwit pod siedziskiem; cienkie elementy konstrukcyjne; szeroko rozstawione tylne nogi; profil boczny z delikatnie pochylonym oparciem; organiczny kształt oparcia; minimalistyczna sylwetka lat 60.</t>
-  </si>
-  <si>
-    <t>Typ 1020</t>
-  </si>
-  <si>
-    <t>Muszelka</t>
-  </si>
-  <si>
-    <t>Wiesław Leśniewski; Stanisław Lejkowski</t>
-  </si>
-  <si>
-    <t>Słupskie Fabryki Mebli</t>
-  </si>
-  <si>
-    <t>muszelkowe profilowane oparcie; jednolita tapicerowana skorupa; zaokrąglona górna krawędź oparcia; smukłe stożkowe nogi; lekka modernistyczna forma; brak podłokietników; organiczna sylwetka</t>
-  </si>
-  <si>
-    <t>profilowana skorupa ze sklejki; tapicerowana skorupa; drewniany stelaż; cztery drewniane nogi; konstrukcja szkieletowa; połączenie sklejki i drewna litego</t>
-  </si>
-  <si>
-    <t>RM58; krzesła muszelkowe produkcji NRD; krzesła skandynawskie lat 60.; fotel Ewa</t>
-  </si>
-  <si>
-    <t>krzesła muszelkowe Słupskich Fabryk Mebli; projekty Wiesława Leśniewskiego i Stanisława Lejkowskiego; meble ze sklejki profilowanej produkowane przez SFM</t>
-  </si>
-  <si>
-    <t>Archiwalne katalogi Słupskich Fabryk Mebli; opracowania kolekcjonerskie dotyczące wzornictwa SFM; materiały renowatorów specjalizujących się w meblach PRL; publikacje poświęcone projektom Wiesława Leśniewskiego i Stanisława Lejkowskiego</t>
-  </si>
-  <si>
-    <t>muszelkowe profilowane oparcie; jednolita tapicerowana skorupa; zaokrąglona górna krawędź oparcia; płynne przejście oparcia w siedzisko; brak podłokietników; cztery smukłe stożkowe drewniane nogi; lekka organiczna bryła; profilowana skorupa ze sklejki; niewielki prześwit pod siedziskiem; forma inspirowana muszlą</t>
-  </si>
-  <si>
-    <t>Bumerang</t>
-  </si>
-  <si>
-    <t>Ryszard Kulm</t>
-  </si>
-  <si>
-    <t>przełom lat 50. i 60. XX w.; produkcja seryjna od początku lat 60</t>
-  </si>
-  <si>
-    <t>Gościcińska Fabryka Mebli</t>
-  </si>
-  <si>
-    <t>charakterystyczne łukowato wygięte przednie nogi przypominające bumerang; lekka ażurowa konstrukcja; tapicerowane siedzisko; tapicerowane oparcie; smukła sylwetka; zwężające się ku dołowi nogi; modernistyczna forma inspirowana skandynawskim wzornictwem</t>
-  </si>
-  <si>
-    <t>drewniany stelaż bukowy; gięte elementy boczne; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; połączenia skręcane i klejone</t>
-  </si>
-  <si>
-    <t>GFM-22; typ 200-190 Rajmunda Hałasa; GFM-57 Skoczek; krzesła skandynawskie lat 60</t>
-  </si>
-  <si>
-    <t>krzesła Gościcińskiej Fabryki Mebli; wariant 299XB (Do weryfikacji); rodzina krzeseł Bumerang</t>
-  </si>
-  <si>
-    <t>Meblostan – Komplet 4 krzeseł Bumerang typ 299; Skarby PRL – Krzesło tapicerowane Bumerang typ 299; Patyna – Komplet krzeseł typ 299 Bumerang; Deccoria – 10 słynnych mebli z PRL; Stary Fotel – Krzesła Bumerang metamorfoza</t>
-  </si>
-  <si>
-    <t>łukowato wygięte przednie nogi w kształcie bumerangu; gięte boczne elementy drewniane; tapicerowane prostokątne siedzisko; tapicerowane oparcie; smukła lekka bryła; cienki drewniany stelaż; zwężające się ku dołowi nogi; wyraźny prześwit pod siedziskiem; organiczny profil boczny; lekko odchylone oparcie; minimalistyczna forma lat 60.; charakterystyczna sylwetka bumerangu</t>
-  </si>
-  <si>
-    <t>Typ 300-227</t>
-  </si>
-  <si>
-    <t>Celia</t>
-  </si>
-  <si>
-    <t>ok. 1965; produkcja na przełomie lat 60. i 70. XX w.</t>
-  </si>
-  <si>
-    <t>Zamojskie Fabryki Mebli</t>
-  </si>
-  <si>
-    <t>brak podłokietników; toczone drewniane nogi umieszczone po bokach części tapicerowanej; trapezowe siedzisko; proste tapicerowane oparcie; lekka minimalistyczna forma; kompaktowe wymiary; stylistyka skandynawskiego modernizmu</t>
-  </si>
-  <si>
-    <t>drewniany stelaż; toczone nogi; tapicerowane siedzisko; tapicerowane oparcie; otwarta konstrukcja bez podłokietników; konstrukcja szkieletowa przeznaczona do produkcji seryjnej</t>
-  </si>
-  <si>
-    <t>typ 300-190 Lisek; typ 366; GFM-64; lekkie fotele klubowe PRL bez podłokietników</t>
-  </si>
-  <si>
-    <t>fotele Zamojskich Fabryk Mebli z lat 60. i 70.; meble klubowe produkowane w Zamościu; modele o minimalistycznej konstrukcji bez podłokietników</t>
-  </si>
-  <si>
-    <t>Meblostan – Fotel CELIA typ 300-227; Patyna – Fotel CELIA typ 300-227 PRL; Szajba Sklep – Fotel Celia typ 300-227; materiały kolekcjonerskie dotyczące Zamojskich Fabryk Mebli</t>
-  </si>
-  <si>
-    <t>brak podłokietników; toczone drewniane nogi umieszczone po bokach korpusu; trapezowe tapicerowane siedzisko; prostokątne tapicerowane oparcie; lekka minimalistyczna bryła; duży prześwit pod siedziskiem; cienki drewniany stelaż; zwężające się ku dołowi nogi; odsłonięte drewniane elementy boczne; kompaktowe proporcje; geometryczny profil boczny; forma inspirowana skandynawskim modernizmem</t>
-  </si>
-  <si>
-    <t>Typ 300-139</t>
-  </si>
-  <si>
-    <t>Stefan</t>
-  </si>
-  <si>
-    <t>Swarzędzka Fabryka Mebli</t>
-  </si>
-  <si>
-    <t>szerokie drewniane podłokietniki o łagodnym łuku; otwarta konstrukcja boczna; luźne tapicerowane poduchy siedziska i oparcia; rozłożysta bryła; lekka skandynawska stylistyka; nisko osadzone siedzisko; masywny drewniany stelaż</t>
-  </si>
-  <si>
-    <t>stelaż z litego drewna bukowego; otwarta rama boczna; osobna poduszka siedziska; osobna poduszka oparcia; pasy tapicerskie; konstrukcja szkieletowa skręcana</t>
-  </si>
-  <si>
-    <t>typ 300-123 Puchała; typ 366; duńskie fotele Kandidaten projektu Ib Kofod-Larsena; fotele skandynawskie lat 60</t>
-  </si>
-  <si>
-    <t>sofa Stefan; zestawy wypoczynkowe Swarzędzkiej Fabryki Mebli; meble eksportowe Swarzędzkiej Fabryki Mebli z lat 60.</t>
-  </si>
-  <si>
-    <t>„Meble w produkcji 1962” – Zjednoczenie Przemysłu Meblarskiego; „Meble do małych mieszkań. Informator”, Wydawnictwo Katalogów i Cenników 1966; Laminerva – „Ikony polskiego designu: Fotel Stefan typ 300-139”; Meblostan – Para foteli Stefan typ 300-139; Patyna – Para foteli Stefan typ 300-139</t>
-  </si>
-  <si>
-    <t>szerokie wyprofilowane drewniane podłokietniki; otwarta drewniana rama boczna; luźna poduszka siedziska; luźna poduszka oparcia; nisko osadzone głębokie siedzisko; prostokątne grube poduchy; lekko odchylone oparcie; masywny bukowy stelaż; duży prześwit pod siedziskiem; szeroki rozstaw przednich nóg; profil boczny inspirowany wzornictwem skandynawskim; rozłożysta bryła eksportowa</t>
-  </si>
-  <si>
-    <t>B-3300</t>
-  </si>
-  <si>
-    <t>ok. 1969; produkcja w końcu lat 60. i na początku lat 70. XX w</t>
-  </si>
-  <si>
-    <t>Zakład Mebli Giętych w Radomsku; Fabryki Mebli Radomsko (późniejsze nazewnictwo zakładu)</t>
-  </si>
-  <si>
-    <t>gięte drewniane podłokietniki; szerokie tapicerowane siedzisko; prostokątne tapicerowane oparcie; otwarta konstrukcja boczna; gięty bukowy stelaż; nisko osadzona bryła; elegancka modernistyczna forma</t>
-  </si>
-  <si>
-    <t>stelaż z giętego drewna bukowego; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; elementy gięte wykonane w technologii Thoneta; konstrukcja skręcana</t>
-  </si>
-  <si>
-    <t>B-310 VAR; B-6028; GFM-64; typ 300-139 Stefan</t>
-  </si>
-  <si>
-    <t>fotele Zakładu Mebli Giętych w Radomsku; modele eksportowe Radomsko z lat 60. i 70.; rodzina foteli z giętego drewna bukowego</t>
-  </si>
-  <si>
-    <t>Patyna – Fotel B-3300 Zakład Mebli Giętych w Radomsku; Meblostan – Para foteli B-3300; archiwalne materiały Fabryk Mebli Radomsko; oferty kolekcjonerskie dokumentujące oryginalne oznaczenie modelu</t>
-  </si>
-  <si>
-    <t>gięte drewniane podłokietniki; otwarta drewniana rama boczna; szerokie prostokątne oparcie; szerokie głębokie siedzisko; bukowy gięty stelaż; duży prześwit pod siedziskiem; łagodnie wygięte boki; zwężające się ku dołowi nogi; lekko pochylone oparcie; masywniejsza bryła niż typ 366; widoczne elementy z giętego drewna; modernistyczna forma gabinetowa</t>
-  </si>
-  <si>
-    <t>Cechy AI</t>
   </si>
 </sst>
 </file>
@@ -4230,7 +4342,7 @@
         <v>92</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>103</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="381.75">
@@ -4238,7 +4350,7 @@
         <v>104</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>113</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="366">
@@ -4246,7 +4358,7 @@
         <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>123</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="91.5">
@@ -4262,7 +4374,7 @@
         <v>38</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>143</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="91.5">

--- a/data/furniture.xlsx
+++ b/data/furniture.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30305"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21A469CB-CEF7-437C-AD60-690DE7A566ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6638F3B0-DE5F-459E-85CC-69FC002880EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Benchmark" sheetId="1" r:id="rId1"/>
-    <sheet name="Katalog" sheetId="2" r:id="rId2"/>
+    <sheet name="Katalog" sheetId="2" r:id="rId1"/>
+    <sheet name="Benchmark" sheetId="1" r:id="rId2"/>
     <sheet name="AI_Features" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -36,246 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="298">
-  <si>
-    <t>Prompt 1</t>
-  </si>
-  <si>
-    <t>Analyze this object.
-Please provide:
-1. What type of object is it?
-2. What specific model or product do you think it might be?
-3. What visual characteristics support your conclusion?
-4. How confident are you (0-100%)?
-5. List up to 3 alternative identifications.</t>
-  </si>
-  <si>
-    <t>Prompt 2</t>
-  </si>
-  <si>
-    <t>This object comes from Polish PRL-era design (1945-1989).
-Identify the most likely object, designer or model.
-Provide confidence score and alternative matches.</t>
-  </si>
-  <si>
-    <t>Chat</t>
-  </si>
-  <si>
-    <t>Photo</t>
-  </si>
-  <si>
-    <t>Object</t>
-  </si>
-  <si>
-    <t>Top 1</t>
-  </si>
-  <si>
-    <t>Exact</t>
-  </si>
-  <si>
-    <t>Top3 contains</t>
-  </si>
-  <si>
-    <t>Model Family</t>
-  </si>
-  <si>
-    <t>Designer</t>
-  </si>
-  <si>
-    <t>Confidence</t>
-  </si>
-  <si>
-    <t>Error Type</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Leakage</t>
-  </si>
-  <si>
-    <t>Gemini</t>
-  </si>
-  <si>
-    <t>1,4,8</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Correct</t>
-  </si>
-  <si>
-    <t>GPT</t>
-  </si>
-  <si>
-    <t>Minor</t>
-  </si>
-  <si>
-    <t>2,3,10</t>
-  </si>
-  <si>
-    <t>lisek</t>
-  </si>
-  <si>
-    <t>B-7727</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>Incorrect</t>
-  </si>
-  <si>
-    <t>Major</t>
-  </si>
-  <si>
-    <t>1,5,6</t>
-  </si>
-  <si>
-    <t>B-310</t>
-  </si>
-  <si>
-    <t>7,9,10</t>
-  </si>
-  <si>
-    <t>300-177</t>
-  </si>
-  <si>
-    <t>300-190</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>1,2,6</t>
-  </si>
-  <si>
-    <t>Ewa</t>
-  </si>
-  <si>
-    <t>Navrátil Shell Chair</t>
-  </si>
-  <si>
-    <t>DDR "Cocktailsessel"</t>
-  </si>
-  <si>
-    <t>2,3,7</t>
-  </si>
-  <si>
-    <t>300-123</t>
-  </si>
-  <si>
-    <t>Generic PRL armchair</t>
-  </si>
-  <si>
-    <t>1,6,9</t>
-  </si>
-  <si>
-    <t>rm58</t>
-  </si>
-  <si>
-    <t>Eames Fiberglass Armchair</t>
-  </si>
-  <si>
-    <t>1,2,3</t>
-  </si>
-  <si>
-    <t>b2020</t>
-  </si>
-  <si>
-    <t>Djinn Armchair</t>
-  </si>
-  <si>
-    <t>F588 Groovy Chair</t>
-  </si>
-  <si>
-    <t>300-201</t>
-  </si>
-  <si>
-    <t>halabala</t>
-  </si>
-  <si>
-    <t>skoczek</t>
-  </si>
-  <si>
-    <t>GFM</t>
-  </si>
-  <si>
-    <t>Aga 200 125</t>
-  </si>
-  <si>
-    <t>200-192</t>
-  </si>
-  <si>
-    <t>200-190</t>
-  </si>
-  <si>
-    <t>b6028</t>
-  </si>
-  <si>
-    <t>Type 366</t>
-  </si>
-  <si>
-    <t>B-310 VAR</t>
-  </si>
-  <si>
-    <t>Type 300-190</t>
-  </si>
-  <si>
-    <t>GFM-22</t>
-  </si>
-  <si>
-    <t>Typ 296 "Motylek"</t>
-  </si>
-  <si>
-    <t>Type 1020</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>typ 200-190</t>
-  </si>
-  <si>
-    <t>Typ 299</t>
-  </si>
-  <si>
-    <t>Type 200-190 "Aga"</t>
-  </si>
-  <si>
-    <t>Type 200-190</t>
-  </si>
-  <si>
-    <t>typ 300-227</t>
-  </si>
-  <si>
-    <t>Unidentified Danish-style lounge chair</t>
-  </si>
-  <si>
-    <t>300-139</t>
-  </si>
-  <si>
-    <t>Type 300-177</t>
-  </si>
-  <si>
-    <t>B3300</t>
-  </si>
-  <si>
-    <t>Contemporary Danish/Scandinavian-inspired dining armchair</t>
-  </si>
-  <si>
-    <t>`</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="319">
   <si>
     <t>ID</t>
   </si>
@@ -382,6 +143,9 @@
   </si>
   <si>
     <t>Lisek</t>
+  </si>
+  <si>
+    <t>300-190</t>
   </si>
   <si>
     <t>Henryk Lis</t>
@@ -431,6 +195,9 @@
 parallel armrests;
 rectangular geometry;
 exposed wooden structure;</t>
+  </si>
+  <si>
+    <t>B-7727</t>
   </si>
   <si>
     <t>Do weryfikacji; często błędnie określany jako „Lisek”</t>
@@ -496,6 +263,9 @@
     <t>Bunny; Zajączek</t>
   </si>
   <si>
+    <t>300-177</t>
+  </si>
+  <si>
     <t>Józef Chierowski (Do weryfikacji – atrybucja często powtarzana w źródłach kolekcjonerskich, słabo potwierdzona w publikacjach naukowych)</t>
   </si>
   <si>
@@ -505,10 +275,10 @@
     <t>Świebodzińskie Fabryki Mebli; Gościcińskie Fabryki Mebli</t>
   </si>
   <si>
-    <t>trójkątne podłokietniki; lekka drewniana konstrukcja; kompaktowe wymiary; szeroko rozstawione nogi; tapicerowane siedzisko i oparcie; forma nawiązująca do modelu 366</t>
-  </si>
-  <si>
-    <t>bukowy stelaż; otwarta konstrukcja boczna; tapicerowane moduły siedziska i oparcia; drewniane podłokietniki zintegrowane z ramą; konstrukcja szkieletowa</t>
+    <t>Fotel o zwartej, niskiej sylwetce z wyraźnie odchylonym prostokątnym oparciem o lekko zwężającej się ku górze formie i zaokrąglonych narożnikach. Siedzisko szerokie, prostokątne, grubo tapicerowane z zaokrągloną przednią krawędzią oraz lamówką biegnącą po obwodzie. Po bokach znajdują się szerokie, płaskie drewniane podłokietniki o kształcie zwężających się trapezów, podparte ukośnymi wspornikami tworzącymi charakterystyczną konstrukcję w kształcie litery „A”. Drewniany stelaż jest wyraźnie odsłonięty i obejmuje boczne belki, cztery smukłe, zwężające się nogi rozstawione pod dużym kątem oraz widoczne śruby mocujące w bocznych elementach konstrukcji. Tapicerka jest gładka, bez pikowania, z pojedynczymi guzikami widocznymi w niektórych egzemplarzach.</t>
+  </si>
+  <si>
+    <t>Konstrukcja oparta na otwartym drewnianym stelażu z bocznymi ramami tworzącymi układ w kształcie litery „A”. Przednie i tylne nogi połączone są ukośnymi elementami nośnymi stanowiącymi jednocześnie podpory podłokietników. Podłokietniki wykonane są jako oddzielne drewniane elementy mocowane do wsporników. Siedzisko i oparcie stanowią dwa oddzielne tapicerowane moduły osadzone pomiędzy bocznymi ramami. Dolna część konstrukcji posiada prostą belkę boczną podtrzymującą siedzisko. W bocznych elementach widoczne są metalowe śruby mocujące. Konstrukcja pozostawia otwartą przestrzeń pod podłokietnikami i pod siedziskiem, bez pełnych paneli bocznych.</t>
   </si>
   <si>
     <t>typ 366; typ 300-190 Lisek; BW-14</t>
@@ -520,7 +290,10 @@
     <t>Meblostan – Fotel Bunny typ 300-177; Nowohuckie Renowacje – Fotel typ 300-177 Zajączek; Patyna.pl – Fotel Bunny typ 300-177; Tkaniny-Meblowe.pl – Fotele z PRL-u; materiały kolekcjonerskie rynku vintage</t>
   </si>
   <si>
-    <t>trójkątne podłokietniki przypominające uszy zająca; otwarta drewniana rama boczna; szeroko rozstawione nogi; podłokietniki połączone z przednimi nogami; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; duży prześwit pod siedziskiem; smukła lekka bryła; odsłonięty drewniany stelaż; skośne tylne nogi; geometryczny profil boczny; kompaktowe proporcje</t>
+    <t>low wide silhouette; compact proportions; A-frame side construction; open wooden side frame; exposed wooden side rails; high upholstered backrest; tapered rectangular backrest; slightly reclined backrest; rounded backrest corners; thick upholstered backrest; deep upholstered seat; rectangular seat; thick seat cushion; rounded front seat edge; separate back cushion; separate seat cushion; flat wooden armrests; wide wooden armrests; trapezoidal armrests; angled armrest supports; splayed tapered legs; tapered wooden legs; front legs attached to side rails; rear legs integrated into backrest; visible side bolts; visible screw joints; solid wooden frame; smooth upholstery; piping; button tufting; open space under seat; minimal exposed wood; exposed wooden lower frame; straight side rails; geometric side profile; wide armrest tops; inclined rear legs; flush upholstered surfaces; open structural frame; triangular side geometry</t>
+  </si>
+  <si>
+    <t>Ewa</t>
   </si>
   <si>
     <t>Fotel Ewa; Muszelka Ewa</t>
@@ -547,35 +320,7 @@
     <t>Meblostan – Para foteli tapicerowanych EWA; Odnowa Mebli – Fotel Ewa; Patyna.pl – Komplet foteli typ Ewa; materiały kolekcjonerskie rynku vintage</t>
   </si>
   <si>
-    <t>rounded_shell;
-bucket_seat;
-integrated_shell;
-one_piece_body;
-continuous_backrest;
-continuous_armrests;
-curved_side_profile;
-organic_shape;
-wide_rounded_backrest;
-rounded_top_backrest;
-high_backrest;
-integrated_armrests;
-wrapped_armrests;
-upholstered_shell;
-soft_shell;
-floating_shell;
-metal_frame;
-steel_frame;
-four_metal_legs;
-slender_metal_legs;
-slightly_splayed_legs;
-black_metal_legs;
-metal_feet;
-round_feet_caps;
-open_space_under_shell;
-no_wooden_frame;
-no_wooden_armrests;
-lightweight_construction;
-minimalist_design;</t>
+    <t>organic bucket armchair; upholstered shell silhouette; integrated armrests and backrest; high rounded backrest; sloping armrest line; deep scooped seat; thick textured fabric; melange upholstery weave; splayed metal legs; tapered tubular legs; angled black legs; metal leg tips; silver pivoting glides; mid-century modern club chair; minimalist base construction; open space under seat; seamless upholstered body; comfortable lounge chair shape; rounded shell; bucket seat; integrated shell; one piece body; continuous backrest; continuous armrests; curved side profile; organic shape; wide rounded backrest; rounded top backrest; high backrest; integrated armrests; wrapped armrests; upholstered shell; soft shell; floating shell; metal frame; steel frame; four metal legs; slender metal legs; slightly splayed legs; black metal legs; metal feet; round feet caps; open space under shell; lightweight construction; minimalist design</t>
   </si>
   <si>
     <t>Typ 300-123</t>
@@ -584,16 +329,19 @@
     <t>Puchała; wersja damska (Do weryfikacji)</t>
   </si>
   <si>
+    <t>300-123</t>
+  </si>
+  <si>
     <t>Mieczysław Puchała</t>
   </si>
   <si>
     <t>1956 (według części źródeł); początek lat 60. XX w.</t>
   </si>
   <si>
-    <t>lekka smukła sylwetka; gięte drewniane podłokietniki; wysokie oparcie; wąskie proporcje; odsłonięta drewniana konstrukcja; toczone nogi; modernistyczna forma inspirowana wzornictwem skandynawskim</t>
-  </si>
-  <si>
-    <t>drewniany stelaż bukowy; otwarta konstrukcja boczna; tapicerowane siedzisko; tapicerowane oparcie; pasy tapicerskie; konstrukcja szkieletowa</t>
+    <t>Fotel o zwartej, lekko odchylonej do tyłu sylwetce z wysokim prostokątnym oparciem o delikatnie zwężającej się ku górze formie i zaokrąglonych narożnikach. Siedzisko szerokie, grubo tapicerowane, o prostokątnym zarysie z zaokrągloną przednią krawędzią oraz płynnym przejściem w oparcie. Po bokach znajdują się drewniane podłokietniki o łukowym przebiegu, podparte pojedynczym skośnym wspornikiem i zakończone prostokątnymi końcówkami. Drewniana konstrukcja obejmuje boczne belki, cztery smukłe, lekko zwężające się nogi oraz wyraźnie wyeksponowane elementy boczne. W miejscu połączenia podłokietników z oparciem widoczne są odsłonięte śruby mocujące. Tapicerka jest gładka, z lamówką poprowadzoną wzdłuż krawędzi oparcia i siedziska.</t>
+  </si>
+  <si>
+    <t>Konstrukcja oparta na drewnianym stelażu z odsłoniętymi bocznymi belkami nośnymi oraz czterema nogami zintegrowanymi z ramą. Siedzisko i oparcie tworzą oddzielne, tapicerowane elementy zamocowane do drewnianej konstrukcji. Drewniane podłokietniki połączone są z tylną częścią konstrukcji oraz podparte pojedynczym skośnym wspornikiem mocowanym do bocznej belki. Po bokach widoczne są metalowe śruby mocujące podłokietniki do konstrukcji oparcia. Konstrukcja ma otwartą przestrzeń pod podłokietnikami i pod siedziskiem, bez poprzeczek pomiędzy przednimi i tylnymi nogami. Tapicerka ma gładkie powierzchnie wykończone lamówką.</t>
   </si>
   <si>
     <t>typ 300-137; typ 300-190 Lisek; typ 366</t>
@@ -605,7 +353,7 @@
     <t>Nowohuckie Renowacje – Fotel typ 300-123 Puchała; Szajba Sklep – Fotel klubowy typ 300-123 proj. M. Puchała; LookInside – Fotel typ 300-123 Puchała; Pakamera – Fotel typ 300-123 M. Puchała; Meblostan – Fotel Puchały typ 300-123</t>
   </si>
   <si>
-    <t>gięte drewniane podłokietniki; smukłe wysokie oparcie; wąskie proporcje korpusu; otwarta drewniana rama boczna; toczone nogi zwężające się ku dołowi; widoczny prześwit pod siedziskiem; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; lekka dynamiczna bryła; cienkie elementy konstrukcyjne; profil boczny z łukowato wygiętym podłokietnikiem; minimalistyczna forma lat 50./60.</t>
+    <t>slim silhouette; compact proportions; open wooden side frame; exposed wooden side rails; high upholstered backrest; tapered rectangular backrest; slightly reclined backrest; rounded backrest corners; thick upholstered backrest; deep upholstered seat; rectangular seat; thick seat cushion; rounded front seat edge; integrated seat and backrest upholstery; curved wooden armrests; flat armrest tops; angled armrest supports; single armrest support; open armrest construction; splayed tapered legs; tapered wooden legs; front legs attached to side rails; rear legs integrated into backrest; visible side bolts; visible screw joints; solid wooden frame; smooth upholstery; piping; open space under seat; minimal exposed wood; separated seat and backrest; straight side rails; exposed wooden lower frame; boxed upholstery profile; flush upholstered surfaces; inclined rear legs; wide seating area; exposed armrest fasteners; continuous side profile</t>
   </si>
   <si>
     <t>RM58</t>
@@ -614,16 +362,19 @@
     <t>Muszelka; RM58</t>
   </si>
   <si>
+    <t>rm58</t>
+  </si>
+  <si>
     <t>Roman Modzelewski</t>
   </si>
   <si>
     <t>Zakłady Mebli Artystycznych w Łodzi (prototyp); Vzór Sp. z o.o. (reedycja od 2012 r.)</t>
   </si>
   <si>
-    <t>organiczna muszelkowa forma; jednolita zamknięta bryła; głębokie kubełkowe siedzisko; szerokie wywinięte boki; opływowy futurystyczny kształt; brak klasycznych podłokietników; rzeźbiarska sylwetka</t>
-  </si>
-  <si>
-    <t>jednoczęściowy korpus z laminatu poliestrowo-szklanego; tapicerowana wkładka siedziska; cztery smukłe nogi; technologia laminatu wyprzedzająca epokę w Polsce; konstrukcja skorupowa</t>
+    <t>Mebel wyróżnia się organiczną, monolityczną sylwetką o płynnych, obłych liniach i gładkiej, lśniącej powierzchni o wysokim połysku. Korpus ma formę jednolitej skorupy, w której oparcie, siedzisko oraz podłokietniki są zintegrowane w jedną, plastyczną całość przypominającą kształtem rozłupaną muszlę lub otwartą kapsułę. Górna krawędź oparcia oraz boki podłokietników mają falistą, płynnie wygiętą linię z zaokrąglonymi krawędziami zwijającymi się delikatnie na zewnątrz. Siedzisko jest głębokie, szerokie i nieckowato wyprofilowane, obniżające się ku tyłowi, co tworzy zwarty, ergonomiczny kubełek. Konstrukcja nie posiada żadnej tapicerki ani widocznych szwów, w całości eksponując gładkie tworzywo. Całość osadzona jest na czterech bardzo smukłych, metalowych nogach o okrągłym przekroju, które są szeroko rozstawione i ukośnie odchylone na zewnątrz, kontrastując z masywnym korpusem.</t>
+  </si>
+  <si>
+    <t>Konstrukcja nośna opiera się na jednolitej, sztywnej skorupie wykonanej z tworzywa sztucznego lub kompozytu, stanowiącej jednocześnie element siedziskowy i strukturalny. Całość opiera się na metalowym stelażu podnożowym, w którym cztery niezależne, cienkie rurki pełniące funkcję nóg są mocowane bezpośrednio do dolnej płaszczyzny korpusu. Nogi zwężają się delikatnie ku dołowi i są zakończone niewielkimi, ciemnymi stopkami ochronnymi. Konstrukcja jest całkowicie otwarta pod siedziskiem, bez dodatkowych łączników, carg czy widocznych śrub na bocznych powierzchniach mebla. Wszystkie punkty montażowe stelaża ukryte są pod spodem owalnego kubełka.</t>
   </si>
   <si>
     <t>fotel Ewa; fotele muszelkowe produkcji NRD; zachodnie fotele fiberglass lat 50.; projekty Eero Saarinena</t>
@@ -635,7 +386,7 @@
     <t>Muzeum Narodowe we Wrocławiu; Vzór – dokumentacja reedycji RM58; Instytut Wzornictwa Przemysłowego; publikacje o twórczości Romana Modzelewskiego; Culture.pl</t>
   </si>
   <si>
-    <t>jednoczęściowa muszelkowa skorupa; organiczna opływowa bryła; głębokie kubełkowe siedzisko; szerokie wywinięte boki; zaokrąglone wysokie oparcie; brak oddzielnych podłokietników; korpus przypominający muszlę; zamknięta forma boczna; cztery cienkie nogi; futurystyczna sylwetka lat 50.; brak widocznej drewnianej konstrukcji; płynne przejścia między siedziskiem i oparciem; asymetrycznie zaokrąglone krawędzie; korpus wykonany jako pojedyncza skorupa</t>
+    <t>organic shell silhouette; glossy composite body; high gloss finish; monolithic chair construction; integrated backrest and armrests; curved wave-like edges; deep scooped seat; non-upholstered body; smooth plastic shell; rounded armrest rims; splayed metal legs; slim cylindrical legs; angled tubular legs; high backrest corners; compact proportions; wide low silhouette; open space under seat; minimal leg structure; minimalist base construction; protective leg tips; uniform molded seat; smooth reflective surface; seamless seat shell; ergonomic bucket shape</t>
   </si>
   <si>
     <t>B-2020</t>
@@ -644,6 +395,9 @@
     <t>Tulipan</t>
   </si>
   <si>
+    <t>b2020</t>
+  </si>
+  <si>
     <t>Teresa Kruszewska</t>
   </si>
   <si>
@@ -653,10 +407,10 @@
     <t>FAMEG Radomsko (reedycja współczesna)</t>
   </si>
   <si>
-    <t>organiczna forma inspirowana kielichem kwiatu; szerokie kubełkowe siedzisko; płynne przejście między siedziskiem i oparciem; miękkie zaokrąglone linie; wyraźnie rozchylone boki; rzeźbiarska bryła</t>
-  </si>
-  <si>
-    <t>korpus ze sklejki formowanej; tapicerowana skorupa; drewniana podstawa; konstrukcja monolityczna; technologia giętej sklejki</t>
+    <t>Mebel charakteryzuje się masywną, organiczną i w pełni tapicerowaną sylwetką o kielichowatym kształcie, przypominającym literę T w widoku od tyłu. Górna krawędź oparcia płynnie rozszerza się ku bokom, tworząc szeroki, wywinięty na zewnątrz i zintegrowany kołnierz, który spełnia jednocześnie funkcję podłokietników o zaokrąglonych krawędziach. Dolna część korpusu ma formę jednolitego, półkolistego cokołu schodzącego bezpośrednio do ziemi, bez widocznych klasycznych nóg. Siedzisko jest grube, okrągłe i poduszkowe, głęboko osadzone wewnątrz otaczającej je z trzech stron konstrukcji oparcia. Całość pokryta jest gładką, jednolitą tkaniną obiciową bez pikowań, guzików czy przeszyć dekoracyjnych, z zachowaniem minimalistycznych, pionowych szwów łączących panele materiału na plecach oraz na wewnętrznej stronie oparcia.</t>
+  </si>
+  <si>
+    <t>Konstrukcja mebla opiera się na pełnym, zamkniętym korpusie szkieletowym, który jest całkowicie ukryty pod warstwą wyściełania i tapicerki. Półkolista, cylindryczna osłona dolna integruje bazę nośną z oparciem i bokami, tworząc jednolitą strukturę konstrukcyjną opierającą się na podłożu za pomocą niskich, niemal niewidocznych ślizgaczy lub stopek zamontowanych u podstawy. Okrągłe siedzisko montowane jest wewnątrz stabilnej wnęki korpusu. Górna rama oparcia i ramiona podłokietników są wyprofilowane na zewnątrz, tworząc monolityczny, usztywniony element nośny. W konstrukcji brak jakichkolwiek odsłoniętych elementów drewnianych, widocznych śrub, łączników czy bocznych kołków.</t>
   </si>
   <si>
     <t>RM58; fotele muszelkowe PRL; fotele skandynawskie o organicznej formie</t>
@@ -668,7 +422,7 @@
     <t>FAMEG – Fotel Tulipan B-2020; dokumentacja reedycji FAMEG; opracowania dotyczące twórczości Teresy Kruszewskiej</t>
   </si>
   <si>
-    <t>kubełkowe siedzisko; forma przypominająca kielich tulipana; szeroko rozchylone boki; jednolita tapicerowana skorupa; zaokrąglone wysokie oparcie; płynne przejście między siedziskiem i oparciem; organiczna bryła; brak widocznej drewnianej ramy bocznej; miękkie obłe krawędzie; rzeźbiarska forma; kompaktowa podstawa; sylwetka kwiatu tulipana</t>
+    <t>cup silhouette; organic shape; fully upholstered body; integrated backrest and armrests; flared upper collar; rounded outspread armrests; circular seat cushion; thick cushion seat; cylindrical base construction; solid upholstered plinth; closed lower frame; high integrated backrest; rounded backrest edges; smooth upholstery; minimal exposed elements; seamless visual construction; vertical back seams; wide upper profile; tapered lower profile; deep inset seat; enclosed side panels; no exposed wooden legs; hidden support feet; compact proportions; solid construction</t>
   </si>
   <si>
     <t>Typ 300-201</t>
@@ -677,16 +431,19 @@
     <t>Śnieżnik; Śnieżka (Do weryfikacji – obie nazwy występują w obiegu kolekcjonerskim, częściej spotykana jest nazwa Śnieżnik)</t>
   </si>
   <si>
+    <t>300-201</t>
+  </si>
+  <si>
     <t>1973 (najwcześniejsza potwierdzona wzmianka źródłowa)</t>
   </si>
   <si>
     <t>Bystrzycka Fabryka Mebli w Bystrzycy Kłodzkiej</t>
   </si>
   <si>
-    <t>lekka konstrukcja drewniana; forma inspirowana modelem Lisek 300-190; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; otwarta rama boczna; charakterystyczne nogi częściowo graniaste i częściowo zaokrąglone; smukłe proporcje</t>
-  </si>
-  <si>
-    <t>drewniany stelaż brzozowy lub bukowy; otwarta konstrukcja boczna; tapicerowane siedzisko; tapicerowane oparcie; pasy tapicerskie; konstrukcja szkieletowa</t>
+    <t>Fotel o zwartej, lekkiej sylwetce z wysokim, lekko odchylonym prostokątnym oparciem o delikatnie zwężającym się ku górze obrysie i zaokrąglonych narożnikach. Siedzisko szerokie, prostokątne, grubo tapicerowane, z prostą przednią krawędzią i łagodnie zaokrąglonymi narożnikami. Po bokach znajdują się smukłe, płaskie drewniane podłokietniki o prostym przebiegu z delikatnie zwężającymi się końcówkami, wsparte pojedynczym pionowym wspornikiem umieszczonym w przedniej części. Oparcie i siedzisko tworzą jednolitą bryłę tapicerowaną bez pikowania i przeszyć dekoracyjnych. Konstrukcja drewniana jest lekka i otwarta, z czterema smukłymi, zwężającymi się nogami oraz prostą dolną belką boczną łączącą przednią i tylną nogę. Charakterystycznym detalem jest śrubowe mocowanie podłokietników do tylnej części konstrukcji, widoczne z boku.</t>
+  </si>
+  <si>
+    <t>Konstrukcja wykonana z otwartego drewnianego stelaża. Cztery smukłe, lekko rozstawione nogi połączone są prostymi bocznymi belkami nośnymi. Podłokietniki stanowią oddzielne drewniane elementy mocowane z tyłu do oparcia pojedynczą śrubą i podparte od spodu pojedynczym pionowym wspornikiem osadzonym nad przednią nogą. Siedzisko i oparcie są osobnymi tapicerowanymi modułami zamocowanymi wewnątrz drewnianej ramy. Przestrzeń pod podłokietnikami pozostaje całkowicie otwarta, bez ukośnych elementów konstrukcyjnych ani paneli bocznych. Widoczna jest jedynie prosta dolna belka boczna stabilizująca stelaż.</t>
   </si>
   <si>
     <t>typ 300-190 Lisek; Śnieżka; BW-14 typ 300-199; B-7727</t>
@@ -698,8 +455,7 @@
     <t>Meblostan – Fotel Śnieżnik typ 300-201; Nowohuckie Renowacje – Fotele PRL; Pakamera – Fotel Śnieżnik typ 300-201; Audiovintage Store – Fotel klubowy Śnieżnik 300-201</t>
   </si>
   <si>
-    <t>otwarta drewniana rama boczna; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; smukła lekka bryła; duży prześwit pod siedziskiem; drewniane podłokietniki zintegrowane z ramą; nogi graniaste od góry; nogi zaokrąglone w dolnej części; skośne tylne nogi; widoczne drewniane elementy konstrukcyjne; forma zbliżona do modelu Lisek; geometryczny profil boczny
-Źródła potwierdzają produkcję w Bystrzyckiej Fabryce Mebli oraz silne pokrewieństwo konstrukcyjne z modelem 300-190 „Lisek”, natomiast projektant pozostaje niepotwierdzony.</t>
+    <t>compact armchair; lightweight wooden frame; open wooden frame; rectangular upholstered backrest; slightly tapered backrest; slightly reclined backrest; rounded backrest corners; thick upholstered backrest; thick upholstered seat; rectangular seat; straight front seat edge; rounded seat corners; smooth upholstery; plain upholstery; no tufting; no buttons; separate seat cushion; separate back cushion; slim wooden armrests; flat wooden armrests; straight armrests; tapered armrest ends; single vertical armrest support; front armrest support; rear armrest screw joint; visible slotted screw; exposed side fastener; tapered wooden legs; slender legs; slightly splayed legs; straight side rail; lower side stretcher; open space under armrests; open side profile; minimalist frame; exposed wooden structure; angular wooden supports; clean geometric lines; Scandinavian modern style; mid-century modern; floating upholstered body; rear-mounted armrests; wooden side frame; slim profile; simple construction; narrow arm supports</t>
   </si>
   <si>
     <t>GFM-57</t>
@@ -717,10 +473,10 @@
     <t>Gościcińska Fabryka Mebli; Zamojskie Fabryki Mebli (produkcja seryjna jako typ 200-203)</t>
   </si>
   <si>
-    <t>łukowate podłokietniki przypominające profil skoczni narciarskiej; elipsoidalne oparcie; lekka ażurowa konstrukcja; zwężające się ku dołowi nogi; tapicerowane siedzisko; smukła sylwetka; organiczna linia boczna</t>
-  </si>
-  <si>
-    <t>drewniany stelaż; otwarta konstrukcja boczna; tapicerowane siedzisko; gięte elementy drewniane; konstrukcja przeznaczona do produkcji seryjnej</t>
+    <t>Mebel charakteryzuje się lekką, dynamiczną sylwetką z silnie wyeksponowanym, giętym stelażem drewnianym o jasnym wybarwieniu. Elementem definiującym profil boczny krzesła są dwie płynnie wygięte, łukowate ramy, które wznoszą się od przodu siedziska ku górze, przechodząc bezpośrednio w pionowe wsporniki oparcia o łagodnym, parabolicznym kształcie. Oparcie ma formę prostokątnego, lekko zakrzywionego, tapicerowanego pasa rozpiętego między szczytami drewnianych ram, pozostawiając dużą, otwartą przestrzeń nad siedziskiem. Siedzisko jest trapezowate z zaokrąglonymi krawędziami, średnio grube i zamontowane wewnątrz bocznego stelaża. Krzesło nie posiada klasycznych, wysokich podłokietników, jednak zakończenia giętych bocznych listew wysuwają się nieznacznie do przodu poza obrys siedziska. Nogi są proste, zwężające się ku dołowi, o prostokątnym przekroju; przednie są ustawione pionowo, natomiast tylne odchylają się ku tyłowi, połączone ze sobą oraz z przednimi podpórkami niskimi, prostymi łącznikami (prożkami).</t>
+  </si>
+  <si>
+    <t>Szkielet nośny mebla wykonany jest z litego, giętego drewna. Konstrukcja boczna opiera się na monolitycznych, łukowatych ramiakach, do których od tyłu przymocowane są skośne nogi tylne, a od przodu pionowe nogi przednie. Tapicerowany panel oparcia jest montowany doczołowo pomiędzy wewnętrzne płaszczyzny ramion stelaża i unieruchomiony za pomocą dwóch widocznych, okrągłych śrub montażowych z metalowymi podkładkami umieszczonych symetrycznie po każdej stronie zewnętrznej belki. Siedzisko osadzone jest na skrzyniowej konstrukcji carg. Stabilność podstawy wzmacniają trzy dolne łączniki (boczne oraz jeden poprzeczny z tyłu), które tworzą zamknięty układ usztywniający ramę nóg.</t>
   </si>
   <si>
     <t>typ 200-190 Rajmunda Hałasa; krzesła Aga; krzesła patyczaki lat 60.; lekkie krzesła tapicerowane PRL</t>
@@ -732,8 +488,7 @@
     <t>Magazif – Krzesło Skoczek; Ikony Designu PL – Krzesło GFM-57 Skoczek; Meblostan – Krzesło Skoczek; Sosenko Home Decor – Krzesło Skoczek; Allegro Artykuł – Krzesło kilka słów o najtrudniejszym meblu</t>
   </si>
   <si>
-    <t>łukowate podłokietniki przypominające skocznię narciarską; elipsoidalne oparcie; otwarta drewniana rama boczna; smukłe zwężające się nogi; tapicerowane siedzisko; duży prześwit pod siedziskiem; płynna linia podłokietnika przechodząca w nogę; lekka ażurowa konstrukcja; organiczny profil boczny; oparcie w kształcie pionowej elipsy; cienkie elementy drewniane; dynamiczna sylwetka inspirowana skokami narciarskimi
-Źródła potwierdzają, że model został zaprojektowany przez Juliusza Kędziorka w Gościcińskiej Fabryce Mebli w 1965 r., otrzymał nagrodę „Dobre–Ładne–Poszukiwane” i został skierowany do produkcji seryjnej jako typ 200-203</t>
+    <t>open wooden side frame; curved side rails; dynamic side profile; low upholstered backrest; rectangular backrest; split backrest design; open space under backrest; trapezoidal seat; floating seat appearance; straight tapered front legs; splayed rear legs; tapered wooden legs; lower stretcher; cross stretcher; visible side bolts; visible screw joints; solid wooden frame; light wood finish; large exposed wooden frame; smooth upholstery; textured fabric weave; compact proportions; slim silhouette; integrated rear supports; rounded front seat edge</t>
   </si>
   <si>
     <t>Typ 200-125 VAR</t>
@@ -742,16 +497,19 @@
     <t>Aga</t>
   </si>
   <si>
+    <t>200-125</t>
+  </si>
+  <si>
     <t>ok. 1972–1975 (w źródłach występują rozbieżności dotyczące dokładnego roku projektu)</t>
   </si>
   <si>
     <t>Wielkopolskie Fabryki Mebli; produkcja seryjna PRL (pozostali producenci wymagają weryfikacji)</t>
   </si>
   <si>
-    <t>wysokie tapicerowane oparcie; trapezowy układ nóg; miękkie tapicerowane siedzisko; smukła skandynawska forma; zwężająca się ku górze bryła; lekkie proporcje; drewniana konstrukcja eksponowana po bokach</t>
-  </si>
-  <si>
-    <t>drewniany stelaż bukowy; tapicerowane siedzisko; tapicerowane oparcie; sprężyny siedziska; cztery drewniane nogi; konstrukcja przeznaczona do intensywnego użytkowania klubowego</t>
+    <t>Krzesło o zwartej, smukłej sylwetce z wysokim, lekko odchylonym oparciem w kształcie zwężającego się ku górze prostokąta z zaokrąglonymi narożnikami. Siedzisko prostokątne, grubo tapicerowane, z lekko zaokrągloną przednią krawędzią oraz lamówką biegnącą wzdłuż obwodu. Brak podłokietników. Drewniana konstrukcja widoczna jest wyłącznie w dolnej części mebla i obejmuje boczne belki oraz cztery smukłe, zwężające się ku dołowi nogi rozstawione pod niewielkim kątem. W profilu widoczne są krótkie ukośne wsporniki pomiędzy przednimi nogami a bocznymi belkami oraz odsłonięte śruby mocujące. Oparcie ma gładkie powierzchnie bez przeszyć dekoracyjnych i wyraźnie zaznaczoną grubość widoczną z boku i od tyłu.</t>
+  </si>
+  <si>
+    <t>Konstrukcja oparta na drewnianym stelażu z odsłoniętymi bocznymi belkami nośnymi tworzącymi otwartą konstrukcję pod siedziskiem. Siedzisko i oparcie wykonane jako oddzielne, tapicerowane elementy zamocowane do drewnianej ramy. Oparcie osadzone pomiędzy tylnymi elementami konstrukcji i połączone z ramą siedziska. Przednie nogi mocowane do bocznych belek oraz usztywnione krótkimi ukośnymi wspornikami. Po bokach widoczne są metalowe śruby mocujące. Konstrukcja nie posiada podłokietników ani poprzeczek łączących nogi. Tapicerka ma gładkie powierzchnie wykończone lamówką na obwodzie siedziska i oparcia.</t>
   </si>
   <si>
     <t>typ 200-190 Rajmunda Hałasa; GFM-57 Skoczek; lekkie krzesła klubowe PRL lat 70.</t>
@@ -763,7 +521,7 @@
     <t>Elle Decoration Polska – Krzesło VAR AGA projektu Józefa Chierowskiego; Nowohuckie Renowacje – Krzesło Aga typ 200-125; Patyna.pl – Krzesła AGA typu 200-125 VAR; Linie Studio – 200-125 VAR; Meblościanka – 200-125 VAR</t>
   </si>
   <si>
-    <t>wysokie tapicerowane oparcie; trapezowy układ nóg; szerokie miękkie siedzisko; brak podłokietników; drewniane nogi rozszerzające się ku dołowi; zwężająca się ku górze sylwetka; lekka skandynawska forma; prostokątne oparcie z zaokrąglonymi krawędziami; widoczne drewniane elementy boczne; smukłe proporcje; geometryczna bryła; profil boczny z pochylonym oparciem</t>
+    <t>slim silhouette; compact proportions; open wooden side frame; visible wooden side rails; high upholstered backrest; tapered rectangular backrest; slightly reclined backrest; rounded backrest corners; thick upholstered backrest; rectangular seat; deep upholstered seat; thick seat cushion; rounded front seat edge; box seat cushion; no armrests; splayed tapered legs; tapered wooden legs; front legs attached to side rails; angled front support; visible side bolts; visible screw joints; solid wooden frame; smooth upholstery; piping; open space under seat; minimal exposed wood; separated seat and backrest; straight side rails; thick backrest profile; flush upholstered surfaces; visible structural side brackets; exposed side fasteners; integrated rear leg construction; boxed upholstery profile; four leg construction; exposed wooden lower frame; inclined rear legs; closed upholstered back; flat seat surface</t>
   </si>
   <si>
     <t>Typ 200-190</t>
@@ -772,6 +530,9 @@
     <t>Hałas; Grzybek</t>
   </si>
   <si>
+    <t>200-190</t>
+  </si>
+  <si>
     <t>Rajmund Teofil Hałas</t>
   </si>
   <si>
@@ -781,10 +542,10 @@
     <t>Zakłady Mebli w Gostyniu (Do weryfikacji); produkcja seryjna w kilku zakładach meblarskich PRL – Do weryfikacji</t>
   </si>
   <si>
-    <t>okrągła forma oparcia przypominająca kapelusz grzyba; tapicerowane oparcie i siedzisko; smukłe zwężające się nogi; lekka konstrukcja; wyraźnie wyodrębnione oparcie nad siedziskiem; proporcje inspirowane wzornictwem skandynawskim; minimalistyczna sylwetka</t>
-  </si>
-  <si>
-    <t>drewniany stelaż; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; mocowane oddzielnie siedzisko i oparcie; nogi zwężające się ku dołowi</t>
+    <t>Krzesło o zwartej, smukłej sylwetce z otwartą konstrukcją oparcia. Oparcie tworzy wąski, poziomy, półowalny element tapicerowany o zaokrąglonych końcach, osadzony na dwóch smukłych pionowych podporach. Siedzisko szerokie, prostokątne z mocno zaokrąglonymi narożnikami i krawędziami, grubo tapicerowane oraz lekko wypukłe. Brak podłokietników. Drewniana konstrukcja jest wyraźnie wyeksponowana i obejmuje pełne boczne profile z dużym, łukowym wycięciem pod siedziskiem, cztery smukłe, lekko zwężające się nogi oraz poprzeczki łączące nogi w przedniej i tylnej części. W górnej części podpór oparcia widoczne są odsłonięte śruby mocujące. Charakterystycznym elementem jest płynne przejście bocznych profili w tylne podpory oparcia oraz duże otwarte przestrzenie pomiędzy elementami konstrukcji.</t>
+  </si>
+  <si>
+    <t>Konstrukcja oparta na masywnym drewnianym stelażu z pełnymi bocznymi elementami stanowiącymi jednocześnie przednie nogi, tylne podpory oparcia oraz boczne belki nośne. Siedzisko wykonane jako oddzielny tapicerowany moduł osadzony na drewnianej ramie. Oparcie stanowi niezależny tapicerowany element mocowany do dwóch pionowych drewnianych wsporników za pomocą widocznych śrub. Konstrukcja posiada przednią i tylną poprzeczkę usztywniającą oraz otwartą przestrzeń pod siedziskiem wynikającą z dużych wycięć w bocznych profilach. Połączenia bocznych elementów mają płynne, zaokrąglone przejścia, bez podłokietników i bez dodatkowych elementów bocznych.</t>
   </si>
   <si>
     <t>Aga 200-125; Skoczek GFM-57; krzesła skandynawskie lat 60.; lekkie krzesła tapicerowane PRL</t>
@@ -796,12 +557,15 @@
     <t>Odnawialnia – Wiem co odnawiam | krzesło Hałasa typ 200-190; Patyna.pl – Krzesła typ 200-190 Rajmund Teofil Hałas; Meblostan – Komplet krzeseł typ 200-190; Daniel Stoiński Redesign – Przewodnik po renowacji krzesła 200-190; Homebook – Krzesło Hałasa typ 200-190</t>
   </si>
   <si>
-    <t>okrągłe oparcie przypominające grzybek; oparcie szersze od wspornika; tapicerowane okrągłe oparcie; tapicerowane siedzisko; smukłe nogi zwężające się ku dołowi; brak podłokietników; lekka skandynawska forma; duży prześwit pod siedziskiem; cienki drewniany stelaż; wyraźne oddzielenie oparcia od siedziska; geometryczna bryła; profil boczny z lekko odchylonym oparciem</t>
+    <t>slim silhouette; compact proportions; open wooden side frame; large exposed wooden frame; sculpted side frame; curved side rails; open backrest construction; low upholstered backrest; rounded rectangular backrest; wing shaped backrest; floating backrest; rounded backrest corners; narrow backrest; deep upholstered seat; rectangular seat; rounded seat corners; thick seat cushion; smooth upholstery; no armrests; straight tapered legs; tapered wooden legs; front legs integrated into side frame; rear legs integrated into backrest; front stretcher; rear stretcher; open space under seat; visible side screws; visible screw joints; exposed backrest fasteners; solid wooden frame; sculpted wooden supports; rounded structural transitions; separated seat and backrest; thin backrest supports; upholstered backrest pad; upholstered seat pad; continuous side profile; rounded lower frame opening; minimal ornamentation</t>
   </si>
   <si>
     <t>B-6028</t>
   </si>
   <si>
+    <t>b-6028</t>
+  </si>
+  <si>
     <t>Barbara Fenrych-Węcławska (Do weryfikacji); Józef Chierowski (Do weryfikacji – atrybucja pojawiająca się wyłącznie w źródłach kolekcjonerskich)</t>
   </si>
   <si>
@@ -811,10 +575,10 @@
     <t>Fabryka Mebli Giętych w Radomsku; FAMEG Radomsko; Radomszczańska Fabryka Mebli Giętych</t>
   </si>
   <si>
-    <t>wysokie profilowane oparcie; szerokie drewniane podłokietniki; gięte elementy bukowe; głębokie siedzisko; lekka otwarta konstrukcja boczna; elegancka smukła sylwetka; forma łącząca cechy fotela klubowego i wypoczynkowego</t>
-  </si>
-  <si>
-    <t>stelaż z giętego drewna bukowego; otwarta konstrukcja ramowa; tapicerowane siedzisko; tapicerowane oparcie; drewniane podłokietniki zintegrowane z ramą; konstrukcja szkieletowa</t>
+    <t>Mebel wyróżnia się dynamiczną, geometryczną sylwetką o otwartej konstrukcji bocznej z silnie wyeksponowanym drewnianym stelażem. Profil boczny definiuje charakterystyczny kształt odwróconej litery V lub litery A, w którym tylne i przednie podpory zbiegają się ku górze, przechodząc płynnie w mocno wygięte, łukowate ramiona. Podłokietniki posiadają formę poziomych, płaskich, drewnianych deseczek o zaokrąglonych krawędziach, przypominających wiosła lub płetwy, które wyraźnie wystają poza przedni obrys pionowych podpórek. Oparcie jest wysokie, lekko odchylone do tyłu, o prostokątnym kształcie z łagodnie zaokrąglonymi narożnikami. Siedzisko jest prostokątne, średnio grube, o płaskiej powierzchni, wysunięte do przodu względem bocznego stelaża. Zarówno oparcie, jak i siedzisko są w pełni tapicerowane gładką, dwukolorową tkaniną o strukturalnym splotu melanżowym, tworząc wizualnie odrębne, niezależne elementy zawieszone wewnątrz drewnianej ramy. Nogi są smukłe, toczone i zwężające się ku dołowi, przy czym tylne są ustawione pod bardzo ostrym kątem, szeroko rozstawione poza obrys oparcia.</t>
+  </si>
+  <si>
+    <t>Szkielet mebla opiera się na otwartej, bocznej ramie z litego drewna, połączonej poziomymi, prostymi cargami pod siedziskiem. Dynamiczną stabilność zapewniają zbiegające się ramiona konstrukcyjne, z których tylna, długa noga przechodzi w łuk podłokietnika, a przednia noga wznosi się ukośnie w górę, podtrzymując wysunięty element podłokietnikowy. W pełni tapicerowane oparcie oraz siedzisko są montowane niezależnie do bocznych ram drewnianych. Na bokach łuków oparcia widoczne są pojedyncze, wpuszczane śruby montażowe, łączące wewnętrzny szkielet oparcia z drewnianym stelażem. Całość konstrukcji spina poprzeczna belka łącząca dolne elementy ramy z tyłu mebla, stabilizując szeroki rozstaw tylnych, skośnych nóg.</t>
   </si>
   <si>
     <t>typ 300-123 Puchała; typ 300-177 Zajączek; B-7727; typ 366</t>
@@ -826,7 +590,10 @@
     <t>MidMod – Fotel B6028 FAMEG Radomsko Polska lata 60; Oldsen Design – Fotel B6028 prod. FAMEG Radomsko; Nowohuckie Renowacje – Fotel PRL B-6028 z lat 60-tych; Fotelowo Facebook – fotel projektu Barbary Fenrych-Węcławskiej; Instagram Renowacja Mebli PRL – B6028 lata produkcji 1960</t>
   </si>
   <si>
-    <t>wysokie prostokątne oparcie; szerokie drewniane podłokietniki; gięte boczne elementy z drewna; otwarta rama boczna; głębokie siedzisko; masywniejsza bryła niż typ 366; bukowy stelaż; duży prześwit pod siedziskiem; profilowane podłokietniki; smukłe nogi zintegrowane z ramą; tapicerowane oparcie i siedzisko; geometryczny profil boczny</t>
+    <t>open wooden side frame; inverted V-frame side construction; dynamic side profile; flat plank armrests; paddle-shaped armrests; extended wooden armrests; curved side rails; high upholstered backrest; slightly reclined backrest; rounded rectangular backrest; rectangular seat; floating seat; splayed tapered legs; angled rear legs; tapered wooden legs; visible side bolts; visible screw joints; solid wooden frame; large exposed wooden frame; clear space under seat; structural wooden connections; smooth upholstery; textured fabric weave; compact proportions; slim silhouette</t>
+  </si>
+  <si>
+    <t>B-310 VAR</t>
   </si>
   <si>
     <t>A. Dutka</t>
@@ -838,10 +605,10 @@
     <t>Zakłady Mebli Giętych w Radomsku; Gołuchowskie Fabryki Mebli</t>
   </si>
   <si>
-    <t>duże gabaryty; szerokie głębokie siedzisko; masywne drewniane podłokietniki; geometryczna forma boczna; lekko pochylone oparcie; otwarta konstrukcja ramowa; modernistyczna sylwetka eksportowa</t>
-  </si>
-  <si>
-    <t>stelaż z drewna bukowego; sprężyny lejowe w siedzisku; tapicerowane siedzisko i oparcie; otwarta konstrukcja boczna; drewniane podłokietniki zintegrowane z ramą; konstrukcja rozbieralna skręcana śrubami</t>
+    <t>Mebel charakteryzuje się dynamiczną, geometryczną sylwetką o otwartej konstrukcji bocznej z wyrazistymi, zintegrowanymi podłokietnikami i nogami. Głównym elementem profilu bocznego jest drewniana rama przypominająca odwróconą literę „V” lub literę „A”, w której przednia i tylna noga zbiegają się ku górze, łącząc się bezpośrednio z płaskim, lekko profilowanym i unoszącym się ku przodowi podłokietnikiem o zaokrąglonych końcach. Siedzisko oraz oparcie stanowią osobne, grube elementy w pełni tapicerowane gładką, jednolitą tkaniną strukturalną. Oparcie jest wysokie, o prostokątnym obrysie z delikatnie zaokrągloną górną krawędzią, zamontowane pod stałym, ergonomicznym kątem odchylenia. Siedzisko ma postać masywnej prostokątnej poduszki z zaokrąglonymi krawędziami. Przednie i tylne nogi mają prostokątny, zwężający się ku dołowi przekrój i są mocno rozchylone, co nadaje meblowi wizualną stabilność i lekkość, pozostawiając otwartą przestrzeń pod siedziskiem.</t>
+  </si>
+  <si>
+    <t>Konstrukcja mebla opiera się na zewnętrznym, otwartym szkielecie z litego drewna, tworzącym niezależne ramy boczne. Charakterystyczne ukośne nogi łączą się w górnej części w węzeł konstrukcyjny podtrzymujący podłokietnik, a ich stabilizację zapewniają poprzeczne, ukryte lub zintegrowane pod siedziskiem ramiaki. W pełni tapicerowane korpusy siedziska i oparcia są osadzone wewnątrz drewnianej konstrukcji. Oparcie mocowane jest do tylnej, przedłużonej części podłokietników za pomocą widocznych na zewnątrz bocznych połączeń śrubowych z okrągłymi zaślepkami. Konstrukcja boczna nóg posiada również widoczne kołki lub śruby montażowe w dolnej partii przedniej nogi, łączące stelaż z ramą nośną siedziska.</t>
   </si>
   <si>
     <t>B-6028; GFM-64; typ 300-190 Lisek; B-7727</t>
@@ -853,22 +620,25 @@
     <t>Meblostan – Para foteli B-310 VAR; Pufa Design – Oryginalny fotel B-310 VAR; Yestersen – Fotel B-310 VAR Polska lata 70.; Reko-Czyny – Fotel B-310 VAR metamorfoza; archiwalne ogłoszenia kolekcjonerskie B-310 VAR</t>
   </si>
   <si>
-    <t>masywne drewniane podłokietniki; szerokie głębokie siedzisko; wysunięte przednie podłokietniki; otwarta drewniana rama boczna; prostokątne tapicerowane oparcie; grube proporcje siedziska; lekko pochylone oparcie; duży prześwit pod siedziskiem; widoczne śruby montażowe w ramie; geometryczny profil boczny; szeroki rozstaw nóg; cięższa bryła niż typ 366; bukowy stelaż; modernistyczna forma eksportowa</t>
+    <t>compact proportions; open wooden side frame; solid wooden frame; triangular side frame; A-frame side construction; geometric wooden frame; high upholstered backrest; tapered rectangular backrest; slightly reclined backrest; rounded backrest corners; thick upholstered backrest; deep upholstered seat; box seat cushion; thick seat cushion; rounded front seat edge; rectangular seat; flat plank armrests; wide wooden armrests; curved armrests; straight tapered legs; splayed tapered legs; rear legs integrated into backrest; visible side bolts; visible screw joints; smooth upholstery; open space under seat; large exposed wooden frame; visible wooden side rails</t>
   </si>
   <si>
     <t>GFM-22 (typ 200/128)</t>
   </si>
   <si>
+    <t>GFM-22</t>
+  </si>
+  <si>
     <t>ok. 1960</t>
   </si>
   <si>
     <t>Gościcińska Fabryka Mebli (GFM)</t>
   </si>
   <si>
-    <t>nerkowate oparcie; lekka ażurowa konstrukcja; smukłe zwężające się nogi; gięta drewniana rama; tapicerowane siedzisko; tapicerowane oparcie; wyraźnie rozstawione tylne nogi</t>
-  </si>
-  <si>
-    <t>drewniany stelaż; gięte elementy z litego drewna; tapicerowane siedzisko; tapicerowane oparcie ze sklejki giętej; konstrukcja szkieletowa przeznaczona do produkcji seryjnej</t>
+    <t>Mebel odznacza się lekką, organiczną sylwetką o jasnym wybarwieniu drewnianego stelaża oraz charakterystycznych, zaokrąglonych kształtach elementów tapicerowanych. Profil boczny wyróżnia się uniesioną ramą siedziska oraz pionowo zbiegającymi się wspornikami oparcia, które zwężają się ku górze. Oparcie ma formę poziomego, spłaszczonego owalu lub elipsy, przypominającej ziarno, i jest całkowicie niezależne od siedziska, tworząc wyraźny prześwit w dolnej części pleców. Siedzisko jest cienkie, ergonomicznie wyprofilowane i lekko wygięte nieckowato ku środkowi, o zaokrąglonej przedniej krawędzi. Krzesło nie posiada podłokietników, co podkreśla jego kompaktowe proporcje. Nogi przednie są proste, o prostokątnym przekroju, delikatnie zwężające się ku dołowi, natomiast nogi tylne są zintegrowane z ramionami oparcia, odchylając się ku tyłowi pod łagodnym kątem. Zarówno oparcie, jak i siedzisko pokryte są gładką, jednolitą tkaniną bez pikowań.</t>
+  </si>
+  <si>
+    <t>Konstrukcja opiera się na otwartej ramie z litego drewna o widocznej strukturze usłojenia. Elementem nośnym siedziska są dwie profilowane, szerokie boczna caragi o dynamicznym, falistym kształcie, które wznoszą się ku tyłowi i łączą z tylnymi wspornikami. Tylne nogi przechodzą płynnie w pionowe ramiaki oparcia, zwężające się ku górze. Owalny panel oparcia jest zamontowany doczołowo do przedniej płaszczyzny tych ramiaków, a od tyłu połączony z nimi za pomocą widocznych śrub montażowych, wkręconych symetrycznie po dwie sztuki z każdej strony. Dodatkowa poprzeczka pozioma stabilizuje rozstaw ramion oparcia bezpośrednio pod dolną krawędzią elipsy. Siedzisko jest zamontowane powierzchniowo na skrzyni z carg, sprawiając wrażenie uniesionego nad stelażem.</t>
   </si>
   <si>
     <t>GFM-57 Skoczek; typ 200-190 Rajmunda Hałasa; Aga 200-125; krzesła skandynawskie z lat 60.</t>
@@ -880,7 +650,7 @@
     <t>Pamono – Mid-Century GFM-22 Chairs by Juliusz Kędziorek; Vinterior – GFM-22 model 200/128; Selency – Iconic GFM-22 Chair by Juliusz Kędziorek; Instagram Zostań z Vintage – Krzesło GFM-22 typ 200/128</t>
   </si>
   <si>
-    <t>nerkowate tapicerowane oparcie; oparcie szersze od wspornika; smukłe zwężające się nogi; lekka ażurowa konstrukcja; gięta drewniana rama; prostokątne tapicerowane siedzisko; duży prześwit pod siedziskiem; cienkie elementy konstrukcyjne; szeroko rozstawione tylne nogi; profil boczny z delikatnie pochylonym oparciem; organiczny kształt oparcia; minimalistyczna sylwetka lat 60.</t>
+    <t>oval upholstered backrest; elliptical backrest; split backrest design; open space under backrest; curved upholstered seat; thin seat cushion; no armrests; open wooden side frame; visible wooden side rails; wavy side aprons; integrated rear legs and backrest; straight tapered front legs; splayed rear legs; tapered wooden legs; visible screw joints; visible rear bolts; solid wooden frame; light wood finish; minimal exposed wood; slim silhouette; compact proportions; smooth upholstery; textured fabric weave; organic frame geometry; floating seat appearance</t>
   </si>
   <si>
     <t>Typ 1020</t>
@@ -895,10 +665,10 @@
     <t>Słupskie Fabryki Mebli</t>
   </si>
   <si>
-    <t>muszelkowe profilowane oparcie; jednolita tapicerowana skorupa; zaokrąglona górna krawędź oparcia; smukłe stożkowe nogi; lekka modernistyczna forma; brak podłokietników; organiczna sylwetka</t>
-  </si>
-  <si>
-    <t>profilowana skorupa ze sklejki; tapicerowana skorupa; drewniany stelaż; cztery drewniane nogi; konstrukcja szkieletowa; połączenie sklejki i drewna litego</t>
+    <t>Mebel wyróżnia się zgrabną, kompaktową sylwetką bez podłokietników, o wyraźnie zaokrąglonych, organicznych liniach części tapicerowanej. Charakterystycznym elementem oparcia jest łukowate, półkoliste wycięcie w jego dolnej części tuż nad siedziskiem, tworzące otwarty prześwit. Samo oparcie jest wysokie, zwężające się lekko ku górze z zaokrąglonymi narożnikami i pochylone pod kątem, a jego dolne krawędzie boczne płynnie schodzą poniżej linii siedziska, otaczając je z tyłu. Siedzisko ma postać grubej, niemal kwadratowej poduszki o mocno zaokrąglonych narożnikach i prostej krawędzi przedniej, wykończonej na całym obwodzie subtelną wypustką (pipingiem). Podstawa mebla jest w pełni ukryta pod tapicerką, z której bezpośrednio wyprowadzono cztery toczone, zwężające się ku dołowi drewniane nogi. Przednie i tylne nogi są zamocowane pod wyraźnym kątem, tworząc stabilną, rozszerzającą się ku dołowi geometrię.</t>
+  </si>
+  <si>
+    <t>Konstrukcja opiera się na wewnętrznym, w pełni tapicerowanym stelażu, w którym elementy nośne siedziska i oparcia są zintegrowane pod warstwą materiału. Oparcie i siedzisko łączą się ze sobą w tylnej części za pomocą bocznych paneli oparcia schodzących poniżej płaszczyzny siedzenia, pozostawiając wolną przestrzeń w centralnej części dzięki ozdobnemu wycięciu. Drewniane, toczone nogi montowane są bezpośrednio do dolnej ramy konstrukcyjnej ukrytej wewnątrz siedziska, bez widocznych zewnętrznych łączników, śrub czy poprzeczek stabilizujących. Tapicerka wykonana z gładkiej tkaniny ściśle przylega do formy mebla, a krawędzie szycia siedziska zostały wzmocnione i podkreślone materiałową wypustką.</t>
   </si>
   <si>
     <t>RM58; krzesła muszelkowe produkcji NRD; krzesła skandynawskie lat 60.; fotel Ewa</t>
@@ -910,12 +680,18 @@
     <t>Archiwalne katalogi Słupskich Fabryk Mebli; opracowania kolekcjonerskie dotyczące wzornictwa SFM; materiały renowatorów specjalizujących się w meblach PRL; publikacje poświęcone projektom Wiesława Leśniewskiego i Stanisława Lejkowskiego</t>
   </si>
   <si>
-    <t>muszelkowe profilowane oparcie; jednolita tapicerowana skorupa; zaokrąglona górna krawędź oparcia; płynne przejście oparcia w siedzisko; brak podłokietników; cztery smukłe stożkowe drewniane nogi; lekka organiczna bryła; profilowana skorupa ze sklejki; niewielki prześwit pod siedziskiem; forma inspirowana muszlą</t>
+    <t>slim silhouette; compact proportions; high upholstered backrest; tapered rectangular backrest; slightly reclined backrest; rounded backrest corners; backrest with circular cutout; backrest with bottom opening; thick upholstered backrest; deep upholstered seat; box seat cushion; thick seat cushion; rounded front seat edge; piping; smooth upholstery; no armrests; splayed tapered legs; straight tapered legs; tapered wooden legs; minimal exposed wood; hidden wooden frame; separate wooden legs; clean upholstery lines; organic modern shape; no visible hardware; open space under seat</t>
+  </si>
+  <si>
+    <t>Typ 299</t>
   </si>
   <si>
     <t>Bumerang</t>
   </si>
   <si>
+    <t>typ 299</t>
+  </si>
+  <si>
     <t>Ryszard Kulm</t>
   </si>
   <si>
@@ -925,10 +701,10 @@
     <t>Gościcińska Fabryka Mebli</t>
   </si>
   <si>
-    <t>charakterystyczne łukowato wygięte przednie nogi przypominające bumerang; lekka ażurowa konstrukcja; tapicerowane siedzisko; tapicerowane oparcie; smukła sylwetka; zwężające się ku dołowi nogi; modernistyczna forma inspirowana skandynawskim wzornictwem</t>
-  </si>
-  <si>
-    <t>drewniany stelaż bukowy; gięte elementy boczne; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; połączenia skręcane i klejone</t>
+    <t>Mebel wyróżnia się lekką, modernistyczną sylwetką o jasnym wybarwieniu drewna z wyraźnie wyeksponowaną strukturą sklejki liściastej. Profil boczny definiuje charakterystyczny, gięty pałąk oparcia, który płynnie schodzi w dół, przechodząc pod poduszkę siedziska i tworząc stabilne podparcie. Oparcie jest szerokie, prostokątne z łagodnie zaokrąglonymi narożnikami i delikatnym wygięciem ergonomicznym; wykonano je z gładkiej, lakierowanej sklejki bez tapicerki. Siedzisko ma kształt zbliżony do kwadratu, jest cienkie, płaskie i tapicerowane gładkim materiałem, osadzonym wewnątrz widocznej, otwartej ramy drewnianej. Krzesło nie posiada podłokietników, co nadaje mu kompaktowe proporcje. Elementem wyróżniającym geometrię podstawy są mocno wychylone, zwężające się ku dołowi przednie i tylne nogi o spłaszczonym, owalnym przekroju, połączone w górnej części łukowym węzłem konstrukcyjnym na boku ramy.</t>
+  </si>
+  <si>
+    <t>Konstrukcja mebla opiera się na otwartej, bocznej ramie z klejonego blokowo i profilowanego drewna oraz giętej sklejki. Charakterystyczne, dwuwarstwowe oparcie ze sklejki montowane jest doczołowo od przodu pionowych ramion stelaża za pomocą bocznych wkrętów. Nośny element oparcia schodzi łukiem pod ramę siedziska, gdzie łączy się ze skrzynią. Nogi przednie i tylne tworzą zintegrowaną, odwróconą parę podpór bocznych – w miejscu ich zbiegu, na zewnętrznej stronie ramy siedziska, widoczne są metalowe, okrągłe nity lub śruby montażowe spajające konstrukcję nóg z caragami. Pod siedziskiem, na froncie, znajduje się pojedyncza, prosta poprzeczka stabilizująca szerokość rozstawu stelaża.</t>
   </si>
   <si>
     <t>GFM-22; typ 200-190 Rajmunda Hałasa; GFM-57 Skoczek; krzesła skandynawskie lat 60</t>
@@ -940,7 +716,7 @@
     <t>Meblostan – Komplet 4 krzeseł Bumerang typ 299; Skarby PRL – Krzesło tapicerowane Bumerang typ 299; Patyna – Komplet krzeseł typ 299 Bumerang; Deccoria – 10 słynnych mebli z PRL; Stary Fotel – Krzesła Bumerang metamorfoza</t>
   </si>
   <si>
-    <t>łukowato wygięte przednie nogi w kształcie bumerangu; gięte boczne elementy drewniane; tapicerowane prostokątne siedzisko; tapicerowane oparcie; smukła lekka bryła; cienki drewniany stelaż; zwężające się ku dołowi nogi; wyraźny prześwit pod siedziskiem; organiczny profil boczny; lekko odchylone oparcie; minimalistyczna forma lat 60.; charakterystyczna sylwetka bumerangu</t>
+    <t>open wooden side frame; inverted V-frame side construction; dynamic side profile; exposed plywood backrest; rectangular backrest; rounded backrest corners; curved wooden backrest supports; thin upholstered seat; square seat; minimal exposed wood; floating seat appearance; splayed tapered legs; straight tapered legs; angled wooden legs; visible side bolts; visible screw joints; front cross stretcher; solid wooden frame; light wood finish; large exposed wooden frame; clear space under seat; no armrests; compact proportions; slim silhouette; smooth upholstery</t>
   </si>
   <si>
     <t>Typ 300-227</t>
@@ -949,16 +725,19 @@
     <t>Celia</t>
   </si>
   <si>
+    <t>300-227</t>
+  </si>
+  <si>
     <t>ok. 1965; produkcja na przełomie lat 60. i 70. XX w.</t>
   </si>
   <si>
     <t>Zamojskie Fabryki Mebli</t>
   </si>
   <si>
-    <t>brak podłokietników; toczone drewniane nogi umieszczone po bokach części tapicerowanej; trapezowe siedzisko; proste tapicerowane oparcie; lekka minimalistyczna forma; kompaktowe wymiary; stylistyka skandynawskiego modernizmu</t>
-  </si>
-  <si>
-    <t>drewniany stelaż; toczone nogi; tapicerowane siedzisko; tapicerowane oparcie; otwarta konstrukcja bez podłokietników; konstrukcja szkieletowa przeznaczona do produkcji seryjnej</t>
+    <t>Mebel charakteryzuje się kompaktową sylwetką o wyważonych proporcjach bez podłokietników, z szerokim siedziskiem i wysokim, lekko odchylonym oparciem. Tapicerowane oparcie posiada kształt zwężającego się ku górze prostokąta o zaokrąglonych narożnikach, natomiast tapicerowane siedzisko ma prostokątny obrys z łagodnie zaokrągloną przednią krawędzią. Widoczna drewniana rama boczna tworzy geometryczny układ, w którym ukośne przednie i tylne nogi są połączone poziomą poprzeczką. Przednie nogi, lekko rozchylone na boki, sięgają górną krawędzią do poziomu siedziska, natomiast tylne nogi wznoszą się wyżej i integrują z bokami oparcia. Całość opiera się na smukłych, toczonych i zwężających się ku dołowi drewnianych nogach, z charakterystycznymi widocznymi łbami śrub montażowych na zewnętrznych płaszczyznach ramy.</t>
+  </si>
+  <si>
+    <t>Konstrukcja opiera się na otwartej, drewnianej ramie bocznej z litego drewna, stabilizowanej poziomymi cargami pod siedziskiem. Przednie, zwężane ku dołowi nogi są połączone z poziomą listwą boczna i zamocowane do konstrukcji siedziska za pomocą widocznych od zewnątrz połączeń śrubowych. Tylne nogi przechodzą w sposób ciągły od podłoża, łączą się z poziomą poprzeczką boczną, a ich przedłużone górne ramiona są przykręcone bezpośrednio do boków tapicerowanego oparcia za pomocą widocznych śrub bocznych. Siedzisko i oparcie stanowią oddzielne elementy tapicerowane gładką tkaniną, zamontowane wewnątrz otwartego szkieletu drewnianego, co pozostawia wolną przestrzeń pod siedziskiem.</t>
   </si>
   <si>
     <t>typ 300-190 Lisek; typ 366; GFM-64; lekkie fotele klubowe PRL bez podłokietników</t>
@@ -970,7 +749,7 @@
     <t>Meblostan – Fotel CELIA typ 300-227; Patyna – Fotel CELIA typ 300-227 PRL; Szajba Sklep – Fotel Celia typ 300-227; materiały kolekcjonerskie dotyczące Zamojskich Fabryk Mebli</t>
   </si>
   <si>
-    <t>brak podłokietników; toczone drewniane nogi umieszczone po bokach korpusu; trapezowe tapicerowane siedzisko; prostokątne tapicerowane oparcie; lekka minimalistyczna bryła; duży prześwit pod siedziskiem; cienki drewniany stelaż; zwężające się ku dołowi nogi; odsłonięte drewniane elementy boczne; kompaktowe proporcje; geometryczny profil boczny; forma inspirowana skandynawskim modernizmem</t>
+    <t>slim silhouette; compact proportions; wide silhouette; open wooden side frame; solid wooden frame; straight side rails; high upholstered backrest; tapered rectangular backrest; slightly reclined backrest; rounded backrest corners; thick upholstered backrest; deep upholstered seat; rounded front seat edge; rectangular seat; no armrests; splayed tapered legs; straight tapered legs; tapered wooden legs; front legs attached to side rails; rear legs integrated into backrest; visible side bolts; visible screw joints; lower stretcher; smooth upholstery; open space under seat; large exposed wooden frame; visible wooden side rails</t>
   </si>
   <si>
     <t>Typ 300-139</t>
@@ -979,13 +758,16 @@
     <t>Stefan</t>
   </si>
   <si>
+    <t>300-139</t>
+  </si>
+  <si>
     <t>Swarzędzka Fabryka Mebli</t>
   </si>
   <si>
-    <t>szerokie drewniane podłokietniki o łagodnym łuku; otwarta konstrukcja boczna; luźne tapicerowane poduchy siedziska i oparcia; rozłożysta bryła; lekka skandynawska stylistyka; nisko osadzone siedzisko; masywny drewniany stelaż</t>
-  </si>
-  <si>
-    <t>stelaż z litego drewna bukowego; otwarta rama boczna; osobna poduszka siedziska; osobna poduszka oparcia; pasy tapicerskie; konstrukcja szkieletowa skręcana</t>
+    <t>Fotel o niskiej, szerokiej sylwetce z wyraźnie odchylonym oparciem i głębokim siedziskiem. Oparcie ma prostokątny kształt z lekko zaokrąglonymi narożnikami i stanowi oddzielną, grubą poduszkę osadzoną pod kątem. Siedzisko jest szerokie, prostokątne, grubo tapicerowane, z prostą przednią krawędzią i wyraźnie zaznaczoną grubością. Konstrukcja drewniana jest w dużej części odsłonięta i tworzy otwartą ramę boczną z prostokątnymi podłokietnikami o delikatnie zwężającym się przekroju. Podłokietniki przechodzą płynnie w przednie podpory i łączą się z tylną częścią ramy. Nogi są smukłe, lekko rozstawione na zewnątrz i zwężają się ku dołowi. Od tyłu widoczne jest oparcie wsparte szeregiem pionowych drewnianych listew pomiędzy górną i dolną belką.</t>
+  </si>
+  <si>
+    <t>Konstrukcja oparta na otwartym drewnianym stelażu z wyraźnie wyeksponowanymi bocznymi ramami połączonymi dolnymi belkami poprzecznymi. Siedzisko i oparcie wykonane są jako dwa oddzielne tapicerowane moduły osadzone wewnątrz drewnianej konstrukcji. Oparcie podparte jest zespołem pionowych drewnianych listew zamocowanych pomiędzy górną i dolną belką tylnej ramy oraz ustawione pod kątem względem siedziska. Podłokietniki stanowią integralną część bocznych ram i są połączone z przednimi podporami oraz tylną częścią konstrukcji. Pod siedziskiem widoczne są drewniane belki nośne tworzące otwartą konstrukcję bez pełnych paneli bocznych. Nie są widoczne odsłonięte śruby ani metalowe elementy mocujące.</t>
   </si>
   <si>
     <t>typ 300-123 Puchała; typ 366; duńskie fotele Kandidaten projektu Ib Kofod-Larsena; fotele skandynawskie lat 60</t>
@@ -997,22 +779,25 @@
     <t>„Meble w produkcji 1962” – Zjednoczenie Przemysłu Meblarskiego; „Meble do małych mieszkań. Informator”, Wydawnictwo Katalogów i Cenników 1966; Laminerva – „Ikony polskiego designu: Fotel Stefan typ 300-139”; Meblostan – Para foteli Stefan typ 300-139; Patyna – Para foteli Stefan typ 300-139</t>
   </si>
   <si>
-    <t>szerokie wyprofilowane drewniane podłokietniki; otwarta drewniana rama boczna; luźna poduszka siedziska; luźna poduszka oparcia; nisko osadzone głębokie siedzisko; prostokątne grube poduchy; lekko odchylone oparcie; masywny bukowy stelaż; duży prześwit pod siedziskiem; szeroki rozstaw przednich nóg; profil boczny inspirowany wzornictwem skandynawskim; rozłożysta bryła eksportowa</t>
+    <t>low wide silhouette; wide silhouette; open wooden side frame; large exposed wooden frame; rectangular wooden armrests; integrated wooden armrests; straight armrests; angled armrest supports; high upholstered backrest; rectangular backrest; slightly reclined backrest; thick upholstered backrest; deep upholstered seat; rectangular seat; thick seat cushion; separate back cushion; separate seat cushion; solid wooden frame; open space under seat; visible wooden side rails; exposed wooden seat frame; vertical back slats; slatted back support; tapered wooden legs; splayed tapered legs; front legs integrated into side frame; rear legs integrated into backrest; lower side stretcher; smooth upholstery; flush upholstered surfaces; minimal exposed hardware; rounded frame transitions; inclined backrest frame; geometric side profile; open frame construction; thick seat profile; thick backrest profile; continuous side frame; exposed rear slat structure</t>
   </si>
   <si>
     <t>B-3300</t>
   </si>
   <si>
+    <t>b3300</t>
+  </si>
+  <si>
     <t>ok. 1969; produkcja w końcu lat 60. i na początku lat 70. XX w</t>
   </si>
   <si>
     <t>Zakład Mebli Giętych w Radomsku; Fabryki Mebli Radomsko (późniejsze nazewnictwo zakładu)</t>
   </si>
   <si>
-    <t>gięte drewniane podłokietniki; szerokie tapicerowane siedzisko; prostokątne tapicerowane oparcie; otwarta konstrukcja boczna; gięty bukowy stelaż; nisko osadzona bryła; elegancka modernistyczna forma</t>
-  </si>
-  <si>
-    <t>stelaż z giętego drewna bukowego; tapicerowane siedzisko; tapicerowane oparcie; konstrukcja szkieletowa; elementy gięte wykonane w technologii Thoneta; konstrukcja skręcana</t>
+    <t>Mebel odznacza się przysadzistą, szeroką sylwetką z mocno wyeksponowanym, giętym stelażem drewnianym o ciemnym wybarwieniu. Charakterystycznym elementem jest półokrągłe oparcie w kształcie podkowy, które płynnie przechodzi w zintegrowane, pochylone ku przodowi podłokietniki. Oparcie składa się z grubej, zakrzywionej ramy drewnianej o okrągłym przekroju oraz tapicerowanego pasa, którego krawędzie są ozdobione gęsto rozmieszczonymi, metalowymi pineskami tapicerskimi. Poniżej głównego luku oparcia biegnie dodatkowa, równoległa poprzeczka z giętego drewna, stabilizująca konstrukcję i tworząca prześwit w tylnej części. Siedzisko jest trapezowate, płaskie, z lekko zaokrąglonymi rogami, obszyte gładką tkaniną i zamontowane na szerokich, łukowato wygiętych cargach. Nogi przednie są proste, zwężające się ku dołowi, natomiast nogi tylne są silnie odchylone do tyłu pod ostrym kątem, co nadaje meblowi dynamiczny profil boczny.</t>
+  </si>
+  <si>
+    <t>Szkielet mebla wykonany jest w całości z litego, giętego drewna o okrągłych i owalnych przekrojach elementów. Konstrukcja oparcia opiera się na dwupoziomowej, półkolistej ramie, gdzie górny pałąk zintegrowany z podłokietnikami połączony jest pionowymi i skośnymi wspornikami z dolną ramą siedziska oraz tylnymi nogami. Tapicerowany pas oparcia jest rozpięty wewnątrz drewnianego łuku i przymocowany za pomocą ozdobnych gwoździ tapicerskich. Siedzisko jest zamontowane na masywnej skrzyni z szerokich, giętych listew (carag), tworzących stabilną podstawę. Przednie pionowe nogi są bezpośrednio połączone z zakończeniami podłokietników oraz cargą, podczas gdy skośne nogi tylne krzyżują się z dolnym pałąkiem oparcia, zapewniając sztywność strukturalną. Połączenia stolarskie są gładkie, klejone, bez widocznych metalowych śrub zewnętrznych na bokach.</t>
   </si>
   <si>
     <t>B-310 VAR; B-6028; GFM-64; typ 300-139 Stefan</t>
@@ -1024,7 +809,207 @@
     <t>Patyna – Fotel B-3300 Zakład Mebli Giętych w Radomsku; Meblostan – Para foteli B-3300; archiwalne materiały Fabryk Mebli Radomsko; oferty kolekcjonerskie dokumentujące oryginalne oznaczenie modelu</t>
   </si>
   <si>
-    <t>gięte drewniane podłokietniki; otwarta drewniana rama boczna; szerokie prostokątne oparcie; szerokie głębokie siedzisko; bukowy gięty stelaż; duży prześwit pod siedziskiem; łagodnie wygięte boki; zwężające się ku dołowi nogi; lekko pochylone oparcie; masywniejsza bryła niż typ 366; widoczne elementy z giętego drewna; modernistyczna forma gabinetowa</t>
+    <t>horseshoe backrest; wrap-around wooden frame; curved wooden armrests; sloping armrests; low upholstered backrest; decorative upholstery tacks; brass stud trim; exposed wooden frame; dark stained wood; bentwood frame construction; splayed rear legs; straight tapered front legs; trapezoidal seat; smooth upholstery; lower rear stretcher; open space under backrest; wide silhouette; compact proportions; round profile wooden rails; structural wooden supports; integrated side frame; robust wooden structure; angled rear supports; solid wood frame; padded backrest band</t>
+  </si>
+  <si>
+    <t>Prompt 1</t>
+  </si>
+  <si>
+    <t>Analyze this object.
+Please provide:
+1. What type of object is it?
+2. What specific model or product do you think it might be?
+3. What visual characteristics support your conclusion?
+4. How confident are you (0-100%)?
+5. List up to 3 alternative identifications.</t>
+  </si>
+  <si>
+    <t>Prompt 2</t>
+  </si>
+  <si>
+    <t>This object comes from Polish PRL-era design (1945-1989).
+Identify the most likely object, designer or model.
+Provide confidence score and alternative matches.</t>
+  </si>
+  <si>
+    <t>Chat</t>
+  </si>
+  <si>
+    <t>Photo</t>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <t>Top 1</t>
+  </si>
+  <si>
+    <t>Exact</t>
+  </si>
+  <si>
+    <t>Top3 contains</t>
+  </si>
+  <si>
+    <t>Model Family</t>
+  </si>
+  <si>
+    <t>Designer</t>
+  </si>
+  <si>
+    <t>Confidence</t>
+  </si>
+  <si>
+    <t>Error Type</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Leakage</t>
+  </si>
+  <si>
+    <t>Gemini</t>
+  </si>
+  <si>
+    <t>1,4,8</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Correct</t>
+  </si>
+  <si>
+    <t>GPT</t>
+  </si>
+  <si>
+    <t>Minor</t>
+  </si>
+  <si>
+    <t>2,3,10</t>
+  </si>
+  <si>
+    <t>lisek</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Incorrect</t>
+  </si>
+  <si>
+    <t>Major</t>
+  </si>
+  <si>
+    <t>1,5,6</t>
+  </si>
+  <si>
+    <t>B-310</t>
+  </si>
+  <si>
+    <t>7,9,10</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>1,2,6</t>
+  </si>
+  <si>
+    <t>Navrátil Shell Chair</t>
+  </si>
+  <si>
+    <t>DDR "Cocktailsessel"</t>
+  </si>
+  <si>
+    <t>2,3,7</t>
+  </si>
+  <si>
+    <t>Generic PRL armchair</t>
+  </si>
+  <si>
+    <t>1,6,9</t>
+  </si>
+  <si>
+    <t>Eames Fiberglass Armchair</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>Djinn Armchair</t>
+  </si>
+  <si>
+    <t>F588 Groovy Chair</t>
+  </si>
+  <si>
+    <t>halabala</t>
+  </si>
+  <si>
+    <t>skoczek</t>
+  </si>
+  <si>
+    <t>GFM</t>
+  </si>
+  <si>
+    <t>Aga 200 125</t>
+  </si>
+  <si>
+    <t>200-192</t>
+  </si>
+  <si>
+    <t>b6028</t>
+  </si>
+  <si>
+    <t>Type 366</t>
+  </si>
+  <si>
+    <t>Type 300-190</t>
+  </si>
+  <si>
+    <t>Typ 296 "Motylek"</t>
+  </si>
+  <si>
+    <t>Type 1020</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>typ 200-190</t>
+  </si>
+  <si>
+    <t>Type 200-190 "Aga"</t>
+  </si>
+  <si>
+    <t>Type 200-190</t>
+  </si>
+  <si>
+    <t>typ 300-227</t>
+  </si>
+  <si>
+    <t>Unidentified Danish-style lounge chair</t>
+  </si>
+  <si>
+    <t>Type 300-177</t>
+  </si>
+  <si>
+    <t>B3300</t>
+  </si>
+  <si>
+    <t>Contemporary Danish/Scandinavian-inspired dining armchair</t>
+  </si>
+  <si>
+    <t>MVP</t>
   </si>
   <si>
     <t>Cechy AI</t>
@@ -1110,6 +1095,9 @@
 drewniany stelaż</t>
   </si>
   <si>
+    <t>trójkątne podłokietniki przypominające uszy zająca; otwarta drewniana rama boczna; szeroko rozstawione nogi; podłokietniki połączone z przednimi nogami; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; duży prześwit pod siedziskiem; smukła lekka bryła; odsłonięty drewniany stelaż; skośne tylne nogi; geometryczny profil boczny; kompaktowe proporcje</t>
+  </si>
+  <si>
     <t>muszelkowy korpus;
 kubełkowe siedzisko;
 jednolita tapicerowana bryła;
@@ -1135,6 +1123,53 @@
 otwarta konstrukcja;
 obszerne siedzisko;
 obszerne oparcie</t>
+  </si>
+  <si>
+    <t>gięte drewniane podłokietniki; smukłe wysokie oparcie; wąskie proporcje korpusu; otwarta drewniana rama boczna; toczone nogi zwężające się ku dołowi; widoczny prześwit pod siedziskiem; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; lekka dynamiczna bryła; cienkie elementy konstrukcyjne; profil boczny z łukowato wygiętym podłokietnikiem; minimalistyczna forma lat 50./60.</t>
+  </si>
+  <si>
+    <t>jednoczęściowa muszelkowa skorupa; organiczna opływowa bryła; głębokie kubełkowe siedzisko; szerokie wywinięte boki; zaokrąglone wysokie oparcie; brak oddzielnych podłokietników; korpus przypominający muszlę; zamknięta forma boczna; cztery cienkie nogi; futurystyczna sylwetka lat 50.; brak widocznej drewnianej konstrukcji; płynne przejścia między siedziskiem i oparciem; asymetrycznie zaokrąglone krawędzie; korpus wykonany jako pojedyncza skorupa</t>
+  </si>
+  <si>
+    <t>kubełkowe siedzisko; forma przypominająca kielich tulipana; szeroko rozchylone boki; jednolita tapicerowana skorupa; zaokrąglone wysokie oparcie; płynne przejście między siedziskiem i oparciem; organiczna bryła; brak widocznej drewnianej ramy bocznej; miękkie obłe krawędzie; rzeźbiarska forma; kompaktowa podstawa; sylwetka kwiatu tulipana</t>
+  </si>
+  <si>
+    <t>otwarta drewniana rama boczna; prostokątne tapicerowane oparcie; prostokątne tapicerowane siedzisko; smukła lekka bryła; duży prześwit pod siedziskiem; drewniane podłokietniki zintegrowane z ramą; nogi graniaste od góry; nogi zaokrąglone w dolnej części; skośne tylne nogi; widoczne drewniane elementy konstrukcyjne; forma zbliżona do modelu Lisek; geometryczny profil boczny
+Źródła potwierdzają produkcję w Bystrzyckiej Fabryce Mebli oraz silne pokrewieństwo konstrukcyjne z modelem 300-190 „Lisek”, natomiast projektant pozostaje niepotwierdzony.</t>
+  </si>
+  <si>
+    <t>łukowate podłokietniki przypominające skocznię narciarską; elipsoidalne oparcie; otwarta drewniana rama boczna; smukłe zwężające się nogi; tapicerowane siedzisko; duży prześwit pod siedziskiem; płynna linia podłokietnika przechodząca w nogę; lekka ażurowa konstrukcja; organiczny profil boczny; oparcie w kształcie pionowej elipsy; cienkie elementy drewniane; dynamiczna sylwetka inspirowana skokami narciarskimi
+Źródła potwierdzają, że model został zaprojektowany przez Juliusza Kędziorka w Gościcińskiej Fabryce Mebli w 1965 r., otrzymał nagrodę „Dobre–Ładne–Poszukiwane” i został skierowany do produkcji seryjnej jako typ 200-203</t>
+  </si>
+  <si>
+    <t>wysokie tapicerowane oparcie; trapezowy układ nóg; szerokie miękkie siedzisko; brak podłokietników; drewniane nogi rozszerzające się ku dołowi; zwężająca się ku górze sylwetka; lekka skandynawska forma; prostokątne oparcie z zaokrąglonymi krawędziami; widoczne drewniane elementy boczne; smukłe proporcje; geometryczna bryła; profil boczny z pochylonym oparciem</t>
+  </si>
+  <si>
+    <t>okrągłe oparcie przypominające grzybek; oparcie szersze od wspornika; tapicerowane okrągłe oparcie; tapicerowane siedzisko; smukłe nogi zwężające się ku dołowi; brak podłokietników; lekka skandynawska forma; duży prześwit pod siedziskiem; cienki drewniany stelaż; wyraźne oddzielenie oparcia od siedziska; geometryczna bryła; profil boczny z lekko odchylonym oparciem</t>
+  </si>
+  <si>
+    <t>wysokie prostokątne oparcie; szerokie drewniane podłokietniki; gięte boczne elementy z drewna; otwarta rama boczna; głębokie siedzisko; masywniejsza bryła niż typ 366; bukowy stelaż; duży prześwit pod siedziskiem; profilowane podłokietniki; smukłe nogi zintegrowane z ramą; tapicerowane oparcie i siedzisko; geometryczny profil boczny</t>
+  </si>
+  <si>
+    <t>masywne drewniane podłokietniki; szerokie głębokie siedzisko; wysunięte przednie podłokietniki; otwarta drewniana rama boczna; prostokątne tapicerowane oparcie; grube proporcje siedziska; lekko pochylone oparcie; duży prześwit pod siedziskiem; widoczne śruby montażowe w ramie; geometryczny profil boczny; szeroki rozstaw nóg; cięższa bryła niż typ 366; bukowy stelaż; modernistyczna forma eksportowa</t>
+  </si>
+  <si>
+    <t>nerkowate tapicerowane oparcie; oparcie szersze od wspornika; smukłe zwężające się nogi; lekka ażurowa konstrukcja; gięta drewniana rama; prostokątne tapicerowane siedzisko; duży prześwit pod siedziskiem; cienkie elementy konstrukcyjne; szeroko rozstawione tylne nogi; profil boczny z delikatnie pochylonym oparciem; organiczny kształt oparcia; minimalistyczna sylwetka lat 60.</t>
+  </si>
+  <si>
+    <t>muszelkowe profilowane oparcie; jednolita tapicerowana skorupa; zaokrąglona górna krawędź oparcia; płynne przejście oparcia w siedzisko; brak podłokietników; cztery smukłe stożkowe drewniane nogi; lekka organiczna bryła; profilowana skorupa ze sklejki; niewielki prześwit pod siedziskiem; forma inspirowana muszlą</t>
+  </si>
+  <si>
+    <t>łukowato wygięte przednie nogi w kształcie bumerangu; gięte boczne elementy drewniane; tapicerowane prostokątne siedzisko; tapicerowane oparcie; smukła lekka bryła; cienki drewniany stelaż; zwężające się ku dołowi nogi; wyraźny prześwit pod siedziskiem; organiczny profil boczny; lekko odchylone oparcie; minimalistyczna forma lat 60.; charakterystyczna sylwetka bumerangu</t>
+  </si>
+  <si>
+    <t>brak podłokietników; toczone drewniane nogi umieszczone po bokach korpusu; trapezowe tapicerowane siedzisko; prostokątne tapicerowane oparcie; lekka minimalistyczna bryła; duży prześwit pod siedziskiem; cienki drewniany stelaż; zwężające się ku dołowi nogi; odsłonięte drewniane elementy boczne; kompaktowe proporcje; geometryczny profil boczny; forma inspirowana skandynawskim modernizmem</t>
+  </si>
+  <si>
+    <t>szerokie wyprofilowane drewniane podłokietniki; otwarta drewniana rama boczna; luźna poduszka siedziska; luźna poduszka oparcia; nisko osadzone głębokie siedzisko; prostokątne grube poduchy; lekko odchylone oparcie; masywny bukowy stelaż; duży prześwit pod siedziskiem; szeroki rozstaw przednich nóg; profil boczny inspirowany wzornictwem skandynawskim; rozłożysta bryła eksportowa</t>
+  </si>
+  <si>
+    <t>gięte drewniane podłokietniki; otwarta drewniana rama boczna; szerokie prostokątne oparcie; szerokie głębokie siedzisko; bukowy gięty stelaż; duży prześwit pod siedziskiem; łagodnie wygięte boki; zwężające się ku dołowi nogi; lekko pochylone oparcie; masywniejsza bryła niż typ 366; widoczne elementy z giętego drewna; modernistyczna forma gabinetowa</t>
   </si>
 </sst>
 </file>
@@ -1260,6 +1295,12 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1591,12 +1632,6 @@
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -1611,8 +1646,38 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAC340A0-F689-4CF5-934F-277213A09CD2}" name="Tabela1" displayName="Tabela1" ref="A2:M42" totalsRowShown="0" headerRowDxfId="20">
-  <autoFilter ref="A2:M42" xr:uid="{AAC340A0-F689-4CF5-934F-277213A09CD2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0B9BF425-AAE6-496E-A318-81223EDA70A0}" name="Table2" displayName="Table2" ref="A1:O21" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="A1:O21" xr:uid="{0B9BF425-AAE6-496E-A318-81223EDA70A0}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{BEC8128C-B6F8-41AF-8B4E-AC51172C6F9B}" name="ID" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{A4D5EBAD-8137-4068-9AB3-4017AE021691}" name="Model" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{2E31A0DA-DF43-4372-8896-81E05381952A}" name="Potoczna nazwa" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{21289632-27BD-4A17-A0EC-06689B74EAF5}" name="REFERENCE_ID" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{BFBF567B-85D5-410F-86B7-E7A5AE9C3740}" name="Projektant" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{C0BA823A-68AD-4568-86DC-D7A0821FE81E}" name="Rok" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{A85EDE16-4C80-416A-961D-E6418592861C}" name="Typ" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{B6F3255D-9933-44DB-84CE-345F6ADC20CF}" name="Producent" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{444D790F-7610-4FF6-B3B8-84C2F85CD109}" name="Cechy Charakterystyczne" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{98CF13B3-BB3C-451C-BD71-AA322E9D297B}" name="Konstrukcja" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{CED6A324-3FA7-4066-97E4-A5BE6D00D638}" name="Mylony z" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{7D23AC8B-5C76-4D9D-94A1-5E0E701AC60B}" name="Rodzina modeli" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{6E7FC306-D5DA-4E3A-8481-0DE3695A5890}" name="Źródła" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{86F52982-86F4-44FD-8A46-84423C74DFF2}" name="Poziom pewności" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{633CC391-CD9D-4406-9436-B55C83554066}" name="Search Features" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAC340A0-F689-4CF5-934F-277213A09CD2}" name="Tabela1" displayName="Tabela1" ref="A2:M62" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A2:M62" xr:uid="{AAC340A0-F689-4CF5-934F-277213A09CD2}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="MVP"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M8">
     <sortCondition ref="C2:C8"/>
   </sortState>
@@ -1625,37 +1690,13 @@
     <tableColumn id="5" xr3:uid="{FC87805C-8F21-4877-A2BB-F94A46848488}" name="Top3 contains"/>
     <tableColumn id="12" xr3:uid="{083260FC-C283-425D-8992-A120FCD63F58}" name="Model Family"/>
     <tableColumn id="6" xr3:uid="{C375EF1E-B099-4419-8B9C-B2440FD0A8ED}" name="Designer"/>
-    <tableColumn id="7" xr3:uid="{DD17F6C6-7610-4EE0-A977-F8A13F1B8EBA}" name="Confidence" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{DD17F6C6-7610-4EE0-A977-F8A13F1B8EBA}" name="Confidence" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{B609250C-19DF-4BCE-8148-69FA85A5C4D5}" name="Error Type"/>
     <tableColumn id="9" xr3:uid="{7ECB45DF-B162-4E08-85FE-5889D14F4EA2}" name="Notes"/>
     <tableColumn id="10" xr3:uid="{7DB3FB91-9C91-4420-A0AD-58F455F6AD18}" name="Severity"/>
     <tableColumn id="11" xr3:uid="{96BAEC9B-0AC8-4906-ABDE-8FA5C27BD1EF}" name="Leakage"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0B9BF425-AAE6-496E-A318-81223EDA70A0}" name="Table2" displayName="Table2" ref="A1:O21" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:O21" xr:uid="{0B9BF425-AAE6-496E-A318-81223EDA70A0}"/>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{BEC8128C-B6F8-41AF-8B4E-AC51172C6F9B}" name="ID" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{A4D5EBAD-8137-4068-9AB3-4017AE021691}" name="Model" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{2E31A0DA-DF43-4372-8896-81E05381952A}" name="Potoczna nazwa" dataDxfId="14"/>
-    <tableColumn id="16" xr3:uid="{21289632-27BD-4A17-A0EC-06689B74EAF5}" name="REFERENCE_ID" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{BFBF567B-85D5-410F-86B7-E7A5AE9C3740}" name="Projektant" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{C0BA823A-68AD-4568-86DC-D7A0821FE81E}" name="Rok" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{A85EDE16-4C80-416A-961D-E6418592861C}" name="Typ" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{B6F3255D-9933-44DB-84CE-345F6ADC20CF}" name="Producent" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{444D790F-7610-4FF6-B3B8-84C2F85CD109}" name="Cechy Charakterystyczne" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{98CF13B3-BB3C-451C-BD71-AA322E9D297B}" name="Konstrukcja" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{CED6A324-3FA7-4066-97E4-A5BE6D00D638}" name="Mylony z" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{7D23AC8B-5C76-4D9D-94A1-5E0E701AC60B}" name="Rodzina modeli" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{6E7FC306-D5DA-4E3A-8481-0DE3695A5890}" name="Źródła" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{86F52982-86F4-44FD-8A46-84423C74DFF2}" name="Poziom pewności" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{633CC391-CD9D-4406-9436-B55C83554066}" name="Search Features" dataDxfId="2"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1966,19 +2007,1022 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E570A043-1276-4CEE-AF12-19208D26EAA5}">
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" customWidth="1"/>
+    <col min="8" max="8" width="24.5703125" customWidth="1"/>
+    <col min="9" max="9" width="36.5703125" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" customWidth="1"/>
+    <col min="11" max="11" width="27" customWidth="1"/>
+    <col min="12" max="12" width="31" customWidth="1"/>
+    <col min="13" max="13" width="24.140625" customWidth="1"/>
+    <col min="14" max="14" width="18.5703125" customWidth="1"/>
+    <col min="15" max="15" width="17.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="409.6">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="9">
+        <v>366</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="409.6">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="9">
+        <v>1967</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="409.6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="409.6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="N5" s="11">
+        <v>0.82</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="409.6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="9">
+        <v>1962</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="N6" s="11">
+        <v>0.85</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="409.6">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="N7" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="409.6">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="9">
+        <v>1958</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="N8" s="11">
+        <v>0.99</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="409.6">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="N9" s="11">
+        <v>0.92</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="409.6">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="N10" s="11">
+        <v>0.87</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="409.6">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="9">
+        <v>1965</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="N11" s="11">
+        <v>0.96</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="409.6">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="N12" s="11">
+        <v>0.94</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="409.6">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="N13" s="11">
+        <v>0.96</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="409.6">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="N14" s="11">
+        <v>0.72</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="409.6">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="N15" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="409.6">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="N16" s="11">
+        <v>0.93</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="409.6">
+      <c r="A17" s="9">
+        <v>16</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D17" s="9">
+        <v>1020</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17" s="9">
+        <v>1962</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="N17" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="409.6">
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="N18" s="11">
+        <v>0.91</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="409.6">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D19" t="s">
+        <v>205</v>
+      </c>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="N19" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="409.6">
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="N20" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="409.6">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="N21" s="11">
+        <v>0.86</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U50"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="64.5703125" customWidth="1"/>
     <col min="21" max="21" width="69" customWidth="1"/>
   </cols>
@@ -2001,57 +3045,57 @@
       <c r="P1" s="13"/>
       <c r="Q1" s="13"/>
       <c r="R1" s="2" t="s">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>2</v>
+        <v>236</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>3</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>238</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>5</v>
+        <v>239</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>6</v>
+        <v>240</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>7</v>
+        <v>241</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>8</v>
+        <v>242</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>9</v>
+        <v>243</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>10</v>
+        <v>244</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>11</v>
+        <v>245</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>12</v>
+        <v>246</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>13</v>
+        <v>247</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>14</v>
+        <v>248</v>
       </c>
       <c r="L2" t="s">
-        <v>15</v>
+        <v>249</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>16</v>
+        <v>250</v>
       </c>
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
@@ -2061,12 +3105,12 @@
       <c r="S2" s="1"/>
       <c r="U2" s="1"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" hidden="1">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>366</v>
@@ -2075,27 +3119,27 @@
         <v>366</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="I3" s="4">
         <v>0.98</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" hidden="1">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>366</v>
@@ -2104,2215 +3148,1546 @@
         <v>366</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="I4" s="4">
         <v>0.9</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>21</v>
+        <v>255</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" hidden="1">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>258</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>259</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="I5" s="4">
         <v>0.98</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" hidden="1">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>258</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>260</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>260</v>
       </c>
       <c r="I6" s="4">
         <v>0.75</v>
       </c>
       <c r="K6" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" hidden="1">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>264</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>366</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>260</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>260</v>
       </c>
       <c r="I7" s="4">
         <v>0.95</v>
       </c>
       <c r="K7" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" hidden="1">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>264</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>265</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>260</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>260</v>
       </c>
       <c r="I8" s="4">
         <v>0.8</v>
       </c>
       <c r="K8" t="s">
+        <v>262</v>
+      </c>
+      <c r="L8" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" hidden="1">
+      <c r="A9" t="s">
+        <v>251</v>
+      </c>
+      <c r="B9" t="s">
+        <v>266</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="L8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>260</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="I9" s="4">
         <v>0.98</v>
       </c>
       <c r="K9" t="s">
+        <v>262</v>
+      </c>
+      <c r="L9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" hidden="1">
+      <c r="A10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
         <v>29</v>
       </c>
-      <c r="L9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>260</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G10" t="s">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="I10" s="4">
         <v>0.85</v>
       </c>
       <c r="K10" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" hidden="1">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>268</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>269</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I11" s="4">
         <v>0.85</v>
       </c>
       <c r="K11" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" hidden="1">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>268</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>270</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I12" s="4">
         <v>0.85</v>
       </c>
       <c r="K12" t="s">
+        <v>262</v>
+      </c>
+      <c r="L12" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" hidden="1">
+      <c r="A13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" t="s">
+        <v>271</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
         <v>29</v>
       </c>
-      <c r="L12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" t="s">
-        <v>35</v>
-      </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="I13" s="4">
         <v>0.98</v>
       </c>
       <c r="K13" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" hidden="1">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>271</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>272</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I14" s="4">
         <v>0.85</v>
       </c>
       <c r="K14" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" hidden="1">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>273</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="I15" s="4">
         <v>0.95</v>
       </c>
       <c r="K15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" hidden="1">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>273</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>274</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G16" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I16" s="4">
         <v>0.75</v>
       </c>
       <c r="K16" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" hidden="1">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>276</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F17" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G17" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I17" s="4">
         <v>0.99</v>
       </c>
       <c r="K17" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" hidden="1">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>277</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G18" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I18" s="4">
         <v>0.95</v>
       </c>
       <c r="K18" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" hidden="1">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="D19">
         <v>366</v>
       </c>
       <c r="E19" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F19" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G19" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I19" s="4">
         <v>0.98</v>
       </c>
       <c r="K19" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" hidden="1">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>278</v>
       </c>
       <c r="E20" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G20" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I20" s="4">
         <v>0.35</v>
       </c>
       <c r="K20" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" hidden="1">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>279</v>
       </c>
       <c r="D21">
         <v>296</v>
       </c>
       <c r="E21" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G21" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I21" s="4">
         <v>0.85</v>
       </c>
       <c r="K21" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" hidden="1">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>279</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>280</v>
       </c>
       <c r="E22" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G22" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I22" s="4">
         <v>0.85</v>
       </c>
       <c r="K22" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L22" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" hidden="1">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>282</v>
       </c>
       <c r="E23" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F23" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G23" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I23" s="4">
         <v>0.95</v>
       </c>
       <c r="K23" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" hidden="1">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>272</v>
       </c>
       <c r="E24" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F24" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G24" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I24" s="4">
         <v>0.95</v>
       </c>
       <c r="K24" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" hidden="1">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="G25" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="H25" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="I25" s="4">
         <v>0.98</v>
       </c>
       <c r="K25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" hidden="1">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E26" t="s">
-        <v>27</v>
+        <v>260</v>
       </c>
       <c r="F26" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G26" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I26" s="4">
         <v>0.85</v>
       </c>
       <c r="K26" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L26" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" hidden="1">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>283</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>284</v>
       </c>
       <c r="E27" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F27" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G27" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I27" s="4">
         <v>0.95</v>
       </c>
       <c r="K27" t="s">
+        <v>262</v>
+      </c>
+      <c r="L27" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" hidden="1">
+      <c r="A28" t="s">
+        <v>256</v>
+      </c>
+      <c r="B28" t="s">
+        <v>275</v>
+      </c>
+      <c r="C28" t="s">
+        <v>283</v>
+      </c>
+      <c r="D28" t="s">
         <v>29</v>
       </c>
-      <c r="L27" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" t="s">
-        <v>35</v>
-      </c>
       <c r="E28" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F28" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G28" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I28" s="4">
         <v>0.85</v>
       </c>
       <c r="K28" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L28" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" hidden="1">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C29" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="D29" t="s">
-        <v>61</v>
+        <v>285</v>
       </c>
       <c r="E29" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F29" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G29" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I29" s="4">
         <v>0.95</v>
       </c>
       <c r="K29" t="s">
+        <v>262</v>
+      </c>
+      <c r="L29" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" hidden="1">
+      <c r="A30" t="s">
+        <v>256</v>
+      </c>
+      <c r="B30" t="s">
+        <v>275</v>
+      </c>
+      <c r="C30" t="s">
+        <v>161</v>
+      </c>
+      <c r="D30" t="s">
         <v>29</v>
       </c>
-      <c r="L29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" t="s">
-        <v>35</v>
-      </c>
       <c r="E30" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G30" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I30" s="4">
         <v>0.85</v>
       </c>
       <c r="K30" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L30" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" hidden="1">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
+        <v>172</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>286</v>
       </c>
       <c r="E31" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F31" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G31" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I31" s="4">
         <v>0.95</v>
       </c>
       <c r="K31" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" hidden="1">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>172</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F32" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G32" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I32" s="4">
         <v>0.85</v>
       </c>
       <c r="K32" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" hidden="1">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>287</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>287</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="F33" t="s">
-        <v>65</v>
+        <v>288</v>
       </c>
       <c r="G33" t="s">
-        <v>65</v>
+        <v>288</v>
       </c>
       <c r="I33" s="4">
         <v>0.95</v>
       </c>
       <c r="K33" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" hidden="1">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>287</v>
       </c>
       <c r="D34" t="s">
-        <v>66</v>
+        <v>289</v>
       </c>
       <c r="E34" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G34" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I34" s="4">
         <v>0.7</v>
       </c>
       <c r="K34" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L34" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" hidden="1">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C35" t="s">
-        <v>67</v>
+        <v>191</v>
       </c>
       <c r="D35" t="s">
-        <v>68</v>
+        <v>290</v>
       </c>
       <c r="E35" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F35" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G35" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I35" s="4">
         <v>0.95</v>
       </c>
       <c r="K35" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L35" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" hidden="1">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>191</v>
       </c>
       <c r="D36" t="s">
-        <v>69</v>
+        <v>291</v>
       </c>
       <c r="E36" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F36" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G36" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I36" s="4">
         <v>0.95</v>
       </c>
       <c r="K36" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L36" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" hidden="1">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C37" t="s">
-        <v>70</v>
+        <v>292</v>
       </c>
       <c r="D37" t="s">
-        <v>61</v>
+        <v>285</v>
       </c>
       <c r="E37" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F37" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G37" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I37" s="4">
         <v>0.95</v>
       </c>
       <c r="K37" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L37" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" hidden="1">
       <c r="A38" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C38" t="s">
-        <v>70</v>
+        <v>292</v>
       </c>
       <c r="D38" t="s">
-        <v>71</v>
+        <v>293</v>
       </c>
       <c r="E38" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F38" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G38" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I38" s="4">
         <v>0.95</v>
       </c>
       <c r="K38" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L38" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" hidden="1">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C39" t="s">
-        <v>72</v>
+        <v>216</v>
       </c>
       <c r="D39" t="s">
-        <v>73</v>
+        <v>294</v>
       </c>
       <c r="E39" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F39" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G39" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I39" s="4">
         <v>0.95</v>
       </c>
       <c r="K39" t="s">
+        <v>262</v>
+      </c>
+      <c r="L39" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" hidden="1">
+      <c r="A40" t="s">
+        <v>256</v>
+      </c>
+      <c r="B40" t="s">
+        <v>275</v>
+      </c>
+      <c r="C40" t="s">
+        <v>216</v>
+      </c>
+      <c r="D40" t="s">
         <v>29</v>
       </c>
-      <c r="L39" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12">
-      <c r="A40" t="s">
-        <v>22</v>
-      </c>
-      <c r="B40" t="s">
-        <v>47</v>
-      </c>
-      <c r="C40" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40" t="s">
-        <v>35</v>
-      </c>
       <c r="E40" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F40" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G40" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I40" s="4">
         <v>0.82</v>
       </c>
       <c r="K40" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L40" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" hidden="1">
       <c r="A41" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C41" t="s">
-        <v>74</v>
+        <v>295</v>
       </c>
       <c r="D41" t="s">
-        <v>61</v>
+        <v>285</v>
       </c>
       <c r="E41" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F41" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G41" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I41" s="4">
         <v>0.95</v>
       </c>
       <c r="K41" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L41" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="30.75">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="30.75" hidden="1">
       <c r="A42" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C42" t="s">
-        <v>74</v>
+        <v>295</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>75</v>
+        <v>296</v>
       </c>
       <c r="E42" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="F42" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="G42" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I42" s="4">
         <v>0.95</v>
       </c>
       <c r="K42" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L42" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" t="s">
+        <v>297</v>
+      </c>
+      <c r="B43" t="s">
+        <v>252</v>
+      </c>
+      <c r="C43">
+        <v>366</v>
+      </c>
+      <c r="D43">
+        <v>366</v>
+      </c>
+      <c r="E43" t="s">
+        <v>254</v>
+      </c>
+      <c r="F43" t="s">
+        <v>254</v>
+      </c>
+      <c r="G43" t="s">
+        <v>254</v>
+      </c>
+      <c r="I43" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="K43" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" t="s">
+        <v>297</v>
+      </c>
+      <c r="B44" t="s">
+        <v>258</v>
+      </c>
+      <c r="C44" t="s">
+        <v>259</v>
+      </c>
+      <c r="D44" t="s">
+        <v>259</v>
+      </c>
+      <c r="E44" t="s">
+        <v>254</v>
+      </c>
+      <c r="F44" t="s">
+        <v>254</v>
+      </c>
+      <c r="G44" t="s">
+        <v>254</v>
+      </c>
+      <c r="I44" s="4">
+        <v>0.87</v>
+      </c>
+      <c r="K44" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" t="s">
+        <v>297</v>
+      </c>
+      <c r="B45" t="s">
+        <v>264</v>
+      </c>
+      <c r="C45" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" t="s">
+        <v>259</v>
+      </c>
+      <c r="E45" t="s">
+        <v>261</v>
+      </c>
+      <c r="F45" t="s">
+        <v>254</v>
+      </c>
+      <c r="G45" t="s">
+        <v>254</v>
+      </c>
+      <c r="I45" s="4">
+        <v>0.97</v>
+      </c>
+      <c r="K45" t="s">
+        <v>262</v>
+      </c>
+      <c r="L45" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" t="s">
+        <v>297</v>
+      </c>
+      <c r="B46" t="s">
+        <v>266</v>
+      </c>
+      <c r="C46" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46">
+        <v>366</v>
+      </c>
+      <c r="E46" t="s">
+        <v>261</v>
+      </c>
+      <c r="F46" t="s">
+        <v>261</v>
+      </c>
+      <c r="G46" t="s">
+        <v>254</v>
+      </c>
+      <c r="I46" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="K46" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" t="s">
+        <v>297</v>
+      </c>
+      <c r="B47" t="s">
+        <v>268</v>
+      </c>
+      <c r="C47" t="s">
+        <v>61</v>
+      </c>
+      <c r="I47" s="4"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" t="s">
+        <v>297</v>
+      </c>
+      <c r="B48" t="s">
+        <v>271</v>
+      </c>
+      <c r="C48" t="s">
+        <v>73</v>
+      </c>
+      <c r="I48" s="4"/>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>297</v>
+      </c>
+      <c r="B49" t="s">
+        <v>273</v>
+      </c>
+      <c r="C49" t="s">
+        <v>84</v>
+      </c>
+      <c r="I49" s="4"/>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>297</v>
+      </c>
       <c r="B50" t="s">
-        <v>76</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C50" t="s">
+        <v>95</v>
+      </c>
+      <c r="I50" s="4"/>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>297</v>
+      </c>
+      <c r="B51" t="s">
+        <v>275</v>
+      </c>
+      <c r="C51" t="s">
+        <v>107</v>
+      </c>
+      <c r="I51" s="4"/>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
+        <v>297</v>
+      </c>
+      <c r="B52" t="s">
+        <v>275</v>
+      </c>
+      <c r="C52" t="s">
+        <v>279</v>
+      </c>
+      <c r="I52" s="4"/>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" t="s">
+        <v>297</v>
+      </c>
+      <c r="B53" t="s">
+        <v>275</v>
+      </c>
+      <c r="C53" t="s">
+        <v>281</v>
+      </c>
+      <c r="I53" s="4"/>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" t="s">
+        <v>297</v>
+      </c>
+      <c r="B54" t="s">
+        <v>275</v>
+      </c>
+      <c r="C54" t="s">
+        <v>140</v>
+      </c>
+      <c r="I54" s="4"/>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" t="s">
+        <v>297</v>
+      </c>
+      <c r="B55" t="s">
+        <v>275</v>
+      </c>
+      <c r="C55" t="s">
+        <v>283</v>
+      </c>
+      <c r="I55" s="4"/>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" t="s">
+        <v>297</v>
+      </c>
+      <c r="B56" t="s">
+        <v>275</v>
+      </c>
+      <c r="C56" t="s">
+        <v>161</v>
+      </c>
+      <c r="I56" s="4"/>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" t="s">
+        <v>297</v>
+      </c>
+      <c r="B57" t="s">
+        <v>275</v>
+      </c>
+      <c r="C57" t="s">
+        <v>172</v>
+      </c>
+      <c r="I57" s="4"/>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" t="s">
+        <v>297</v>
+      </c>
+      <c r="B58" t="s">
+        <v>275</v>
+      </c>
+      <c r="C58" t="s">
+        <v>287</v>
+      </c>
+      <c r="I58" s="4"/>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" t="s">
+        <v>297</v>
+      </c>
+      <c r="B59" t="s">
+        <v>275</v>
+      </c>
+      <c r="C59" t="s">
+        <v>191</v>
+      </c>
+      <c r="I59" s="4"/>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" t="s">
+        <v>297</v>
+      </c>
+      <c r="B60" t="s">
+        <v>275</v>
+      </c>
+      <c r="C60" t="s">
+        <v>292</v>
+      </c>
+      <c r="I60" s="4"/>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" t="s">
+        <v>297</v>
+      </c>
+      <c r="B61" t="s">
+        <v>275</v>
+      </c>
+      <c r="C61" t="s">
+        <v>216</v>
+      </c>
+      <c r="I61" s="4"/>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" t="s">
+        <v>297</v>
+      </c>
+      <c r="B62" t="s">
+        <v>275</v>
+      </c>
+      <c r="C62" t="s">
+        <v>295</v>
+      </c>
+      <c r="I62" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:Q1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E570A043-1276-4CEE-AF12-19208D26EAA5}">
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.5703125" customWidth="1"/>
-    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.7109375" customWidth="1"/>
-    <col min="11" max="11" width="27" customWidth="1"/>
-    <col min="12" max="12" width="31" customWidth="1"/>
-    <col min="13" max="13" width="24.140625" customWidth="1"/>
-    <col min="14" max="14" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="409.6">
-      <c r="A2" s="9">
-        <v>1</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D2" s="9">
-        <v>366</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="N2" s="11">
-        <v>0.98</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="409.6">
-      <c r="A3" s="9">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F3" s="9">
-        <v>1967</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="N3" s="11">
-        <v>0.88</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="409.6">
-      <c r="A4" s="9">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="N4" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="409.6">
-      <c r="A5" s="9">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="N5" s="11">
-        <v>0.82</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="409.6">
-      <c r="A6" s="9">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="F6" s="9">
-        <v>1962</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="N6" s="11">
-        <v>0.85</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="409.6">
-      <c r="A7" s="9">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="N7" s="11">
-        <v>0.9</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="409.6">
-      <c r="A8" s="9">
-        <v>7</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="F8" s="9">
-        <v>1958</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="N8" s="11">
-        <v>0.99</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="366">
-      <c r="A9" s="9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="N9" s="11">
-        <v>0.92</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="409.6">
-      <c r="A10" s="9">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="N10" s="11">
-        <v>0.87</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="409.6">
-      <c r="A11" s="9">
-        <v>10</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F11" s="9">
-        <v>1965</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="N11" s="11">
-        <v>0.96</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="409.6">
-      <c r="A12" s="9">
-        <v>11</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="N12" s="11">
-        <v>0.94</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="409.6">
-      <c r="A13" s="9">
-        <v>12</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="N13" s="11">
-        <v>0.96</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="366">
-      <c r="A14" s="9">
-        <v>13</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="N14" s="11">
-        <v>0.72</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="409.6">
-      <c r="A15" s="9">
-        <v>14</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="N15" s="11">
-        <v>0.9</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="396.75">
-      <c r="A16" s="9">
-        <v>15</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="N16" s="11">
-        <v>0.93</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="321">
-      <c r="A17" s="9">
-        <v>16</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="F17" s="9">
-        <v>1962</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="N17" s="11">
-        <v>0.9</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="381.75">
-      <c r="A18" s="9">
-        <v>17</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="N18" s="11">
-        <v>0.91</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="409.6">
-      <c r="A19" s="9">
-        <v>18</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="C19" t="s">
-        <v>266</v>
-      </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="N19" s="11">
-        <v>0.95</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="396.75">
-      <c r="A20" s="9">
-        <v>19</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="N20" s="11">
-        <v>0.95</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="366">
-      <c r="A21" s="9">
-        <v>20</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="N21" s="11">
-        <v>0.86</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>292</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -4331,170 +4706,170 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="7" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="381.75">
       <c r="A2" s="9" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="381.75">
       <c r="A3" s="9" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="366">
       <c r="A4" s="9" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="91.5">
       <c r="A5" s="9" t="s">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>134</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="381.75">
       <c r="A6" s="9" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="91.5">
       <c r="A7" s="9" t="s">
-        <v>144</v>
+        <v>71</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>153</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="106.5">
       <c r="A8" s="9" t="s">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>163</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="76.5">
       <c r="A9" s="9" t="s">
-        <v>164</v>
+        <v>93</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>174</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="152.25">
       <c r="A10" s="9" t="s">
-        <v>175</v>
+        <v>105</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>184</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="183">
       <c r="A11" s="9" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>195</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="91.5">
       <c r="A12" s="9" t="s">
-        <v>196</v>
+        <v>127</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>205</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="91.5">
       <c r="A13" s="9" t="s">
-        <v>206</v>
+        <v>138</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>216</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="76.5">
       <c r="A14" s="9" t="s">
-        <v>217</v>
+        <v>150</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>226</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="91.5">
       <c r="A15" s="9" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>235</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="91.5">
       <c r="A16" s="9" t="s">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>244</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="76.5">
       <c r="A17" s="9" t="s">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>254</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="91.5">
       <c r="A18" s="9" t="s">
-        <v>67</v>
+        <v>191</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>264</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="91.5">
       <c r="A19" s="9" t="s">
-        <v>265</v>
+        <v>203</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>274</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="91.5">
       <c r="A20" s="9" t="s">
-        <v>275</v>
+        <v>214</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="76.5">
       <c r="A21" s="9" t="s">
-        <v>284</v>
+        <v>224</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
